--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -5211,7 +5211,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -11555,7 +11555,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -11637,7 +11637,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -16868,7 +16868,7 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O203" t="inlineStr">
@@ -16950,7 +16950,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -23252,9 +23252,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -25215,14 +25215,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
+        </is>
+      </c>
       <c r="I305" t="inlineStr">
         <is>
           <t xml:space="preserve">caNT read</t>
-        </is>
-      </c>
-      <c r="J305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -19577,9 +19577,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -19654,9 +19654,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -20059,9 +20059,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -26793,9 +26793,9 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -28393,14 +28393,34 @@
       </c>
     </row>
     <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLAUDE BOX 1</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1</t>
+        </is>
+      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">hek caspex g8</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p23</t>
+          <t xml:space="preserve">P6</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -28410,12 +28430,12 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-07-28</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">28-07-25</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28425,193 +28445,253 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g8</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-emcm6az9</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLAUDE BOX 1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A2</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hek tox4 KO g8</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P5</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-28</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28-07-25</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
           <t xml:space="preserve">KO</t>
         </is>
       </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-243</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="E345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK gNT</t>
-        </is>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p18</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
+      <c r="M345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g8</t>
+        </is>
+      </c>
+      <c r="R345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-x8hm3iw7</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fff</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A1</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCAP</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p5</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L345" t="inlineStr">
+      <c r="H346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-28</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28-07-25</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
         </is>
       </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-329</t>
-        </is>
-      </c>
-    </row>
-    <row r="346">
-      <c r="E346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
-        </is>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p26</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr">
+      <c r="M346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-zde7yyzi</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fff</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A2</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lncap caspex</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P6</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="L346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX</t>
-        </is>
-      </c>
-      <c r="M346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-330</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="E347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
-        </is>
-      </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p18</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-07-28</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">28-07-25</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">3xFLAG</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -28621,7 +28701,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -28631,24 +28711,24 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">stored</t>
         </is>
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-331</t>
+          <t xml:space="preserve">v-rb9gprqv</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p23</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -28658,22 +28738,22 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -28688,7 +28768,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28698,19 +28778,19 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-355</t>
+          <t xml:space="preserve">v-243</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 KO rep 3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -28730,12 +28810,12 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -28750,7 +28830,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28760,19 +28840,19 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-356</t>
+          <t xml:space="preserve">v-329</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 OX rep 3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p26</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -28792,7 +28872,7 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -28822,67 +28902,315 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-357</t>
+          <t xml:space="preserve">v-330</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="E351" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p18</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/8/2026</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3xFLAG</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-331</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="E352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 gNT</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/8/2026</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="R352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-355</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="E353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 KO rep 3</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p16</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/8/2026</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-356</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="E354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 OX rep 3</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p16</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/8/2026</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OX</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">withdrawn</t>
+        </is>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-357</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="E355" t="inlineStr">
+        <is>
           <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
-      <c r="F351" t="inlineStr">
+      <c r="F355" t="inlineStr">
         <is>
           <t xml:space="preserve">p15</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr">
+      <c r="G355" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H351" t="inlineStr">
+      <c r="H355" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
-      <c r="I351" t="inlineStr">
+      <c r="I355" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr">
+      <c r="K355" t="inlineStr">
         <is>
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="L351" t="inlineStr">
+      <c r="L355" t="inlineStr">
         <is>
           <t xml:space="preserve">3xFLAG</t>
         </is>
       </c>
-      <c r="M351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R351" t="inlineStr">
+      <c r="M355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R355" t="inlineStr">
         <is>
           <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
-      <c r="S351" t="inlineStr">
+      <c r="S355" t="inlineStr">
         <is>
           <t xml:space="preserve">v-358</t>
         </is>
@@ -32724,22 +33052,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP BMK</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">LNCAP</t>
         </is>
       </c>
       <c r="E126">
@@ -32755,7 +33068,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) no sort</t>
+          <t xml:space="preserve">LNCAP BMK</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -32786,7 +33099,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap (m3) no sort</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -32817,7 +33130,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -32848,7 +33161,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -32879,7 +33192,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -32910,7 +33223,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1</t>
+          <t xml:space="preserve">LnCap ER</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -32941,7 +33254,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98%</t>
+          <t xml:space="preserve">LnCap V1G1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -32972,7 +33285,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select</t>
+          <t xml:space="preserve">LnCap478 #2 98%</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -32982,7 +33295,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -33003,7 +33316,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C</t>
+          <t xml:space="preserve">LnCapCASPEX no select</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -33034,17 +33347,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">LnCapCASPEX no select C</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -33065,12 +33378,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB-231</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -33080,7 +33393,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E137">
@@ -33096,7 +33409,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -33111,7 +33424,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="E138">
@@ -33127,124 +33440,203 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">MDA-MB-231</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E139">
+        <v>1</v>
+      </c>
+      <c r="F139">
         <v>0</v>
       </c>
-      <c r="F139">
+      <c r="G139">
         <v>1</v>
-      </c>
-      <c r="G139">
-        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">hek caspex g8</t>
         </is>
       </c>
       <c r="E140">
+        <v>1</v>
+      </c>
+      <c r="F140">
         <v>0</v>
       </c>
-      <c r="F140">
+      <c r="G140">
         <v>1</v>
-      </c>
-      <c r="G140">
-        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 KO rep 3</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KO</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">hek tox4 KO g8</t>
         </is>
       </c>
       <c r="E141">
+        <v>1</v>
+      </c>
+      <c r="F141">
         <v>0</v>
       </c>
-      <c r="F141">
+      <c r="G141">
         <v>1</v>
-      </c>
-      <c r="G141">
-        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t xml:space="preserve">lncap caspex</t>
+        </is>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>1</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OX</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 KO rep 3</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <v>1</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
           <t xml:space="preserve">Huh7 OX rep 3</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t xml:space="preserve">OX</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E142">
+      <c r="D146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="E146">
         <v>0</v>
       </c>
-      <c r="F142">
+      <c r="F146">
         <v>1</v>
       </c>
-      <c r="G142">
+      <c r="G146">
         <v>0</v>
       </c>
     </row>
@@ -34078,6 +34470,90 @@
         <v>81</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freezer</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CLAUDE BOX 1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>81</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="J10">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">freezer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">From CAA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fff</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <v>81</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -11140,7 +11140,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -11304,7 +11304,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -13789,7 +13789,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -13871,7 +13871,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -15715,7 +15715,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -16617,7 +16617,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -16699,7 +16699,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -16781,7 +16781,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">50CR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -28393,34 +28393,14 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLAUDE BOX 1</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A1</t>
-        </is>
-      </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek caspex g8</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">P6</t>
+          <t xml:space="preserve">p23</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -28430,12 +28410,12 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-28</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">28-07-25</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28445,7 +28425,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -28455,54 +28435,34 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">g8</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-emcm6az9</t>
+          <t xml:space="preserve">v-243</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLAUDE BOX 1</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A2</t>
-        </is>
-      </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek tox4 KO g8</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">P5</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -28512,12 +28472,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-28</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">28-07-25</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28527,7 +28487,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -28542,49 +28502,29 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">g8</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-x8hm3iw7</t>
+          <t xml:space="preserve">v-329</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fff</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A1</t>
-        </is>
-      </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP</t>
+          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p26</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -28594,22 +28534,22 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-28</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">28-07-25</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -28629,44 +28569,24 @@
       </c>
       <c r="R346" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-zde7yyzi</t>
+          <t xml:space="preserve">v-330</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fff</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A2</t>
-        </is>
-      </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">lncap caspex</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">P6</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -28676,22 +28596,22 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-28</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">28-07-25</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">3xFLAG</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -28701,7 +28621,7 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
@@ -28711,24 +28631,24 @@
       </c>
       <c r="R347" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-rb9gprqv</t>
+          <t xml:space="preserve">v-331</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p23</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -28738,22 +28658,22 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
@@ -28768,7 +28688,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28778,19 +28698,19 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-243</t>
+          <t xml:space="preserve">v-355</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Huh7 KO rep 3</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -28810,12 +28730,12 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
@@ -28830,7 +28750,7 @@
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28840,19 +28760,19 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-329</t>
+          <t xml:space="preserve">v-356</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
+          <t xml:space="preserve">Huh7 OX rep 3</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p26</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -28872,7 +28792,7 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -28902,19 +28822,19 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-330</t>
+          <t xml:space="preserve">v-357</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -28934,7 +28854,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -28963,254 +28883,6 @@
         </is>
       </c>
       <c r="S351" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-331</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="E352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 gNT</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p15</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
-      <c r="L352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="M352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="R352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-355</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="E353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 KO rep 3</t>
-        </is>
-      </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p16</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
-      <c r="L353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KO</t>
-        </is>
-      </c>
-      <c r="M353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-356</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="E354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 OX rep 3</t>
-        </is>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p16</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
-      <c r="L354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX</t>
-        </is>
-      </c>
-      <c r="M354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-357</t>
-        </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="E355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
-        </is>
-      </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p15</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
-      <c r="L355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3xFLAG</t>
-        </is>
-      </c>
-      <c r="M355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">withdrawn</t>
-        </is>
-      </c>
-      <c r="S355" t="inlineStr">
         <is>
           <t xml:space="preserve">v-358</t>
         </is>
@@ -33052,7 +32724,22 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP</t>
+          <t xml:space="preserve">LNCAP BMK</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E126">
@@ -33068,7 +32755,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCAP BMK</t>
+          <t xml:space="preserve">LnCap (m3) no sort</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -33099,7 +32786,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) no sort</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -33130,7 +32817,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -33161,7 +32848,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -33192,7 +32879,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap ER</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -33223,7 +32910,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap ER</t>
+          <t xml:space="preserve">LnCap V1G1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -33254,7 +32941,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap V1G1</t>
+          <t xml:space="preserve">LnCap478 #2 98%</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -33285,7 +32972,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap478 #2 98%</t>
+          <t xml:space="preserve">LnCapCASPEX no select</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -33295,7 +32982,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -33316,7 +33003,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select</t>
+          <t xml:space="preserve">LnCapCASPEX no select C</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -33347,17 +33034,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select C</t>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -33378,12 +33065,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">MDA-MB-231</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -33393,7 +33080,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="E137">
@@ -33409,7 +33096,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -33424,7 +33111,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E138">
@@ -33440,203 +33127,124 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB-231</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
         <v>1</v>
       </c>
-      <c r="F139">
+      <c r="G139">
         <v>0</v>
-      </c>
-      <c r="G139">
-        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek caspex g8</t>
+          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OX</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
         <v>1</v>
       </c>
-      <c r="F140">
+      <c r="G140">
         <v>0</v>
-      </c>
-      <c r="G140">
-        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek tox4 KO g8</t>
+          <t xml:space="preserve">Huh7 KO rep 3</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KO</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141">
         <v>1</v>
       </c>
-      <c r="F141">
+      <c r="G141">
         <v>0</v>
-      </c>
-      <c r="G141">
-        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">lncap caspex</t>
+          <t xml:space="preserve">Huh7 OX rep 3</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OX</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142">
         <v>1</v>
       </c>
-      <c r="F142">
-        <v>0</v>
-      </c>
       <c r="G142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KO</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E143">
-        <v>0</v>
-      </c>
-      <c r="F143">
-        <v>1</v>
-      </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK ATF3 OX rep 3</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E144">
-        <v>0</v>
-      </c>
-      <c r="F144">
-        <v>1</v>
-      </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 KO rep 3</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">KO</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E145">
-        <v>0</v>
-      </c>
-      <c r="F145">
-        <v>1</v>
-      </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7 OX rep 3</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="E146">
-        <v>0</v>
-      </c>
-      <c r="F146">
-        <v>1</v>
-      </c>
-      <c r="G146">
         <v>0</v>
       </c>
     </row>
@@ -34470,90 +34078,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freezer</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLAUDE BOX 1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grid</t>
-        </is>
-      </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-      <c r="G10">
-        <v>9</v>
-      </c>
-      <c r="H10">
-        <v>81</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-      <c r="J10">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">freezer</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">From CAA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fff</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grid</t>
-        </is>
-      </c>
-      <c r="F11">
-        <v>9</v>
-      </c>
-      <c r="G11">
-        <v>9</v>
-      </c>
-      <c r="H11">
-        <v>81</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <v>79</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -5206,7 +5206,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -16945,7 +16945,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -310,6 +310,43 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BAro box deneme</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>9</v>
+      </c>
+      <c r="H2">
+        <v>81</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -310,43 +310,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BAro box deneme</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grid</t>
-        </is>
-      </c>
-      <c r="F2">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>9</v>
-      </c>
-      <c r="H2">
-        <v>81</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>81</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -184,14 +184,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -266,14 +266,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -348,14 +348,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -430,14 +430,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -512,14 +512,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-09</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">9/4/2026</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -594,14 +594,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-09</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">9/4/2026</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -840,14 +840,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-10</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">10/2/2026</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1578,14 +1578,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-08</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1660,14 +1660,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-08</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1742,14 +1742,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-08</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1824,14 +1824,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-08</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1906,14 +1906,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-07</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">7/5/2025</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1988,14 +1988,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-07</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">7/5/2025</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2070,14 +2070,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-07</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">7/5/2025</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3176,14 +3176,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2023-02-03</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">3/2/2023</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3340,14 +3340,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-02</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">2/5/2025</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3750,14 +3750,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-06</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">6/2/2026</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3914,14 +3914,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-05</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">5/2/2026</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3996,14 +3996,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-02</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4160,14 +4160,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-02</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4324,14 +4324,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-03</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">3/3/2026</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4406,14 +4406,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-03</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">3/3/2026</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5686,14 +5686,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-02</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5850,14 +5850,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-02</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6096,14 +6096,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6178,14 +6178,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6752,14 +6752,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-10</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6834,14 +6834,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-11</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6916,14 +6916,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-11</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">11/3/2026</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6998,14 +6998,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-10</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -7162,14 +7162,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-07</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">7/7/2025</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7254,14 +7254,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-09</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">9/6/2026</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7418,14 +7418,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-09</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">9/6/2026</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7500,14 +7500,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-08</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2026</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8320,14 +8320,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-10</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">10/11/2025</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -8402,14 +8402,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-10</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">10/11/2025</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8484,14 +8484,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-06-02</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">2/6/2025</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -8576,14 +8576,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-08</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2026</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -8740,14 +8740,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-09</t>
+        </is>
+      </c>
       <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">9/10/2025</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -8822,14 +8822,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-09</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">9/10/2025</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -8904,14 +8904,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-09</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">9/10/2025</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -9314,14 +9314,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -9396,14 +9396,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -9642,14 +9642,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-06</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">6/1/2025</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -10216,14 +10216,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
       <c r="I123" t="inlineStr">
         <is>
           <t xml:space="preserve">5/12/2025</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -10298,14 +10298,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr">
         <is>
           <t xml:space="preserve">11/12/2025</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -10380,14 +10380,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-07</t>
+        </is>
+      </c>
       <c r="I125" t="inlineStr">
         <is>
           <t xml:space="preserve">7/10/2025</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -10954,14 +10954,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I132" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -11036,14 +11036,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -11118,14 +11118,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-07</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr">
         <is>
           <t xml:space="preserve">7/10/2025</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11364,14 +11364,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -11446,14 +11446,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I138" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -11528,14 +11528,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -11610,14 +11610,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -11692,14 +11692,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -11774,14 +11774,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-12</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -11856,14 +11856,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-10</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
           <t xml:space="preserve">10/3/2026</t>
-        </is>
-      </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -13265,14 +13265,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -13357,14 +13357,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I161" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -14095,14 +14095,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-08-11</t>
+        </is>
+      </c>
       <c r="I170" t="inlineStr">
         <is>
           <t xml:space="preserve">11/8/2025</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -14259,14 +14259,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I172" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -14341,14 +14341,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I173" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -14423,14 +14423,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I174" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -14505,14 +14505,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I175" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -14587,14 +14587,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-06</t>
+        </is>
+      </c>
       <c r="I176" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -14669,14 +14669,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I177" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -14751,14 +14751,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I178" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -15693,14 +15693,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I189" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -15775,14 +15775,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I190" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -16021,14 +16021,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-06-02</t>
+        </is>
+      </c>
       <c r="I193" t="inlineStr">
         <is>
           <t xml:space="preserve">2/6/2025</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -16103,14 +16103,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-07-03</t>
+        </is>
+      </c>
       <c r="I194" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -16431,14 +16431,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-04</t>
+        </is>
+      </c>
       <c r="I198" t="inlineStr">
         <is>
           <t xml:space="preserve">4/11/2025</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -16595,14 +16595,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-04</t>
+        </is>
+      </c>
       <c r="I200" t="inlineStr">
         <is>
           <t xml:space="preserve">4/11/2025</t>
-        </is>
-      </c>
-      <c r="J200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -17671,14 +17671,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-04</t>
+        </is>
+      </c>
       <c r="I213" t="inlineStr">
         <is>
           <t xml:space="preserve">4/6/2026</t>
-        </is>
-      </c>
-      <c r="J213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -17763,14 +17763,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-04</t>
+        </is>
+      </c>
       <c r="I214" t="inlineStr">
         <is>
           <t xml:space="preserve">4/6/2026</t>
-        </is>
-      </c>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -18511,14 +18511,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-01-05</t>
+        </is>
+      </c>
       <c r="I223" t="inlineStr">
         <is>
           <t xml:space="preserve">5/1/2024</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -18839,14 +18839,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024-04-05</t>
+        </is>
+      </c>
       <c r="I227" t="inlineStr">
         <is>
           <t xml:space="preserve">5/4/2024</t>
-        </is>
-      </c>
-      <c r="J227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -19167,14 +19167,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I231" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -19495,14 +19495,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-05</t>
+        </is>
+      </c>
       <c r="I235" t="inlineStr">
         <is>
           <t xml:space="preserve">5/3/2026</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -19813,14 +19813,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-06</t>
+        </is>
+      </c>
       <c r="I239" t="inlineStr">
         <is>
           <t xml:space="preserve">6/11/2025</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -19977,14 +19977,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-06</t>
+        </is>
+      </c>
       <c r="I241" t="inlineStr">
         <is>
           <t xml:space="preserve">6/11/2025</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -20136,14 +20136,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I243" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -20218,14 +20218,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I244" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -20300,14 +20300,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I245" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -20382,14 +20382,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-12</t>
+        </is>
+      </c>
       <c r="I246" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -20546,14 +20546,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
       <c r="I248" t="inlineStr">
         <is>
           <t xml:space="preserve">11/12/2025</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20792,14 +20792,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
       <c r="I251" t="inlineStr">
         <is>
           <t xml:space="preserve">5/12/2025</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -20874,14 +20874,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-11-10</t>
+        </is>
+      </c>
       <c r="I252" t="inlineStr">
         <is>
           <t xml:space="preserve">10/11/2025</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -20956,14 +20956,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-08-10</t>
+        </is>
+      </c>
       <c r="I253" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -21038,14 +21038,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-02</t>
+        </is>
+      </c>
       <c r="I254" t="inlineStr">
         <is>
           <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -21120,14 +21120,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-04</t>
+        </is>
+      </c>
       <c r="I255" t="inlineStr">
         <is>
           <t xml:space="preserve">4/12/2025</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -21202,14 +21202,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-04</t>
+        </is>
+      </c>
       <c r="I256" t="inlineStr">
         <is>
           <t xml:space="preserve">4/12/2025</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -21284,14 +21284,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
       <c r="I257" t="inlineStr">
         <is>
           <t xml:space="preserve">5/12/2025</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -21366,14 +21366,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-02</t>
+        </is>
+      </c>
       <c r="I258" t="inlineStr">
         <is>
           <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -21448,14 +21448,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-02</t>
+        </is>
+      </c>
       <c r="I259" t="inlineStr">
         <is>
           <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -22176,14 +22176,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-02</t>
+        </is>
+      </c>
       <c r="I268" t="inlineStr">
         <is>
           <t xml:space="preserve">2/1/2026</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -22258,14 +22258,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-02</t>
+        </is>
+      </c>
       <c r="I269" t="inlineStr">
         <is>
           <t xml:space="preserve">2/1/2026</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22340,14 +22340,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-02</t>
+        </is>
+      </c>
       <c r="I270" t="inlineStr">
         <is>
           <t xml:space="preserve">2/1/2026</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -22422,14 +22422,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I271" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -22914,14 +22914,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I277" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -23483,14 +23483,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-05</t>
+        </is>
+      </c>
       <c r="I284" t="inlineStr">
         <is>
           <t xml:space="preserve">5/1/2026</t>
-        </is>
-      </c>
-      <c r="J284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23811,14 +23811,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I288" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23893,14 +23893,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I289" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23975,14 +23975,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I290" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24057,14 +24057,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I291" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -24139,14 +24139,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I292" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24221,14 +24221,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I293" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24303,14 +24303,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
       <c r="I294" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24631,14 +24631,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-05</t>
+        </is>
+      </c>
       <c r="I298" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
-        </is>
-      </c>
-      <c r="J298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24713,14 +24713,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I299" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24795,14 +24795,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I300" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24877,14 +24877,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I301" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -24959,14 +24959,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-01</t>
+        </is>
+      </c>
       <c r="I302" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
-        </is>
-      </c>
-      <c r="J302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -25369,14 +25369,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-02</t>
+        </is>
+      </c>
       <c r="I307" t="inlineStr">
         <is>
           <t xml:space="preserve">2/5/2025</t>
-        </is>
-      </c>
-      <c r="J307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25451,14 +25451,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I308" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25533,14 +25533,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I309" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25615,14 +25615,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I310" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25697,14 +25697,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I311" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25779,14 +25779,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I312" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25861,14 +25861,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
       <c r="I313" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
-        </is>
-      </c>
-      <c r="J313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -26025,14 +26025,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-02</t>
+        </is>
+      </c>
       <c r="I315" t="inlineStr">
         <is>
           <t xml:space="preserve">2/5/2025</t>
-        </is>
-      </c>
-      <c r="J315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26373,14 +26373,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-04</t>
+        </is>
+      </c>
       <c r="I319" t="inlineStr">
         <is>
           <t xml:space="preserve">4/6/2026</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26942,14 +26942,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I326" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -27106,14 +27106,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I328" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27188,14 +27188,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I329" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27270,14 +27270,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
       <c r="I330" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
-        </is>
-      </c>
-      <c r="J330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27352,14 +27352,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-10</t>
+        </is>
+      </c>
       <c r="I331" t="inlineStr">
         <is>
           <t xml:space="preserve">10/2/2026</t>
-        </is>
-      </c>
-      <c r="J331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27516,14 +27516,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-06</t>
+        </is>
+      </c>
       <c r="I333" t="inlineStr">
         <is>
           <t xml:space="preserve">6/2/2026</t>
-        </is>
-      </c>
-      <c r="J333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -184,14 +184,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-05</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -266,14 +266,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-05</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -348,14 +348,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-05</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -430,14 +430,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-05</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -512,14 +512,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-09</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">9/4/2026</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -594,14 +594,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-09</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">9/4/2026</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -840,14 +840,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-10</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t xml:space="preserve">10/2/2026</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1578,14 +1578,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-08</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1660,14 +1660,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-08</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1742,14 +1742,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-08</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1824,14 +1824,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-08</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2025</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1906,14 +1906,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-07</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">7/5/2025</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1988,14 +1988,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-07</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">7/5/2025</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2070,14 +2070,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-07</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">7/5/2025</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3176,14 +3176,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2023-02-03</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">3/2/2023</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3340,14 +3340,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-02</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">2/5/2025</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3750,14 +3750,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-06</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">6/2/2026</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3914,14 +3914,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-05</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">5/2/2026</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -3996,14 +3996,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-02</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4160,14 +4160,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-02</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -4324,14 +4324,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-03</t>
-        </is>
-      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">3/3/2026</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4406,14 +4406,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-03</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">3/3/2026</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -5686,14 +5686,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-02</t>
-        </is>
-      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -5850,14 +5850,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-02</t>
-        </is>
-      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">2/2/2026</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6096,14 +6096,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -6178,14 +6178,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -6752,14 +6752,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-10</t>
-        </is>
-      </c>
       <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">10/3/2026</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6834,14 +6834,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-11</t>
-        </is>
-      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -6916,14 +6916,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-11</t>
-        </is>
-      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">11/3/2026</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -6998,14 +6998,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-10</t>
-        </is>
-      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">10/3/2026</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -7162,14 +7162,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-07-07</t>
-        </is>
-      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">7/7/2025</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -7254,14 +7254,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-09</t>
-        </is>
-      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t xml:space="preserve">9/6/2026</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -7418,14 +7418,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-09</t>
-        </is>
-      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t xml:space="preserve">9/6/2026</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -7500,14 +7500,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-08</t>
-        </is>
-      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2026</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -8320,14 +8320,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-10</t>
-        </is>
-      </c>
       <c r="I100" t="inlineStr">
         <is>
           <t xml:space="preserve">10/11/2025</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -8402,14 +8402,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-10</t>
-        </is>
-      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">10/11/2025</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -8484,14 +8484,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-02</t>
-        </is>
-      </c>
       <c r="I102" t="inlineStr">
         <is>
           <t xml:space="preserve">2/6/2025</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -8576,14 +8576,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-08</t>
-        </is>
-      </c>
       <c r="I103" t="inlineStr">
         <is>
           <t xml:space="preserve">8/5/2026</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -8740,14 +8740,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-10-09</t>
-        </is>
-      </c>
       <c r="I105" t="inlineStr">
         <is>
           <t xml:space="preserve">9/10/2025</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -8822,14 +8822,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-10-09</t>
-        </is>
-      </c>
       <c r="I106" t="inlineStr">
         <is>
           <t xml:space="preserve">9/10/2025</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -8904,14 +8904,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-10-09</t>
-        </is>
-      </c>
       <c r="I107" t="inlineStr">
         <is>
           <t xml:space="preserve">9/10/2025</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -9314,14 +9314,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-06</t>
-        </is>
-      </c>
       <c r="I112" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -9396,14 +9396,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-06</t>
-        </is>
-      </c>
       <c r="I113" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -9642,14 +9642,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-01-06</t>
-        </is>
-      </c>
       <c r="I116" t="inlineStr">
         <is>
           <t xml:space="preserve">6/1/2025</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -10216,14 +10216,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-05</t>
-        </is>
-      </c>
       <c r="I123" t="inlineStr">
         <is>
           <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -10298,14 +10298,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-11</t>
-        </is>
-      </c>
       <c r="I124" t="inlineStr">
         <is>
           <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -10380,14 +10380,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-10-07</t>
-        </is>
-      </c>
       <c r="I125" t="inlineStr">
         <is>
           <t xml:space="preserve">7/10/2025</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -10954,14 +10954,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-12</t>
-        </is>
-      </c>
       <c r="I132" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -11036,14 +11036,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-12</t>
-        </is>
-      </c>
       <c r="I133" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -11118,14 +11118,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-10-07</t>
-        </is>
-      </c>
       <c r="I134" t="inlineStr">
         <is>
           <t xml:space="preserve">7/10/2025</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11364,14 +11364,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-12</t>
-        </is>
-      </c>
       <c r="I137" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -11446,14 +11446,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-12</t>
-        </is>
-      </c>
       <c r="I138" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -11528,14 +11528,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-12</t>
-        </is>
-      </c>
       <c r="I139" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -11610,14 +11610,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-12</t>
-        </is>
-      </c>
       <c r="I140" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -11692,14 +11692,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-12</t>
-        </is>
-      </c>
       <c r="I141" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -11774,14 +11774,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-12</t>
-        </is>
-      </c>
       <c r="I142" t="inlineStr">
         <is>
           <t xml:space="preserve">12/6/2026</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -11856,14 +11856,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-10</t>
-        </is>
-      </c>
       <c r="I143" t="inlineStr">
         <is>
           <t xml:space="preserve">10/3/2026</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -13265,14 +13265,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-07-03</t>
-        </is>
-      </c>
       <c r="I160" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -13357,14 +13357,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-07-03</t>
-        </is>
-      </c>
       <c r="I161" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
@@ -14095,14 +14095,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-08-11</t>
-        </is>
-      </c>
       <c r="I170" t="inlineStr">
         <is>
           <t xml:space="preserve">11/8/2025</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
@@ -14259,14 +14259,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01</t>
-        </is>
-      </c>
       <c r="I172" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -14341,14 +14341,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01</t>
-        </is>
-      </c>
       <c r="I173" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -14423,14 +14423,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-06</t>
-        </is>
-      </c>
       <c r="I174" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -14505,14 +14505,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-06</t>
-        </is>
-      </c>
       <c r="I175" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -14587,14 +14587,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-06</t>
-        </is>
-      </c>
       <c r="I176" t="inlineStr">
         <is>
           <t xml:space="preserve">6/5/2026</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -14669,14 +14669,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01</t>
-        </is>
-      </c>
       <c r="I177" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
@@ -14751,14 +14751,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01</t>
-        </is>
-      </c>
       <c r="I178" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
@@ -15693,14 +15693,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-07-03</t>
-        </is>
-      </c>
       <c r="I189" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -15775,14 +15775,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-07-03</t>
-        </is>
-      </c>
       <c r="I190" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -16021,14 +16021,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-06-02</t>
-        </is>
-      </c>
       <c r="I193" t="inlineStr">
         <is>
           <t xml:space="preserve">2/6/2025</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -16103,14 +16103,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-07-03</t>
-        </is>
-      </c>
       <c r="I194" t="inlineStr">
         <is>
           <t xml:space="preserve">3/7/2025</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
@@ -16431,14 +16431,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-04</t>
-        </is>
-      </c>
       <c r="I198" t="inlineStr">
         <is>
           <t xml:space="preserve">4/11/2025</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -16595,14 +16595,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-04</t>
-        </is>
-      </c>
       <c r="I200" t="inlineStr">
         <is>
           <t xml:space="preserve">4/11/2025</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -17671,14 +17671,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04</t>
-        </is>
-      </c>
       <c r="I213" t="inlineStr">
         <is>
           <t xml:space="preserve">4/6/2026</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -17763,14 +17763,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04</t>
-        </is>
-      </c>
       <c r="I214" t="inlineStr">
         <is>
           <t xml:space="preserve">4/6/2026</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -18511,14 +18511,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2024-01-05</t>
-        </is>
-      </c>
       <c r="I223" t="inlineStr">
         <is>
           <t xml:space="preserve">5/1/2024</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
@@ -18839,14 +18839,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2024-04-05</t>
-        </is>
-      </c>
       <c r="I227" t="inlineStr">
         <is>
           <t xml:space="preserve">5/4/2024</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -19167,14 +19167,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
       <c r="I231" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -19495,14 +19495,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-05</t>
-        </is>
-      </c>
       <c r="I235" t="inlineStr">
         <is>
           <t xml:space="preserve">5/3/2026</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -19813,14 +19813,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-06</t>
-        </is>
-      </c>
       <c r="I239" t="inlineStr">
         <is>
           <t xml:space="preserve">6/11/2025</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -19977,14 +19977,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-06</t>
-        </is>
-      </c>
       <c r="I241" t="inlineStr">
         <is>
           <t xml:space="preserve">6/11/2025</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -20136,14 +20136,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-12</t>
-        </is>
-      </c>
       <c r="I243" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -20218,14 +20218,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-12</t>
-        </is>
-      </c>
       <c r="I244" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -20300,14 +20300,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-12</t>
-        </is>
-      </c>
       <c r="I245" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -20382,14 +20382,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-12</t>
-        </is>
-      </c>
       <c r="I246" t="inlineStr">
         <is>
           <t xml:space="preserve">12/12/2025</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -20546,14 +20546,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-11</t>
-        </is>
-      </c>
       <c r="I248" t="inlineStr">
         <is>
           <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20792,14 +20792,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-05</t>
-        </is>
-      </c>
       <c r="I251" t="inlineStr">
         <is>
           <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -20874,14 +20874,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-10</t>
-        </is>
-      </c>
       <c r="I252" t="inlineStr">
         <is>
           <t xml:space="preserve">10/11/2025</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -20956,14 +20956,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
       <c r="I253" t="inlineStr">
         <is>
           <t xml:space="preserve">10/8/2026</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
@@ -21038,14 +21038,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-02</t>
-        </is>
-      </c>
       <c r="I254" t="inlineStr">
         <is>
           <t xml:space="preserve">2/12/2025</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -21120,14 +21120,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-04</t>
-        </is>
-      </c>
       <c r="I255" t="inlineStr">
         <is>
           <t xml:space="preserve">4/12/2025</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -21202,14 +21202,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-04</t>
-        </is>
-      </c>
       <c r="I256" t="inlineStr">
         <is>
           <t xml:space="preserve">4/12/2025</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -21284,14 +21284,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-05</t>
-        </is>
-      </c>
       <c r="I257" t="inlineStr">
         <is>
           <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -21366,14 +21366,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-02</t>
-        </is>
-      </c>
       <c r="I258" t="inlineStr">
         <is>
           <t xml:space="preserve">2/12/2025</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -21448,14 +21448,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-02</t>
-        </is>
-      </c>
       <c r="I259" t="inlineStr">
         <is>
           <t xml:space="preserve">2/12/2025</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -22176,14 +22176,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-02</t>
-        </is>
-      </c>
       <c r="I268" t="inlineStr">
         <is>
           <t xml:space="preserve">2/1/2026</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -22258,14 +22258,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-02</t>
-        </is>
-      </c>
       <c r="I269" t="inlineStr">
         <is>
           <t xml:space="preserve">2/1/2026</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22340,14 +22340,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-02</t>
-        </is>
-      </c>
       <c r="I270" t="inlineStr">
         <is>
           <t xml:space="preserve">2/1/2026</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -22422,14 +22422,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
       <c r="I271" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -22914,14 +22914,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H277" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
       <c r="I277" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -23483,14 +23483,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-05</t>
-        </is>
-      </c>
       <c r="I284" t="inlineStr">
         <is>
           <t xml:space="preserve">5/1/2026</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23811,14 +23811,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
       <c r="I288" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23893,14 +23893,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
       <c r="I289" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23975,14 +23975,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
       <c r="I290" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24057,14 +24057,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
       <c r="I291" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -24139,14 +24139,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
       <c r="I292" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24221,14 +24221,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
       <c r="I293" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24303,14 +24303,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
       <c r="I294" t="inlineStr">
         <is>
           <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24631,14 +24631,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-05</t>
-        </is>
-      </c>
       <c r="I298" t="inlineStr">
         <is>
           <t xml:space="preserve">5/5/2025</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24713,14 +24713,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01</t>
-        </is>
-      </c>
       <c r="I299" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24795,14 +24795,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01</t>
-        </is>
-      </c>
       <c r="I300" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24877,14 +24877,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01</t>
-        </is>
-      </c>
       <c r="I301" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -24959,14 +24959,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-01</t>
-        </is>
-      </c>
       <c r="I302" t="inlineStr">
         <is>
           <t xml:space="preserve">1/6/2026</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -25369,14 +25369,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-02</t>
-        </is>
-      </c>
       <c r="I307" t="inlineStr">
         <is>
           <t xml:space="preserve">2/5/2025</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25451,14 +25451,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
       <c r="I308" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25533,14 +25533,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
       <c r="I309" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25615,14 +25615,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
       <c r="I310" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25697,14 +25697,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
       <c r="I311" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25779,14 +25779,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
       <c r="I312" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25861,14 +25861,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
       <c r="I313" t="inlineStr">
         <is>
           <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -26025,14 +26025,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H315" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-02</t>
-        </is>
-      </c>
       <c r="I315" t="inlineStr">
         <is>
           <t xml:space="preserve">2/5/2025</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26373,14 +26373,14 @@
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-06-04</t>
-        </is>
-      </c>
       <c r="I319" t="inlineStr">
         <is>
           <t xml:space="preserve">4/6/2026</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26942,14 +26942,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
       <c r="I326" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -27106,14 +27106,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
       <c r="I328" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27188,14 +27188,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
       <c r="I329" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27270,14 +27270,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
       <c r="I330" t="inlineStr">
         <is>
           <t xml:space="preserve">10/4/2026</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27352,14 +27352,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
-      <c r="H331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-10</t>
-        </is>
-      </c>
       <c r="I331" t="inlineStr">
         <is>
           <t xml:space="preserve">10/2/2026</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27516,14 +27516,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-06</t>
-        </is>
-      </c>
       <c r="I333" t="inlineStr">
         <is>
           <t xml:space="preserve">6/2/2026</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -19308,7 +19308,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -19318,12 +19318,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -19333,37 +19333,37 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-06-26</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R233" t="inlineStr">
@@ -19373,7 +19373,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-326</t>
         </is>
       </c>
     </row>
@@ -19390,7 +19390,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -19400,12 +19400,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -19415,37 +19415,37 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-06-23</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-06-26</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R234" t="inlineStr">
@@ -19455,7 +19455,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-327</t>
         </is>
       </c>
     </row>
@@ -19472,7 +19472,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -19482,52 +19482,52 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p27</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-03-05</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">5/3/2026</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R235" t="inlineStr">
@@ -19537,7 +19537,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-328</t>
         </is>
       </c>
     </row>
@@ -19554,62 +19554,57 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
-        </is>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-23</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R236" t="inlineStr">
@@ -19619,7 +19614,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-335</t>
         </is>
       </c>
     </row>
@@ -19636,62 +19631,57 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-23</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R237" t="inlineStr">
@@ -19701,7 +19691,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-336</t>
         </is>
       </c>
     </row>
@@ -19718,62 +19708,62 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-11-27</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">27-11-25</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R238" t="inlineStr">
@@ -19783,7 +19773,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-337</t>
         </is>
       </c>
     </row>
@@ -19800,62 +19790,62 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R239" t="inlineStr">
@@ -19865,7 +19855,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-338</t>
         </is>
       </c>
     </row>
@@ -19882,22 +19872,22 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -19907,37 +19897,37 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R240" t="inlineStr">
@@ -19947,7 +19937,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-339</t>
         </is>
       </c>
     </row>
@@ -19964,62 +19954,62 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R241" t="inlineStr">
@@ -20029,7 +20019,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-340</t>
         </is>
       </c>
     </row>
@@ -20046,22 +20036,22 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -20069,14 +20059,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-29</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29-12-25</t>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -20086,7 +20071,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -20101,7 +20086,7 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R242" t="inlineStr">
@@ -20111,7 +20096,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-341</t>
         </is>
       </c>
     </row>
@@ -20128,22 +20113,22 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -20153,22 +20138,22 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -20183,7 +20168,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
@@ -20193,7 +20178,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20210,22 +20195,22 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -20235,22 +20220,22 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -20265,7 +20250,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -20275,7 +20260,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -20292,22 +20277,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -20317,22 +20302,22 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -20347,7 +20332,7 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R245" t="inlineStr">
@@ -20357,7 +20342,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -20374,22 +20359,22 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -20399,22 +20384,22 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -20429,7 +20414,7 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R246" t="inlineStr">
@@ -20439,7 +20424,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -20456,22 +20441,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -20481,22 +20466,22 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -20511,7 +20496,7 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R247" t="inlineStr">
@@ -20521,7 +20506,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -20538,62 +20523,62 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-11</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">11/12/2025</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -20603,7 +20588,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -20620,22 +20605,22 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -20645,22 +20630,22 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -20675,7 +20660,7 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R249" t="inlineStr">
@@ -20685,7 +20670,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -20702,22 +20687,22 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -20727,22 +20712,22 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -20757,7 +20742,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -20767,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -20784,22 +20769,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -20807,34 +20792,39 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -20844,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -20861,22 +20851,22 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -20886,17 +20876,17 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -20926,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -20943,22 +20933,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -20968,17 +20958,17 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -20998,7 +20988,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
@@ -21008,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21025,62 +21015,62 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -21090,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -21107,22 +21097,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -21132,37 +21122,37 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -21172,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -21189,22 +21179,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -21214,37 +21204,37 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -21254,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -21271,62 +21261,62 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -21336,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -21353,62 +21343,62 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -21418,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -21435,62 +21425,62 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -21500,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -21517,62 +21507,57 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -21582,7 +21567,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -21599,22 +21584,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -21624,37 +21609,32 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -21664,7 +21644,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -21681,62 +21661,62 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21746,7 +21726,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -21768,57 +21748,57 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p4</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-31</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31-12-25</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -21828,7 +21808,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -21850,57 +21830,57 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p4</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-31</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31-12-25</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -21910,7 +21890,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -21932,7 +21912,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -21942,22 +21922,22 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -21992,7 +21972,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22014,7 +21994,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -22024,22 +22004,22 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -22074,7 +22054,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -22096,17 +22076,17 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -22116,12 +22096,12 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -22146,7 +22126,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -22156,7 +22136,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -22178,32 +22158,32 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -22228,7 +22208,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22238,7 +22218,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -22260,57 +22240,57 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22320,7 +22300,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -22342,17 +22322,17 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -22362,37 +22342,37 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22402,7 +22382,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -22424,57 +22404,57 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22484,7 +22464,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -22506,17 +22486,17 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -22526,22 +22506,22 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -22556,7 +22536,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -22566,7 +22546,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -22588,37 +22568,37 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -22638,7 +22618,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22648,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -22670,17 +22650,17 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -22690,17 +22670,17 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -22720,7 +22700,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22730,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -22752,42 +22732,42 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
-        </is>
-      </c>
-      <c r="J275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -22812,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -22834,17 +22814,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -22854,17 +22834,17 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -22884,7 +22864,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22894,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -22916,17 +22896,17 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -22936,17 +22916,17 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -22966,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22976,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -22998,17 +22978,17 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -23018,12 +22998,12 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23033,7 +23013,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -23058,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -23080,17 +23060,17 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -23100,12 +23080,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23115,7 +23095,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -23130,7 +23110,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23140,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -23162,17 +23142,17 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -23182,12 +23162,12 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -23197,7 +23177,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -23212,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23222,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -23244,17 +23224,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -23262,14 +23242,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-05-04</t>
-        </is>
-      </c>
-      <c r="I281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4/5/2026</t>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23294,7 +23269,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23304,7 +23279,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -23326,17 +23301,17 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -23346,12 +23321,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23361,7 +23336,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -23376,7 +23351,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23386,7 +23361,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -23408,32 +23383,32 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23443,7 +23418,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -23458,7 +23433,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23468,7 +23443,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -23490,32 +23465,32 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23525,7 +23500,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -23550,7 +23525,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -23572,32 +23547,32 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -23607,7 +23582,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -23622,7 +23597,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23632,7 +23607,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -23654,42 +23629,42 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p13</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-14</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-01-26</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -23704,7 +23679,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23714,7 +23689,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -23736,42 +23711,42 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -23786,17 +23761,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23806,7 +23771,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -23828,17 +23793,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -23848,22 +23813,22 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -23878,17 +23843,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q288" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23898,7 +23853,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -23920,42 +23875,42 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -23970,7 +23925,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23980,7 +23935,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -24002,17 +23957,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -24022,37 +23977,37 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24062,7 +24017,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -24084,17 +24039,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -24104,37 +24059,37 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24144,7 +24099,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -24166,57 +24121,57 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24226,7 +24181,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -24248,17 +24203,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24268,17 +24223,17 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -24308,7 +24263,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -24330,17 +24285,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p45769</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24348,19 +24303,24 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -24370,7 +24330,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
@@ -24385,7 +24345,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -24407,37 +24367,37 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -24447,7 +24407,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -24457,7 +24417,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24467,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -24489,17 +24449,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24509,37 +24469,37 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24549,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -24571,57 +24531,57 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24631,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -24653,17 +24613,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -24673,37 +24633,37 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24713,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -24735,17 +24695,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24755,22 +24715,22 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -24795,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -24817,17 +24777,17 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24837,22 +24797,22 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24867,7 +24827,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24877,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -24899,42 +24859,42 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -24944,12 +24904,12 @@
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24959,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -24981,17 +24941,17 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -25001,22 +24961,22 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -25031,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25041,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -25063,37 +25023,37 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -25123,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -25145,17 +25105,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25165,22 +25125,22 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -25205,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -25227,57 +25187,57 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">caNT read</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25287,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -25309,57 +25269,57 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25369,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -25391,57 +25351,57 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25451,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -25473,57 +25433,57 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25533,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -25555,57 +25515,57 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25615,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -25637,57 +25597,57 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25697,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -25719,37 +25679,37 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -25769,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25779,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -25801,17 +25761,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p218</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25821,27 +25781,27 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -25851,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25861,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -25883,52 +25843,52 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">I9</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
@@ -25943,54 +25903,54 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-06-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -26015,7 +25975,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -26025,54 +25985,54 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-326</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-23</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-06-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26097,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26107,39 +26067,39 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-327</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p27</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -26149,12 +26109,12 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-05</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/3/2026</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26179,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26189,54 +26149,59 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-328</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-26</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -26256,7 +26221,17 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26266,54 +26241,59 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-335</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-26</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -26333,7 +26313,17 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26343,59 +26333,59 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-336</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-27</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-11-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -26415,7 +26405,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26425,59 +26415,59 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-337</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -26497,7 +26487,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26507,39 +26497,39 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-338</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26549,17 +26539,17 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -26589,39 +26579,39 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-339</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -26631,17 +26621,17 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -26671,39 +26661,39 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-340</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26711,14 +26701,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J323" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -26748,39 +26743,39 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-341</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p45769</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26788,24 +26783,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-12</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12/12/2025</t>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26815,7 +26805,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -26830,64 +26820,64 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26897,7 +26887,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -26912,39 +26902,39 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -26954,22 +26944,22 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26984,7 +26974,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26994,39 +26984,39 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27036,22 +27026,22 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27066,7 +27056,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27076,39 +27066,39 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -27118,22 +27108,22 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-17</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-12-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27148,7 +27138,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27158,79 +27148,79 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27240,39 +27230,39 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27282,17 +27272,17 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-17</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-12-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -27322,64 +27312,64 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-17</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-12-25</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27389,12 +27379,12 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27404,39 +27394,39 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27446,37 +27436,37 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27486,39 +27476,39 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27528,22 +27518,22 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27568,39 +27558,39 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27610,22 +27600,22 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27650,29 +27640,29 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -27682,22 +27672,22 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27732,54 +27722,54 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27804,7 +27794,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27814,54 +27804,54 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27886,7 +27876,7 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27896,54 +27886,54 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27978,54 +27968,54 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28060,54 +28050,54 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28142,54 +28132,59 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -28209,7 +28204,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28219,39 +28214,39 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">DuPar50CR+1</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p218</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -28261,12 +28256,17 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -28276,7 +28276,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CisR</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28296,39 +28296,39 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p8</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -28338,37 +28338,37 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
@@ -40276,17 +40276,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -40304,10 +40304,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J6">
-        <v>81</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7">
@@ -40323,7 +40323,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -40341,10 +40341,10 @@
         <v>81</v>
       </c>
       <c r="I7">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>51</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -40313,17 +40313,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Freezer 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Not placed yet</t>
+          <t xml:space="preserve">Rack 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
+          <t xml:space="preserve">Unnamed box</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -40360,7 +40360,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unnamed box</t>
+          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -40347,43 +40347,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not placed yet</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not placed yet</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Baro CELLS #1 (-80)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grid</t>
-        </is>
-      </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
-      <c r="G8">
-        <v>9</v>
-      </c>
-      <c r="H8">
-        <v>81</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>81</v>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20118,17 +20118,17 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -20138,17 +20138,17 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-mtrdw768-0</t>
         </is>
       </c>
     </row>
@@ -20200,17 +20200,17 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -20220,17 +20220,17 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-mtrdw768-1</t>
         </is>
       </c>
     </row>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20364,7 +20364,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -20446,7 +20446,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -20466,12 +20466,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-17</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-12-25</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -20528,32 +20528,32 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20563,22 +20563,22 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R248" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -20692,57 +20692,57 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -20774,17 +20774,17 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -20794,12 +20794,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -20809,22 +20809,22 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -20856,17 +20856,17 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -20876,17 +20876,17 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -20938,12 +20938,12 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -20958,37 +20958,37 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -21020,57 +21020,57 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21102,12 +21102,12 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -21122,37 +21122,37 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21184,32 +21184,32 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -21234,7 +21234,7 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -21266,32 +21266,32 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -21316,7 +21316,7 @@
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -21348,32 +21348,32 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -21398,7 +21398,7 @@
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -21430,7 +21430,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -21450,12 +21450,12 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -21512,47 +21512,52 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">2/12/2025</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
@@ -21567,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -21589,52 +21594,57 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">2/12/2025</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -21644,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -21666,17 +21676,17 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -21686,17 +21696,12 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -21716,7 +21721,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21726,7 +21731,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -21743,22 +21748,22 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -21768,37 +21773,32 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -21808,7 +21808,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -21825,22 +21825,22 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -21850,37 +21850,37 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -21890,7 +21890,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -21912,32 +21912,32 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -21962,7 +21962,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -21994,32 +21994,32 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -22076,22 +22076,22 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -22126,7 +22126,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22158,17 +22158,17 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -22178,12 +22178,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -22240,17 +22240,17 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -22260,12 +22260,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -22322,22 +22322,22 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -22404,12 +22404,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -22424,12 +22424,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -22486,17 +22486,17 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -22506,37 +22506,37 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -22568,57 +22568,57 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -22650,12 +22650,12 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -22685,7 +22685,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -22732,12 +22732,12 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -22767,7 +22767,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -22814,17 +22814,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -22834,12 +22834,12 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -22896,17 +22896,17 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -22916,12 +22916,12 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -22978,12 +22978,12 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -23060,17 +23060,17 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -23080,12 +23080,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -23142,12 +23142,12 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -23224,37 +23224,42 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -23269,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23279,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -23301,42 +23306,42 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -23351,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23361,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -23383,17 +23388,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -23401,14 +23406,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23433,7 +23433,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23443,7 +23443,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -23465,17 +23465,17 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -23485,12 +23485,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -23515,7 +23515,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23525,7 +23525,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -23547,17 +23547,17 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -23567,12 +23567,12 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -23597,7 +23597,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23607,7 +23607,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -23629,17 +23629,17 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -23649,12 +23649,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23689,7 +23689,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23711,12 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -23793,32 +23793,32 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -23843,7 +23843,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -23875,17 +23875,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -23895,12 +23895,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23925,7 +23925,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -23957,17 +23957,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23977,37 +23977,37 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -24039,17 +24039,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -24059,37 +24059,37 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -24121,17 +24121,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -24203,57 +24203,57 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -24285,57 +24285,57 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -24367,32 +24367,32 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24402,22 +24402,22 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -24449,17 +24449,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24469,12 +24469,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24484,22 +24484,22 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -24531,17 +24531,17 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -24551,12 +24551,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -24613,17 +24613,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -24695,57 +24695,57 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -24777,17 +24777,17 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24797,37 +24797,37 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -24859,12 +24859,12 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -25023,32 +25023,32 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -25105,17 +25105,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25125,12 +25125,12 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -25187,32 +25187,32 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
-        </is>
-      </c>
-      <c r="J305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -25269,17 +25269,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -25289,12 +25289,12 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -25351,32 +25351,32 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">caNT read</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -25433,17 +25433,17 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -25453,22 +25453,22 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -25515,17 +25515,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -25535,22 +25535,22 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -25597,17 +25597,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -25761,17 +25761,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -25843,22 +25843,22 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -25925,32 +25925,32 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26007,12 +26007,12 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -26027,12 +26027,12 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26089,42 +26089,42 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+6</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -26171,17 +26171,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26191,22 +26191,22 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26221,17 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q317" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26241,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -26263,37 +26253,37 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -26313,17 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26333,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -26355,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26375,12 +26355,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26405,7 +26385,17 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26415,7 +26405,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -26437,12 +26427,12 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -26487,7 +26477,17 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26497,7 +26497,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -26519,32 +26519,32 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26569,7 +26569,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26579,7 +26579,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -26601,32 +26601,32 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -26651,7 +26651,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26661,7 +26661,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -26683,12 +26683,12 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -26743,7 +26743,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -26765,17 +26765,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p45769</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26783,9 +26783,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J324" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26795,7 +26800,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26805,7 +26810,7 @@
       </c>
       <c r="N324" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O324" t="inlineStr">
@@ -26820,7 +26825,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -26842,32 +26847,32 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26877,7 +26882,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26887,7 +26892,7 @@
       </c>
       <c r="N325" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O325" t="inlineStr">
@@ -26902,7 +26907,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -26924,17 +26929,17 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p45769</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -26942,24 +26947,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
-      <c r="I326" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/4/2026</t>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26969,12 +26969,12 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26984,7 +26984,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27006,42 +27006,42 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27051,12 +27051,12 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27066,7 +27066,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27088,7 +27088,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -27148,7 +27148,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -27170,12 +27170,12 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -27190,12 +27190,12 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27220,7 +27220,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27230,7 +27230,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -27252,17 +27252,17 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27312,7 +27312,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -27334,32 +27334,32 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27379,12 +27379,12 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -27416,12 +27416,12 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -27436,12 +27436,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27451,7 +27451,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -27466,7 +27466,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27476,7 +27476,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -27498,32 +27498,32 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27543,12 +27543,12 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -27580,17 +27580,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -27662,57 +27662,57 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27722,7 +27722,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -27744,57 +27744,57 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -27826,7 +27826,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -27836,7 +27836,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -27846,12 +27846,12 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -27908,7 +27908,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -27990,7 +27990,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28072,7 +28072,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -28154,57 +28154,57 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K341" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -28236,32 +28236,32 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28271,22 +28271,22 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -28318,158 +28318,238 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="M343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p218</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="M344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E343" t="inlineStr">
+      <c r="E345" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F343" t="inlineStr">
+      <c r="F345" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr">
+      <c r="G345" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H343" t="inlineStr">
+      <c r="H345" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I343" t="inlineStr">
+      <c r="I345" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr">
+      <c r="K345" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L343" t="inlineStr">
+      <c r="L345" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="M343" t="inlineStr">
+      <c r="M345" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N343" t="inlineStr">
+      <c r="N345" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O343" t="inlineStr">
+      <c r="O345" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R343" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S343" t="inlineStr">
+      <c r="R345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S345" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="E344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unreadable row (E 6)</t>
-        </is>
-      </c>
-      <c r="J344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="L344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S344" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-205</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="E345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
-        </is>
-      </c>
-      <c r="J345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="L345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="M345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-206</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (E 6)</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
@@ -28504,14 +28584,14 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-207</t>
+          <t xml:space="preserve">v-205</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
@@ -28546,14 +28626,14 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-208</t>
+          <t xml:space="preserve">v-206</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 8)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
@@ -28588,14 +28668,14 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-234</t>
+          <t xml:space="preserve">v-207</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 9)</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
@@ -28630,14 +28710,14 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-235</t>
+          <t xml:space="preserve">v-208</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 8)</t>
+          <t xml:space="preserve">Unreadable row (H 8)</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -28672,14 +28752,14 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-243</t>
+          <t xml:space="preserve">v-234</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 5)</t>
+          <t xml:space="preserve">Unreadable row (H 9)</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
@@ -28714,14 +28794,14 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-285</t>
+          <t xml:space="preserve">v-235</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 6)</t>
+          <t xml:space="preserve">Unreadable row (I 8)</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -28756,14 +28836,14 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-286</t>
+          <t xml:space="preserve">v-243</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
+          <t xml:space="preserve">Unreadable row (E 5)</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
@@ -28798,14 +28878,14 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-287</t>
+          <t xml:space="preserve">v-285</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (E 6)</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -28840,14 +28920,14 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-288</t>
+          <t xml:space="preserve">v-286</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
@@ -28882,14 +28962,14 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-289</t>
+          <t xml:space="preserve">v-287</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 4)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
@@ -28924,14 +29004,14 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-329</t>
+          <t xml:space="preserve">v-288</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 5)</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -28966,14 +29046,14 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-330</t>
+          <t xml:space="preserve">v-289</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 6)</t>
+          <t xml:space="preserve">Unreadable row (A 4)</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
@@ -29008,14 +29088,14 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-331</t>
+          <t xml:space="preserve">v-329</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 7)</t>
+          <t xml:space="preserve">Unreadable row (A 5)</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -29050,14 +29130,14 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-332</t>
+          <t xml:space="preserve">v-330</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 8)</t>
+          <t xml:space="preserve">Unreadable row (A 6)</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
@@ -29092,14 +29172,14 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-333</t>
+          <t xml:space="preserve">v-331</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 9)</t>
+          <t xml:space="preserve">Unreadable row (A 7)</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
@@ -29134,14 +29214,14 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-334</t>
+          <t xml:space="preserve">v-332</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 8)</t>
+          <t xml:space="preserve">Unreadable row (A 8)</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -29176,14 +29256,14 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-342</t>
+          <t xml:space="preserve">v-333</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 9)</t>
+          <t xml:space="preserve">Unreadable row (A 9)</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -29218,14 +29298,14 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-343</t>
+          <t xml:space="preserve">v-334</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 3)</t>
+          <t xml:space="preserve">Unreadable row (B 8)</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
@@ -29260,14 +29340,14 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-355</t>
+          <t xml:space="preserve">v-342</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 4)</t>
+          <t xml:space="preserve">Unreadable row (B 9)</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -29302,14 +29382,14 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-356</t>
+          <t xml:space="preserve">v-343</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 5)</t>
+          <t xml:space="preserve">Unreadable row (D 3)</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -29344,14 +29424,14 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-357</t>
+          <t xml:space="preserve">v-355</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 6)</t>
+          <t xml:space="preserve">Unreadable row (D 4)</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -29386,14 +29466,14 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-358</t>
+          <t xml:space="preserve">v-356</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 7)</t>
+          <t xml:space="preserve">Unreadable row (D 5)</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
@@ -29428,14 +29508,14 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-359</t>
+          <t xml:space="preserve">v-357</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 8)</t>
+          <t xml:space="preserve">Unreadable row (D 6)</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -29470,14 +29550,14 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-360</t>
+          <t xml:space="preserve">v-358</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 9)</t>
+          <t xml:space="preserve">Unreadable row (D 7)</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
@@ -29512,14 +29592,14 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-361</t>
+          <t xml:space="preserve">v-359</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
+          <t xml:space="preserve">Unreadable row (D 8)</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
@@ -29554,14 +29634,14 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-368</t>
+          <t xml:space="preserve">v-360</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (D 9)</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
@@ -29596,14 +29676,14 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-369</t>
+          <t xml:space="preserve">v-361</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
@@ -29638,14 +29718,14 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-370</t>
+          <t xml:space="preserve">v-368</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 3)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -29680,14 +29760,14 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-373</t>
+          <t xml:space="preserve">v-369</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 4)</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
@@ -29722,14 +29802,14 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-374</t>
+          <t xml:space="preserve">v-370</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="E376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 5)</t>
+          <t xml:space="preserve">Unreadable row (F 3)</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -29764,14 +29844,14 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-375</t>
+          <t xml:space="preserve">v-373</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 6)</t>
+          <t xml:space="preserve">Unreadable row (F 4)</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
@@ -29806,14 +29886,14 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-376</t>
+          <t xml:space="preserve">v-374</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="E378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 7)</t>
+          <t xml:space="preserve">Unreadable row (F 5)</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
@@ -29848,14 +29928,14 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-377</t>
+          <t xml:space="preserve">v-375</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 8)</t>
+          <t xml:space="preserve">Unreadable row (F 6)</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -29890,14 +29970,14 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-378</t>
+          <t xml:space="preserve">v-376</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="E380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 9)</t>
+          <t xml:space="preserve">Unreadable row (F 7)</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -29932,14 +30012,14 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-379</t>
+          <t xml:space="preserve">v-377</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="E381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 2)</t>
+          <t xml:space="preserve">Unreadable row (F 8)</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
@@ -29974,14 +30054,14 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-381</t>
+          <t xml:space="preserve">v-378</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="E382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 3)</t>
+          <t xml:space="preserve">Unreadable row (F 9)</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
@@ -30016,14 +30096,14 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-382</t>
+          <t xml:space="preserve">v-379</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="E383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 4)</t>
+          <t xml:space="preserve">Unreadable row (G 2)</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
@@ -30058,14 +30138,14 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-383</t>
+          <t xml:space="preserve">v-381</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="E384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 5)</t>
+          <t xml:space="preserve">Unreadable row (G 3)</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -30100,14 +30180,14 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-384</t>
+          <t xml:space="preserve">v-382</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="E385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 6)</t>
+          <t xml:space="preserve">Unreadable row (G 4)</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
@@ -30142,14 +30222,14 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-385</t>
+          <t xml:space="preserve">v-383</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="E386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 7)</t>
+          <t xml:space="preserve">Unreadable row (G 5)</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -30184,14 +30264,14 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-386</t>
+          <t xml:space="preserve">v-384</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="E387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 8)</t>
+          <t xml:space="preserve">Unreadable row (G 6)</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
@@ -30226,14 +30306,14 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-387</t>
+          <t xml:space="preserve">v-385</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="E388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 9)</t>
+          <t xml:space="preserve">Unreadable row (G 7)</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
@@ -30268,14 +30348,14 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-388</t>
+          <t xml:space="preserve">v-386</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="E389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 1)</t>
+          <t xml:space="preserve">Unreadable row (G 8)</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
@@ -30310,14 +30390,14 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-389</t>
+          <t xml:space="preserve">v-387</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="E390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 2)</t>
+          <t xml:space="preserve">Unreadable row (G 9)</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
@@ -30352,14 +30432,14 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-390</t>
+          <t xml:space="preserve">v-388</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="E391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 3)</t>
+          <t xml:space="preserve">Unreadable row (H 1)</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
@@ -30394,14 +30474,14 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-391</t>
+          <t xml:space="preserve">v-389</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="E392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 4)</t>
+          <t xml:space="preserve">Unreadable row (H 2)</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
@@ -30436,14 +30516,14 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-392</t>
+          <t xml:space="preserve">v-390</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="E393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 5)</t>
+          <t xml:space="preserve">Unreadable row (H 3)</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -30478,14 +30558,14 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-393</t>
+          <t xml:space="preserve">v-391</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="E394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 6)</t>
+          <t xml:space="preserve">Unreadable row (H 4)</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
@@ -30520,14 +30600,14 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-394</t>
+          <t xml:space="preserve">v-392</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="E395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 7)</t>
+          <t xml:space="preserve">Unreadable row (H 5)</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
@@ -30562,14 +30642,14 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-395</t>
+          <t xml:space="preserve">v-393</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="E396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 8)</t>
+          <t xml:space="preserve">Unreadable row (H 6)</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
@@ -30604,14 +30684,14 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-396</t>
+          <t xml:space="preserve">v-394</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="E397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 9)</t>
+          <t xml:space="preserve">Unreadable row (H 7)</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -30646,14 +30726,14 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-397</t>
+          <t xml:space="preserve">v-395</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="E398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 1)</t>
+          <t xml:space="preserve">Unreadable row (H 8)</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
@@ -30688,14 +30768,14 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-398</t>
+          <t xml:space="preserve">v-396</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="E399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 2)</t>
+          <t xml:space="preserve">Unreadable row (H 9)</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -30730,14 +30810,14 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-399</t>
+          <t xml:space="preserve">v-397</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="E400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 3)</t>
+          <t xml:space="preserve">Unreadable row (I 1)</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
@@ -30772,14 +30852,14 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-400</t>
+          <t xml:space="preserve">v-398</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="E401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 4)</t>
+          <t xml:space="preserve">Unreadable row (I 2)</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
@@ -30814,14 +30894,14 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-401</t>
+          <t xml:space="preserve">v-399</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="E402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 5)</t>
+          <t xml:space="preserve">Unreadable row (I 3)</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -30856,14 +30936,14 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-402</t>
+          <t xml:space="preserve">v-400</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="E403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 6)</t>
+          <t xml:space="preserve">Unreadable row (I 4)</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -30898,14 +30978,14 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-403</t>
+          <t xml:space="preserve">v-401</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="E404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 7)</t>
+          <t xml:space="preserve">Unreadable row (I 5)</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -30940,14 +31020,14 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-404</t>
+          <t xml:space="preserve">v-402</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="E405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 8)</t>
+          <t xml:space="preserve">Unreadable row (I 6)</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -30982,14 +31062,14 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-405</t>
+          <t xml:space="preserve">v-403</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="E406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 9)</t>
+          <t xml:space="preserve">Unreadable row (I 7)</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -31024,14 +31104,14 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-406</t>
+          <t xml:space="preserve">v-404</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="E407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 1)</t>
+          <t xml:space="preserve">Unreadable row (I 8)</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -31066,14 +31146,14 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-407</t>
+          <t xml:space="preserve">v-405</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="E408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 2)</t>
+          <t xml:space="preserve">Unreadable row (I 9)</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -31108,14 +31188,14 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-408</t>
+          <t xml:space="preserve">v-406</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="E409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 3)</t>
+          <t xml:space="preserve">Unreadable row (A 1)</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -31150,14 +31230,14 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-409</t>
+          <t xml:space="preserve">v-407</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="E410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 4)</t>
+          <t xml:space="preserve">Unreadable row (A 2)</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -31192,14 +31272,14 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-410</t>
+          <t xml:space="preserve">v-408</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="E411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 5)</t>
+          <t xml:space="preserve">Unreadable row (A 3)</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
@@ -31234,14 +31314,14 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-411</t>
+          <t xml:space="preserve">v-409</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="E412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 6)</t>
+          <t xml:space="preserve">Unreadable row (A 4)</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -31276,14 +31356,14 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-412</t>
+          <t xml:space="preserve">v-410</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="E413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 7)</t>
+          <t xml:space="preserve">Unreadable row (A 5)</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -31318,14 +31398,14 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-413</t>
+          <t xml:space="preserve">v-411</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="E414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 8)</t>
+          <t xml:space="preserve">Unreadable row (A 6)</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -31360,14 +31440,14 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-414</t>
+          <t xml:space="preserve">v-412</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="E415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 9)</t>
+          <t xml:space="preserve">Unreadable row (A 7)</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -31402,14 +31482,14 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-415</t>
+          <t xml:space="preserve">v-413</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="E416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 1)</t>
+          <t xml:space="preserve">Unreadable row (A 8)</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -31444,14 +31524,14 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-416</t>
+          <t xml:space="preserve">v-414</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="E417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 2)</t>
+          <t xml:space="preserve">Unreadable row (A 9)</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -31486,14 +31566,14 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-417</t>
+          <t xml:space="preserve">v-415</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="E418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 3)</t>
+          <t xml:space="preserve">Unreadable row (B 1)</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -31528,14 +31608,14 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-418</t>
+          <t xml:space="preserve">v-416</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="E419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 4)</t>
+          <t xml:space="preserve">Unreadable row (B 2)</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
@@ -31570,14 +31650,14 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-419</t>
+          <t xml:space="preserve">v-417</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="E420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 5)</t>
+          <t xml:space="preserve">Unreadable row (B 3)</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
@@ -31612,14 +31692,14 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-420</t>
+          <t xml:space="preserve">v-418</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="E421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 6)</t>
+          <t xml:space="preserve">Unreadable row (B 4)</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
@@ -31654,14 +31734,14 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-421</t>
+          <t xml:space="preserve">v-419</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="E422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 7)</t>
+          <t xml:space="preserve">Unreadable row (B 5)</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
@@ -31696,14 +31776,14 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-422</t>
+          <t xml:space="preserve">v-420</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="E423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 8)</t>
+          <t xml:space="preserve">Unreadable row (B 6)</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -31738,14 +31818,14 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-423</t>
+          <t xml:space="preserve">v-421</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="E424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 9)</t>
+          <t xml:space="preserve">Unreadable row (B 7)</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -31780,14 +31860,14 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-424</t>
+          <t xml:space="preserve">v-422</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="E425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 1)</t>
+          <t xml:space="preserve">Unreadable row (B 8)</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -31822,14 +31902,14 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-425</t>
+          <t xml:space="preserve">v-423</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="E426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 2)</t>
+          <t xml:space="preserve">Unreadable row (B 9)</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
@@ -31864,14 +31944,14 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-426</t>
+          <t xml:space="preserve">v-424</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="E427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 3)</t>
+          <t xml:space="preserve">Unreadable row (C 1)</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -31906,14 +31986,14 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-427</t>
+          <t xml:space="preserve">v-425</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="E428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 4)</t>
+          <t xml:space="preserve">Unreadable row (C 2)</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -31948,14 +32028,14 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-428</t>
+          <t xml:space="preserve">v-426</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="E429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 5)</t>
+          <t xml:space="preserve">Unreadable row (C 3)</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -31990,14 +32070,14 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-429</t>
+          <t xml:space="preserve">v-427</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="E430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 6)</t>
+          <t xml:space="preserve">Unreadable row (C 4)</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
@@ -32032,14 +32112,14 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-430</t>
+          <t xml:space="preserve">v-428</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="E431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 7)</t>
+          <t xml:space="preserve">Unreadable row (C 5)</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
@@ -32074,14 +32154,14 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-431</t>
+          <t xml:space="preserve">v-429</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="E432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 8)</t>
+          <t xml:space="preserve">Unreadable row (C 6)</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -32116,14 +32196,14 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-432</t>
+          <t xml:space="preserve">v-430</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="E433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 9)</t>
+          <t xml:space="preserve">Unreadable row (C 7)</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
@@ -32158,14 +32238,14 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-433</t>
+          <t xml:space="preserve">v-431</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="E434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 1)</t>
+          <t xml:space="preserve">Unreadable row (C 8)</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -32200,14 +32280,14 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-434</t>
+          <t xml:space="preserve">v-432</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="E435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 2)</t>
+          <t xml:space="preserve">Unreadable row (C 9)</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -32242,14 +32322,14 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-435</t>
+          <t xml:space="preserve">v-433</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="E436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 3)</t>
+          <t xml:space="preserve">Unreadable row (D 1)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -32284,14 +32364,14 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-436</t>
+          <t xml:space="preserve">v-434</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="E437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 4)</t>
+          <t xml:space="preserve">Unreadable row (D 2)</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -32326,14 +32406,14 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-437</t>
+          <t xml:space="preserve">v-435</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="E438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 5)</t>
+          <t xml:space="preserve">Unreadable row (D 3)</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -32368,14 +32448,14 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-438</t>
+          <t xml:space="preserve">v-436</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="E439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 6)</t>
+          <t xml:space="preserve">Unreadable row (D 4)</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -32410,14 +32490,14 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-439</t>
+          <t xml:space="preserve">v-437</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="E440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 7)</t>
+          <t xml:space="preserve">Unreadable row (D 5)</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -32452,14 +32532,14 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-440</t>
+          <t xml:space="preserve">v-438</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="E441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 8)</t>
+          <t xml:space="preserve">Unreadable row (D 6)</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -32494,14 +32574,14 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-441</t>
+          <t xml:space="preserve">v-439</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="E442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 9)</t>
+          <t xml:space="preserve">Unreadable row (D 7)</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -32536,14 +32616,14 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-442</t>
+          <t xml:space="preserve">v-440</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="E443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 1)</t>
+          <t xml:space="preserve">Unreadable row (D 8)</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -32578,14 +32658,14 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-443</t>
+          <t xml:space="preserve">v-441</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="E444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 2)</t>
+          <t xml:space="preserve">Unreadable row (D 9)</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
@@ -32620,14 +32700,14 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-444</t>
+          <t xml:space="preserve">v-442</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="E445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 3)</t>
+          <t xml:space="preserve">Unreadable row (E 1)</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
@@ -32662,14 +32742,14 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-445</t>
+          <t xml:space="preserve">v-443</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="E446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 4)</t>
+          <t xml:space="preserve">Unreadable row (E 2)</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -32704,14 +32784,14 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-446</t>
+          <t xml:space="preserve">v-444</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="E447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 5)</t>
+          <t xml:space="preserve">Unreadable row (E 3)</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -32746,14 +32826,14 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-447</t>
+          <t xml:space="preserve">v-445</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="E448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 6)</t>
+          <t xml:space="preserve">Unreadable row (E 4)</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -32788,14 +32868,14 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-448</t>
+          <t xml:space="preserve">v-446</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="E449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
+          <t xml:space="preserve">Unreadable row (E 5)</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -32830,14 +32910,14 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-449</t>
+          <t xml:space="preserve">v-447</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="E450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (E 6)</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
@@ -32872,14 +32952,14 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-450</t>
+          <t xml:space="preserve">v-448</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="E451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
@@ -32914,14 +32994,14 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-451</t>
+          <t xml:space="preserve">v-449</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="E452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 1)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -32956,14 +33036,14 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-452</t>
+          <t xml:space="preserve">v-450</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="E453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 2)</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -32998,14 +33078,14 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-453</t>
+          <t xml:space="preserve">v-451</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="E454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 3)</t>
+          <t xml:space="preserve">Unreadable row (F 1)</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -33040,14 +33120,14 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-454</t>
+          <t xml:space="preserve">v-452</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="E455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 4)</t>
+          <t xml:space="preserve">Unreadable row (F 2)</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -33082,14 +33162,14 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-455</t>
+          <t xml:space="preserve">v-453</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="E456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 5)</t>
+          <t xml:space="preserve">Unreadable row (F 3)</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -33124,14 +33204,14 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-456</t>
+          <t xml:space="preserve">v-454</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="E457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 6)</t>
+          <t xml:space="preserve">Unreadable row (F 4)</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -33166,14 +33246,14 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-457</t>
+          <t xml:space="preserve">v-455</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="E458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 7)</t>
+          <t xml:space="preserve">Unreadable row (F 5)</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -33208,14 +33288,14 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-458</t>
+          <t xml:space="preserve">v-456</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="E459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 8)</t>
+          <t xml:space="preserve">Unreadable row (F 6)</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -33250,14 +33330,14 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-459</t>
+          <t xml:space="preserve">v-457</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="E460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 9)</t>
+          <t xml:space="preserve">Unreadable row (F 7)</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -33292,14 +33372,14 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-460</t>
+          <t xml:space="preserve">v-458</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="E461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 1)</t>
+          <t xml:space="preserve">Unreadable row (F 8)</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -33334,14 +33414,14 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-461</t>
+          <t xml:space="preserve">v-459</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="E462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 2)</t>
+          <t xml:space="preserve">Unreadable row (F 9)</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -33376,14 +33456,14 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-462</t>
+          <t xml:space="preserve">v-460</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="E463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 3)</t>
+          <t xml:space="preserve">Unreadable row (G 1)</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -33418,14 +33498,14 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-463</t>
+          <t xml:space="preserve">v-461</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="E464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 4)</t>
+          <t xml:space="preserve">Unreadable row (G 2)</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -33460,14 +33540,14 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-464</t>
+          <t xml:space="preserve">v-462</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="E465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 5)</t>
+          <t xml:space="preserve">Unreadable row (G 3)</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -33502,14 +33582,14 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-465</t>
+          <t xml:space="preserve">v-463</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="E466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 6)</t>
+          <t xml:space="preserve">Unreadable row (G 4)</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -33544,14 +33624,14 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-466</t>
+          <t xml:space="preserve">v-464</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="E467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 7)</t>
+          <t xml:space="preserve">Unreadable row (G 5)</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -33586,14 +33666,14 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-467</t>
+          <t xml:space="preserve">v-465</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="E468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 8)</t>
+          <t xml:space="preserve">Unreadable row (G 6)</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -33628,14 +33708,14 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-468</t>
+          <t xml:space="preserve">v-466</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="E469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 9)</t>
+          <t xml:space="preserve">Unreadable row (G 7)</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -33670,14 +33750,14 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-469</t>
+          <t xml:space="preserve">v-467</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="E470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 1)</t>
+          <t xml:space="preserve">Unreadable row (G 8)</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -33712,14 +33792,14 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-470</t>
+          <t xml:space="preserve">v-468</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="E471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 2)</t>
+          <t xml:space="preserve">Unreadable row (G 9)</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
@@ -33754,14 +33834,14 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-471</t>
+          <t xml:space="preserve">v-469</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="E472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 3)</t>
+          <t xml:space="preserve">Unreadable row (H 1)</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -33796,14 +33876,14 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-472</t>
+          <t xml:space="preserve">v-470</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="E473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 4)</t>
+          <t xml:space="preserve">Unreadable row (H 2)</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
@@ -33838,14 +33918,14 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-473</t>
+          <t xml:space="preserve">v-471</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="E474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 5)</t>
+          <t xml:space="preserve">Unreadable row (H 3)</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -33880,14 +33960,14 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-474</t>
+          <t xml:space="preserve">v-472</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="E475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 6)</t>
+          <t xml:space="preserve">Unreadable row (H 4)</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -33922,14 +34002,14 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-475</t>
+          <t xml:space="preserve">v-473</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="E476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 7)</t>
+          <t xml:space="preserve">Unreadable row (H 5)</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -33964,14 +34044,14 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-476</t>
+          <t xml:space="preserve">v-474</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="E477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 8)</t>
+          <t xml:space="preserve">Unreadable row (H 6)</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
@@ -34006,14 +34086,14 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-477</t>
+          <t xml:space="preserve">v-475</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="E478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 9)</t>
+          <t xml:space="preserve">Unreadable row (H 7)</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -34048,14 +34128,14 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-478</t>
+          <t xml:space="preserve">v-476</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="E479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 1)</t>
+          <t xml:space="preserve">Unreadable row (H 8)</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -34090,14 +34170,14 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-479</t>
+          <t xml:space="preserve">v-477</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="E480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 2)</t>
+          <t xml:space="preserve">Unreadable row (H 9)</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
@@ -34132,14 +34212,14 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-480</t>
+          <t xml:space="preserve">v-478</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="E481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 3)</t>
+          <t xml:space="preserve">Unreadable row (I 1)</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -34174,14 +34254,14 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-481</t>
+          <t xml:space="preserve">v-479</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="E482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 4)</t>
+          <t xml:space="preserve">Unreadable row (I 2)</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
@@ -34216,14 +34296,14 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-482</t>
+          <t xml:space="preserve">v-480</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="E483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 5)</t>
+          <t xml:space="preserve">Unreadable row (I 3)</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -34258,14 +34338,14 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-483</t>
+          <t xml:space="preserve">v-481</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="E484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 6)</t>
+          <t xml:space="preserve">Unreadable row (I 4)</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -34300,14 +34380,14 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-484</t>
+          <t xml:space="preserve">v-482</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="E485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 7)</t>
+          <t xml:space="preserve">Unreadable row (I 5)</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -34342,14 +34422,14 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-485</t>
+          <t xml:space="preserve">v-483</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="E486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 8)</t>
+          <t xml:space="preserve">Unreadable row (I 6)</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -34384,47 +34464,131 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-486</t>
+          <t xml:space="preserve">v-484</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="E487" t="inlineStr">
         <is>
+          <t xml:space="preserve">Unreadable row (I 7)</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-485</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="E488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unreadable row (I 8)</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-486</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="E489" t="inlineStr">
+        <is>
           <t xml:space="preserve">Unreadable row (I 9)</t>
         </is>
       </c>
-      <c r="J487" t="inlineStr">
+      <c r="J489" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L487" t="inlineStr">
+      <c r="L489" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
         </is>
       </c>
-      <c r="M487" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N487" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O487" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R487" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S487" t="inlineStr">
+      <c r="M489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
         <is>
           <t xml:space="preserve">v-487</t>
         </is>
@@ -35035,12 +35199,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -35050,7 +35214,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E20">
@@ -35060,18 +35224,18 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -35081,28 +35245,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">DuPar50CR+1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -35122,18 +35286,18 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -35143,7 +35307,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E23">
@@ -35153,18 +35317,18 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -35174,7 +35338,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E24">
@@ -35184,13 +35348,28 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
+          <t xml:space="preserve">LUCX gP1</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E25">
@@ -35200,13 +35379,13 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="E26">
@@ -35222,7 +35401,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="E27">
@@ -35238,38 +35417,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -35279,12 +35443,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E29">
@@ -40304,10 +40468,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J6">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20123,7 +20123,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">hek gnt</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R243" t="inlineStr">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdw768-0</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">hek gnt</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -20250,7 +20250,7 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R244" t="inlineStr">
@@ -20260,7 +20260,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdw768-1</t>
+          <t xml:space="preserve">v-mtrdx0po-1</t>
         </is>
       </c>
     </row>

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -19723,37 +19723,42 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
+          <t xml:space="preserve">hek 3xflag</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p21</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -19778,7 +19783,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-335</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
@@ -19800,37 +19805,42 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
+          <t xml:space="preserve">hek 3xflag</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p21</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -19855,7 +19865,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-336</t>
+          <t xml:space="preserve">v-mtrdyhss-1</t>
         </is>
       </c>
     </row>
@@ -19877,7 +19887,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -19887,7 +19897,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -19895,14 +19905,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-27</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27-11-25</t>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -19937,7 +19942,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-337</t>
+          <t xml:space="preserve">v-335</t>
         </is>
       </c>
     </row>
@@ -19959,7 +19964,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -19969,7 +19974,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -19977,14 +19982,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-06</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6/11/2025</t>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-338</t>
+          <t xml:space="preserve">v-336</t>
         </is>
       </c>
     </row>
@@ -20041,7 +20041,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -20061,12 +20061,12 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-27</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">27-11-25</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-339</t>
+          <t xml:space="preserve">v-337</t>
         </is>
       </c>
     </row>
@@ -20123,7 +20123,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -20183,7 +20183,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-340</t>
+          <t xml:space="preserve">v-338</t>
         </is>
       </c>
     </row>
@@ -20205,7 +20205,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -20215,7 +20215,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -20223,9 +20223,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-27</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -20260,7 +20265,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-341</t>
+          <t xml:space="preserve">v-339</t>
         </is>
       </c>
     </row>
@@ -20282,17 +20287,17 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek gnt</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -20302,12 +20307,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -20342,7 +20347,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-340</t>
         </is>
       </c>
     </row>
@@ -20364,17 +20369,17 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek gnt</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -20382,14 +20387,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -20424,7 +20424,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-1</t>
+          <t xml:space="preserve">v-341</t>
         </is>
       </c>
     </row>
@@ -20446,17 +20446,17 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">hek gnt</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -20466,17 +20466,17 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
@@ -20528,17 +20528,17 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">hek gnt</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -20548,17 +20548,17 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -20588,7 +20588,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-mtrdx0po-1</t>
         </is>
       </c>
     </row>
@@ -20610,7 +20610,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20670,7 +20670,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20692,7 +20692,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -20794,12 +20794,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-17</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-12-25</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -20856,32 +20856,32 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
@@ -20891,22 +20891,22 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -21020,57 +21020,57 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -21102,17 +21102,17 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -21122,12 +21122,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -21137,22 +21137,22 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -21184,17 +21184,17 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -21204,17 +21204,17 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -21266,12 +21266,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -21286,37 +21286,37 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-08-10</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/8/2026</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -21348,57 +21348,57 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21430,12 +21430,12 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -21450,37 +21450,37 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21512,32 +21512,32 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -21594,32 +21594,32 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -21676,32 +21676,32 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -21726,7 +21726,7 @@
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -21778,12 +21778,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -21840,47 +21840,52 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">2/12/2025</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
@@ -21895,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -21917,52 +21922,57 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">2/12/2025</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -21972,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -21994,17 +22004,17 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -22014,17 +22024,12 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
-        </is>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -22044,7 +22049,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22054,7 +22059,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22071,22 +22076,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -22096,37 +22101,32 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
-        </is>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22153,22 +22153,22 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -22178,37 +22178,37 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22240,32 +22240,32 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -22322,32 +22322,32 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -22404,22 +22404,22 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -22454,7 +22454,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22486,17 +22486,17 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -22506,12 +22506,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -22536,7 +22536,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -22568,17 +22568,17 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -22588,12 +22588,12 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -22650,22 +22650,22 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -22732,12 +22732,12 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -22752,12 +22752,12 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -22814,17 +22814,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -22834,37 +22834,37 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -22896,57 +22896,57 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -22978,12 +22978,12 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -23013,7 +23013,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23060,12 +23060,12 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23142,17 +23142,17 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -23162,12 +23162,12 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23224,17 +23224,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -23244,12 +23244,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -23306,12 +23306,12 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -23388,17 +23388,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -23408,12 +23408,12 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -23470,12 +23470,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -23552,37 +23552,42 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="J285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -23597,7 +23602,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23607,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -23629,42 +23634,42 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -23679,7 +23684,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23689,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -23711,17 +23716,17 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23729,14 +23734,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23771,7 +23771,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -23793,17 +23793,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -23813,12 +23813,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23828,7 +23828,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -23843,7 +23843,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -23875,17 +23875,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -23895,12 +23895,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23925,7 +23925,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -23957,17 +23957,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23977,12 +23977,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24017,7 +24017,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24039,12 +24039,12 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24074,7 +24074,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -24089,7 +24089,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24099,7 +24099,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24121,32 +24121,32 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24156,7 +24156,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24203,17 +24203,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24223,12 +24223,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24253,7 +24253,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -24285,17 +24285,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24305,37 +24305,37 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -24367,17 +24367,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -24387,37 +24387,37 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -24449,17 +24449,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -24531,57 +24531,57 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p7</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -24613,57 +24613,57 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p|+7</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-08</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8/1/2026</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -24695,32 +24695,32 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24730,22 +24730,22 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -24777,17 +24777,17 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24812,22 +24812,22 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -24859,17 +24859,17 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -24879,12 +24879,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -24941,17 +24941,17 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24961,12 +24961,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25023,57 +25023,57 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25105,17 +25105,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25125,37 +25125,37 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25187,12 +25187,12 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -25269,12 +25269,12 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -25351,32 +25351,32 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -25433,17 +25433,17 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -25453,12 +25453,12 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -25515,32 +25515,32 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
-        </is>
-      </c>
-      <c r="J309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -25597,17 +25597,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25617,12 +25617,12 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -25679,32 +25679,32 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">caNT read</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -25761,17 +25761,17 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -25781,22 +25781,22 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -25843,17 +25843,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25863,22 +25863,22 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -25925,17 +25925,17 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26007,17 +26007,17 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26089,17 +26089,17 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26171,22 +26171,22 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -26206,7 +26206,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26253,32 +26253,32 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26335,12 +26335,12 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26417,42 +26417,42 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+6</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26519,22 +26519,22 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26549,17 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26569,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -26591,37 +26581,37 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -26641,17 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26661,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -26683,17 +26663,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26703,12 +26683,12 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -26733,7 +26713,17 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26743,7 +26733,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -26765,12 +26755,12 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -26815,7 +26805,17 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26825,7 +26825,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -26847,32 +26847,32 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26897,7 +26897,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26907,7 +26907,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -26929,32 +26929,32 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26989,7 +26989,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27011,12 +27011,12 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -27071,7 +27071,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27093,17 +27093,17 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p45769</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -27111,9 +27111,14 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J328" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-19</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27123,7 +27128,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27133,7 +27138,7 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
@@ -27148,7 +27153,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27170,32 +27175,32 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27205,7 +27210,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27215,7 +27220,7 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
@@ -27230,7 +27235,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27252,17 +27257,17 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p45769</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27270,24 +27275,19 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-04-10</t>
-        </is>
-      </c>
-      <c r="I330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/4/2026</t>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27297,12 +27297,12 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27312,7 +27312,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27334,42 +27334,42 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27379,12 +27379,12 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27416,7 +27416,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -27476,7 +27476,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -27498,12 +27498,12 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -27518,12 +27518,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27533,7 +27533,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -27548,7 +27548,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27558,7 +27558,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -27580,17 +27580,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27615,7 +27615,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27640,7 +27640,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -27662,32 +27662,32 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27697,7 +27697,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -27707,12 +27707,12 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27722,7 +27722,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -27744,12 +27744,12 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -27764,12 +27764,12 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27779,7 +27779,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -27826,32 +27826,32 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27861,7 +27861,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -27871,12 +27871,12 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -27908,17 +27908,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -27958,7 +27958,7 @@
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -27990,57 +27990,57 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28072,57 +28072,57 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28154,7 +28154,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -28164,7 +28164,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -28174,12 +28174,12 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28236,7 +28236,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -28318,7 +28318,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28400,7 +28400,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -28482,57 +28482,57 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+4</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-05-14</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14-05-25</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K345" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -28564,32 +28564,32 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p218</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28599,22 +28599,22 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -28646,158 +28646,238 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
+          <t xml:space="preserve">I7</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p?</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="M347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-161</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p218</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="M348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-162</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -80</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
           <t xml:space="preserve">I9</t>
         </is>
       </c>
-      <c r="E347" t="inlineStr">
+      <c r="E349" t="inlineStr">
         <is>
           <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
-      <c r="F347" t="inlineStr">
+      <c r="F349" t="inlineStr">
         <is>
           <t xml:space="preserve">p8</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr">
+      <c r="G349" t="inlineStr">
         <is>
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="H347" t="inlineStr">
+      <c r="H349" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
-      <c r="I347" t="inlineStr">
+      <c r="I349" t="inlineStr">
         <is>
           <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr">
+      <c r="K349" t="inlineStr">
         <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="L347" t="inlineStr">
+      <c r="L349" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="M347" t="inlineStr">
+      <c r="M349" t="inlineStr">
         <is>
           <t xml:space="preserve">DtxR</t>
         </is>
       </c>
-      <c r="N347" t="inlineStr">
+      <c r="N349" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="O347" t="inlineStr">
+      <c r="O349" t="inlineStr">
         <is>
           <t xml:space="preserve">g3</t>
         </is>
       </c>
-      <c r="R347" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S347" t="inlineStr">
+      <c r="R349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S349" t="inlineStr">
         <is>
           <t xml:space="preserve">v-163</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="E348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unreadable row (E 6)</t>
-        </is>
-      </c>
-      <c r="J348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="L348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="M348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S348" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-205</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="E349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
-        </is>
-      </c>
-      <c r="L349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">WT</t>
-        </is>
-      </c>
-      <c r="M349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S349" t="inlineStr">
-        <is>
-          <t xml:space="preserve">v-206</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (E 6)</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
@@ -28832,14 +28912,14 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-207</t>
+          <t xml:space="preserve">v-205</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
@@ -28874,14 +28954,14 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-208</t>
+          <t xml:space="preserve">v-206</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 8)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
@@ -28916,14 +28996,14 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-234</t>
+          <t xml:space="preserve">v-207</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 9)</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
@@ -28958,14 +29038,14 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-235</t>
+          <t xml:space="preserve">v-208</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 8)</t>
+          <t xml:space="preserve">Unreadable row (H 8)</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
@@ -29000,14 +29080,14 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-243</t>
+          <t xml:space="preserve">v-234</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 5)</t>
+          <t xml:space="preserve">Unreadable row (H 9)</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
@@ -29042,14 +29122,14 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-285</t>
+          <t xml:space="preserve">v-235</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 6)</t>
+          <t xml:space="preserve">Unreadable row (I 8)</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
@@ -29084,14 +29164,14 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-286</t>
+          <t xml:space="preserve">v-243</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
+          <t xml:space="preserve">Unreadable row (E 5)</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -29126,14 +29206,14 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-287</t>
+          <t xml:space="preserve">v-285</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (E 6)</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
@@ -29168,14 +29248,14 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-288</t>
+          <t xml:space="preserve">v-286</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -29210,14 +29290,14 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-289</t>
+          <t xml:space="preserve">v-287</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="E360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 4)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
@@ -29252,14 +29332,14 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-329</t>
+          <t xml:space="preserve">v-288</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="E361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 5)</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
@@ -29294,14 +29374,14 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-330</t>
+          <t xml:space="preserve">v-289</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="E362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 6)</t>
+          <t xml:space="preserve">Unreadable row (A 4)</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -29336,14 +29416,14 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-331</t>
+          <t xml:space="preserve">v-329</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="E363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 7)</t>
+          <t xml:space="preserve">Unreadable row (A 5)</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -29378,14 +29458,14 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-332</t>
+          <t xml:space="preserve">v-330</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="E364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 8)</t>
+          <t xml:space="preserve">Unreadable row (A 6)</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
@@ -29420,14 +29500,14 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-333</t>
+          <t xml:space="preserve">v-331</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="E365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 9)</t>
+          <t xml:space="preserve">Unreadable row (A 7)</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -29462,14 +29542,14 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-334</t>
+          <t xml:space="preserve">v-332</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="E366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 8)</t>
+          <t xml:space="preserve">Unreadable row (A 8)</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -29504,14 +29584,14 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-342</t>
+          <t xml:space="preserve">v-333</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="E367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 9)</t>
+          <t xml:space="preserve">Unreadable row (A 9)</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -29546,14 +29626,14 @@
       </c>
       <c r="S367" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-343</t>
+          <t xml:space="preserve">v-334</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="E368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 3)</t>
+          <t xml:space="preserve">Unreadable row (B 8)</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
@@ -29588,14 +29668,14 @@
       </c>
       <c r="S368" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-355</t>
+          <t xml:space="preserve">v-342</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="E369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 4)</t>
+          <t xml:space="preserve">Unreadable row (B 9)</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -29630,14 +29710,14 @@
       </c>
       <c r="S369" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-356</t>
+          <t xml:space="preserve">v-343</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="E370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 5)</t>
+          <t xml:space="preserve">Unreadable row (D 3)</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
@@ -29672,14 +29752,14 @@
       </c>
       <c r="S370" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-357</t>
+          <t xml:space="preserve">v-355</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="E371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 6)</t>
+          <t xml:space="preserve">Unreadable row (D 4)</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
@@ -29714,14 +29794,14 @@
       </c>
       <c r="S371" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-358</t>
+          <t xml:space="preserve">v-356</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="E372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 7)</t>
+          <t xml:space="preserve">Unreadable row (D 5)</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
@@ -29756,14 +29836,14 @@
       </c>
       <c r="S372" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-359</t>
+          <t xml:space="preserve">v-357</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="E373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 8)</t>
+          <t xml:space="preserve">Unreadable row (D 6)</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
@@ -29798,14 +29878,14 @@
       </c>
       <c r="S373" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-360</t>
+          <t xml:space="preserve">v-358</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="E374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 9)</t>
+          <t xml:space="preserve">Unreadable row (D 7)</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
@@ -29840,14 +29920,14 @@
       </c>
       <c r="S374" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-361</t>
+          <t xml:space="preserve">v-359</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="E375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
+          <t xml:space="preserve">Unreadable row (D 8)</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
@@ -29882,14 +29962,14 @@
       </c>
       <c r="S375" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-368</t>
+          <t xml:space="preserve">v-360</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="E376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (D 9)</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
@@ -29924,14 +30004,14 @@
       </c>
       <c r="S376" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-369</t>
+          <t xml:space="preserve">v-361</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="E377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
@@ -29966,14 +30046,14 @@
       </c>
       <c r="S377" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-370</t>
+          <t xml:space="preserve">v-368</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="E378" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 3)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
@@ -30008,14 +30088,14 @@
       </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-373</t>
+          <t xml:space="preserve">v-369</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="E379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 4)</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
@@ -30050,14 +30130,14 @@
       </c>
       <c r="S379" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-374</t>
+          <t xml:space="preserve">v-370</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="E380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 5)</t>
+          <t xml:space="preserve">Unreadable row (F 3)</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -30092,14 +30172,14 @@
       </c>
       <c r="S380" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-375</t>
+          <t xml:space="preserve">v-373</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="E381" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 6)</t>
+          <t xml:space="preserve">Unreadable row (F 4)</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
@@ -30134,14 +30214,14 @@
       </c>
       <c r="S381" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-376</t>
+          <t xml:space="preserve">v-374</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="E382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 7)</t>
+          <t xml:space="preserve">Unreadable row (F 5)</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
@@ -30176,14 +30256,14 @@
       </c>
       <c r="S382" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-377</t>
+          <t xml:space="preserve">v-375</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="E383" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 8)</t>
+          <t xml:space="preserve">Unreadable row (F 6)</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
@@ -30218,14 +30298,14 @@
       </c>
       <c r="S383" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-378</t>
+          <t xml:space="preserve">v-376</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="E384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 9)</t>
+          <t xml:space="preserve">Unreadable row (F 7)</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -30260,14 +30340,14 @@
       </c>
       <c r="S384" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-379</t>
+          <t xml:space="preserve">v-377</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="E385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 2)</t>
+          <t xml:space="preserve">Unreadable row (F 8)</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
@@ -30302,14 +30382,14 @@
       </c>
       <c r="S385" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-381</t>
+          <t xml:space="preserve">v-378</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="E386" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 3)</t>
+          <t xml:space="preserve">Unreadable row (F 9)</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
@@ -30344,14 +30424,14 @@
       </c>
       <c r="S386" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-382</t>
+          <t xml:space="preserve">v-379</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="E387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 4)</t>
+          <t xml:space="preserve">Unreadable row (G 2)</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
@@ -30386,14 +30466,14 @@
       </c>
       <c r="S387" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-383</t>
+          <t xml:space="preserve">v-381</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="E388" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 5)</t>
+          <t xml:space="preserve">Unreadable row (G 3)</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
@@ -30428,14 +30508,14 @@
       </c>
       <c r="S388" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-384</t>
+          <t xml:space="preserve">v-382</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="E389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 6)</t>
+          <t xml:space="preserve">Unreadable row (G 4)</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
@@ -30470,14 +30550,14 @@
       </c>
       <c r="S389" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-385</t>
+          <t xml:space="preserve">v-383</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="E390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 7)</t>
+          <t xml:space="preserve">Unreadable row (G 5)</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
@@ -30512,14 +30592,14 @@
       </c>
       <c r="S390" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-386</t>
+          <t xml:space="preserve">v-384</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="E391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 8)</t>
+          <t xml:space="preserve">Unreadable row (G 6)</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
@@ -30554,14 +30634,14 @@
       </c>
       <c r="S391" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-387</t>
+          <t xml:space="preserve">v-385</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="E392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 9)</t>
+          <t xml:space="preserve">Unreadable row (G 7)</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
@@ -30596,14 +30676,14 @@
       </c>
       <c r="S392" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-388</t>
+          <t xml:space="preserve">v-386</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="E393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 1)</t>
+          <t xml:space="preserve">Unreadable row (G 8)</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -30638,14 +30718,14 @@
       </c>
       <c r="S393" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-389</t>
+          <t xml:space="preserve">v-387</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="E394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 2)</t>
+          <t xml:space="preserve">Unreadable row (G 9)</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
@@ -30680,14 +30760,14 @@
       </c>
       <c r="S394" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-390</t>
+          <t xml:space="preserve">v-388</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="E395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 3)</t>
+          <t xml:space="preserve">Unreadable row (H 1)</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
@@ -30722,14 +30802,14 @@
       </c>
       <c r="S395" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-391</t>
+          <t xml:space="preserve">v-389</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="E396" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 4)</t>
+          <t xml:space="preserve">Unreadable row (H 2)</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
@@ -30764,14 +30844,14 @@
       </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-392</t>
+          <t xml:space="preserve">v-390</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="E397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 5)</t>
+          <t xml:space="preserve">Unreadable row (H 3)</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
@@ -30806,14 +30886,14 @@
       </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-393</t>
+          <t xml:space="preserve">v-391</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="E398" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 6)</t>
+          <t xml:space="preserve">Unreadable row (H 4)</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
@@ -30848,14 +30928,14 @@
       </c>
       <c r="S398" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-394</t>
+          <t xml:space="preserve">v-392</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="E399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 7)</t>
+          <t xml:space="preserve">Unreadable row (H 5)</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
@@ -30890,14 +30970,14 @@
       </c>
       <c r="S399" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-395</t>
+          <t xml:space="preserve">v-393</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="E400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 8)</t>
+          <t xml:space="preserve">Unreadable row (H 6)</t>
         </is>
       </c>
       <c r="J400" t="inlineStr">
@@ -30932,14 +31012,14 @@
       </c>
       <c r="S400" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-396</t>
+          <t xml:space="preserve">v-394</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="E401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 9)</t>
+          <t xml:space="preserve">Unreadable row (H 7)</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
@@ -30974,14 +31054,14 @@
       </c>
       <c r="S401" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-397</t>
+          <t xml:space="preserve">v-395</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="E402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 1)</t>
+          <t xml:space="preserve">Unreadable row (H 8)</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -31016,14 +31096,14 @@
       </c>
       <c r="S402" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-398</t>
+          <t xml:space="preserve">v-396</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="E403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 2)</t>
+          <t xml:space="preserve">Unreadable row (H 9)</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
@@ -31058,14 +31138,14 @@
       </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-399</t>
+          <t xml:space="preserve">v-397</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="E404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 3)</t>
+          <t xml:space="preserve">Unreadable row (I 1)</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
@@ -31100,14 +31180,14 @@
       </c>
       <c r="S404" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-400</t>
+          <t xml:space="preserve">v-398</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="E405" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 4)</t>
+          <t xml:space="preserve">Unreadable row (I 2)</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
@@ -31142,14 +31222,14 @@
       </c>
       <c r="S405" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-401</t>
+          <t xml:space="preserve">v-399</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="E406" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 5)</t>
+          <t xml:space="preserve">Unreadable row (I 3)</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
@@ -31184,14 +31264,14 @@
       </c>
       <c r="S406" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-402</t>
+          <t xml:space="preserve">v-400</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="E407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 6)</t>
+          <t xml:space="preserve">Unreadable row (I 4)</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
@@ -31226,14 +31306,14 @@
       </c>
       <c r="S407" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-403</t>
+          <t xml:space="preserve">v-401</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="E408" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 7)</t>
+          <t xml:space="preserve">Unreadable row (I 5)</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
@@ -31268,14 +31348,14 @@
       </c>
       <c r="S408" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-404</t>
+          <t xml:space="preserve">v-402</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="E409" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 8)</t>
+          <t xml:space="preserve">Unreadable row (I 6)</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
@@ -31310,14 +31390,14 @@
       </c>
       <c r="S409" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-405</t>
+          <t xml:space="preserve">v-403</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="E410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 9)</t>
+          <t xml:space="preserve">Unreadable row (I 7)</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
@@ -31352,14 +31432,14 @@
       </c>
       <c r="S410" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-406</t>
+          <t xml:space="preserve">v-404</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="E411" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 1)</t>
+          <t xml:space="preserve">Unreadable row (I 8)</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
@@ -31394,14 +31474,14 @@
       </c>
       <c r="S411" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-407</t>
+          <t xml:space="preserve">v-405</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="E412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 2)</t>
+          <t xml:space="preserve">Unreadable row (I 9)</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -31436,14 +31516,14 @@
       </c>
       <c r="S412" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-408</t>
+          <t xml:space="preserve">v-406</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="E413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 3)</t>
+          <t xml:space="preserve">Unreadable row (A 1)</t>
         </is>
       </c>
       <c r="J413" t="inlineStr">
@@ -31478,14 +31558,14 @@
       </c>
       <c r="S413" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-409</t>
+          <t xml:space="preserve">v-407</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="E414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 4)</t>
+          <t xml:space="preserve">Unreadable row (A 2)</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -31520,14 +31600,14 @@
       </c>
       <c r="S414" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-410</t>
+          <t xml:space="preserve">v-408</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="E415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 5)</t>
+          <t xml:space="preserve">Unreadable row (A 3)</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
@@ -31562,14 +31642,14 @@
       </c>
       <c r="S415" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-411</t>
+          <t xml:space="preserve">v-409</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="E416" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 6)</t>
+          <t xml:space="preserve">Unreadable row (A 4)</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -31604,14 +31684,14 @@
       </c>
       <c r="S416" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-412</t>
+          <t xml:space="preserve">v-410</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="E417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 7)</t>
+          <t xml:space="preserve">Unreadable row (A 5)</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
@@ -31646,14 +31726,14 @@
       </c>
       <c r="S417" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-413</t>
+          <t xml:space="preserve">v-411</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="E418" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 8)</t>
+          <t xml:space="preserve">Unreadable row (A 6)</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
@@ -31688,14 +31768,14 @@
       </c>
       <c r="S418" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-414</t>
+          <t xml:space="preserve">v-412</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="E419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (A 9)</t>
+          <t xml:space="preserve">Unreadable row (A 7)</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
@@ -31730,14 +31810,14 @@
       </c>
       <c r="S419" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-415</t>
+          <t xml:space="preserve">v-413</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="E420" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 1)</t>
+          <t xml:space="preserve">Unreadable row (A 8)</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
@@ -31772,14 +31852,14 @@
       </c>
       <c r="S420" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-416</t>
+          <t xml:space="preserve">v-414</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="E421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 2)</t>
+          <t xml:space="preserve">Unreadable row (A 9)</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
@@ -31814,14 +31894,14 @@
       </c>
       <c r="S421" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-417</t>
+          <t xml:space="preserve">v-415</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="E422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 3)</t>
+          <t xml:space="preserve">Unreadable row (B 1)</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
@@ -31856,14 +31936,14 @@
       </c>
       <c r="S422" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-418</t>
+          <t xml:space="preserve">v-416</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="E423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 4)</t>
+          <t xml:space="preserve">Unreadable row (B 2)</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
@@ -31898,14 +31978,14 @@
       </c>
       <c r="S423" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-419</t>
+          <t xml:space="preserve">v-417</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="E424" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 5)</t>
+          <t xml:space="preserve">Unreadable row (B 3)</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
@@ -31940,14 +32020,14 @@
       </c>
       <c r="S424" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-420</t>
+          <t xml:space="preserve">v-418</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="E425" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 6)</t>
+          <t xml:space="preserve">Unreadable row (B 4)</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
@@ -31982,14 +32062,14 @@
       </c>
       <c r="S425" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-421</t>
+          <t xml:space="preserve">v-419</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="E426" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 7)</t>
+          <t xml:space="preserve">Unreadable row (B 5)</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
@@ -32024,14 +32104,14 @@
       </c>
       <c r="S426" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-422</t>
+          <t xml:space="preserve">v-420</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="E427" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 8)</t>
+          <t xml:space="preserve">Unreadable row (B 6)</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -32066,14 +32146,14 @@
       </c>
       <c r="S427" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-423</t>
+          <t xml:space="preserve">v-421</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="E428" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (B 9)</t>
+          <t xml:space="preserve">Unreadable row (B 7)</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
@@ -32108,14 +32188,14 @@
       </c>
       <c r="S428" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-424</t>
+          <t xml:space="preserve">v-422</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="E429" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 1)</t>
+          <t xml:space="preserve">Unreadable row (B 8)</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
@@ -32150,14 +32230,14 @@
       </c>
       <c r="S429" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-425</t>
+          <t xml:space="preserve">v-423</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="E430" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 2)</t>
+          <t xml:space="preserve">Unreadable row (B 9)</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
@@ -32192,14 +32272,14 @@
       </c>
       <c r="S430" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-426</t>
+          <t xml:space="preserve">v-424</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="E431" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 3)</t>
+          <t xml:space="preserve">Unreadable row (C 1)</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
@@ -32234,14 +32314,14 @@
       </c>
       <c r="S431" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-427</t>
+          <t xml:space="preserve">v-425</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="E432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 4)</t>
+          <t xml:space="preserve">Unreadable row (C 2)</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
@@ -32276,14 +32356,14 @@
       </c>
       <c r="S432" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-428</t>
+          <t xml:space="preserve">v-426</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="E433" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 5)</t>
+          <t xml:space="preserve">Unreadable row (C 3)</t>
         </is>
       </c>
       <c r="J433" t="inlineStr">
@@ -32318,14 +32398,14 @@
       </c>
       <c r="S433" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-429</t>
+          <t xml:space="preserve">v-427</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="E434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 6)</t>
+          <t xml:space="preserve">Unreadable row (C 4)</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
@@ -32360,14 +32440,14 @@
       </c>
       <c r="S434" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-430</t>
+          <t xml:space="preserve">v-428</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="E435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 7)</t>
+          <t xml:space="preserve">Unreadable row (C 5)</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
@@ -32402,14 +32482,14 @@
       </c>
       <c r="S435" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-431</t>
+          <t xml:space="preserve">v-429</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="E436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 8)</t>
+          <t xml:space="preserve">Unreadable row (C 6)</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
@@ -32444,14 +32524,14 @@
       </c>
       <c r="S436" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-432</t>
+          <t xml:space="preserve">v-430</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="E437" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (C 9)</t>
+          <t xml:space="preserve">Unreadable row (C 7)</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
@@ -32486,14 +32566,14 @@
       </c>
       <c r="S437" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-433</t>
+          <t xml:space="preserve">v-431</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="E438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 1)</t>
+          <t xml:space="preserve">Unreadable row (C 8)</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
@@ -32528,14 +32608,14 @@
       </c>
       <c r="S438" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-434</t>
+          <t xml:space="preserve">v-432</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="E439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 2)</t>
+          <t xml:space="preserve">Unreadable row (C 9)</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
@@ -32570,14 +32650,14 @@
       </c>
       <c r="S439" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-435</t>
+          <t xml:space="preserve">v-433</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="E440" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 3)</t>
+          <t xml:space="preserve">Unreadable row (D 1)</t>
         </is>
       </c>
       <c r="J440" t="inlineStr">
@@ -32612,14 +32692,14 @@
       </c>
       <c r="S440" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-436</t>
+          <t xml:space="preserve">v-434</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="E441" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 4)</t>
+          <t xml:space="preserve">Unreadable row (D 2)</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
@@ -32654,14 +32734,14 @@
       </c>
       <c r="S441" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-437</t>
+          <t xml:space="preserve">v-435</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="E442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 5)</t>
+          <t xml:space="preserve">Unreadable row (D 3)</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
@@ -32696,14 +32776,14 @@
       </c>
       <c r="S442" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-438</t>
+          <t xml:space="preserve">v-436</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="E443" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 6)</t>
+          <t xml:space="preserve">Unreadable row (D 4)</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
@@ -32738,14 +32818,14 @@
       </c>
       <c r="S443" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-439</t>
+          <t xml:space="preserve">v-437</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="E444" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 7)</t>
+          <t xml:space="preserve">Unreadable row (D 5)</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
@@ -32780,14 +32860,14 @@
       </c>
       <c r="S444" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-440</t>
+          <t xml:space="preserve">v-438</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="E445" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 8)</t>
+          <t xml:space="preserve">Unreadable row (D 6)</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
@@ -32822,14 +32902,14 @@
       </c>
       <c r="S445" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-441</t>
+          <t xml:space="preserve">v-439</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="E446" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (D 9)</t>
+          <t xml:space="preserve">Unreadable row (D 7)</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
@@ -32864,14 +32944,14 @@
       </c>
       <c r="S446" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-442</t>
+          <t xml:space="preserve">v-440</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="E447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 1)</t>
+          <t xml:space="preserve">Unreadable row (D 8)</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
@@ -32906,14 +32986,14 @@
       </c>
       <c r="S447" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-443</t>
+          <t xml:space="preserve">v-441</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="E448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 2)</t>
+          <t xml:space="preserve">Unreadable row (D 9)</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
@@ -32948,14 +33028,14 @@
       </c>
       <c r="S448" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-444</t>
+          <t xml:space="preserve">v-442</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="E449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 3)</t>
+          <t xml:space="preserve">Unreadable row (E 1)</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
@@ -32990,14 +33070,14 @@
       </c>
       <c r="S449" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-445</t>
+          <t xml:space="preserve">v-443</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="E450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 4)</t>
+          <t xml:space="preserve">Unreadable row (E 2)</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
@@ -33032,14 +33112,14 @@
       </c>
       <c r="S450" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-446</t>
+          <t xml:space="preserve">v-444</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="E451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 5)</t>
+          <t xml:space="preserve">Unreadable row (E 3)</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
@@ -33074,14 +33154,14 @@
       </c>
       <c r="S451" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-447</t>
+          <t xml:space="preserve">v-445</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="E452" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 6)</t>
+          <t xml:space="preserve">Unreadable row (E 4)</t>
         </is>
       </c>
       <c r="J452" t="inlineStr">
@@ -33116,14 +33196,14 @@
       </c>
       <c r="S452" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-448</t>
+          <t xml:space="preserve">v-446</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="E453" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
+          <t xml:space="preserve">Unreadable row (E 5)</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
@@ -33158,14 +33238,14 @@
       </c>
       <c r="S453" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-449</t>
+          <t xml:space="preserve">v-447</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="E454" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (E 6)</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
@@ -33200,14 +33280,14 @@
       </c>
       <c r="S454" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-450</t>
+          <t xml:space="preserve">v-448</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="E455" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -33242,14 +33322,14 @@
       </c>
       <c r="S455" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-451</t>
+          <t xml:space="preserve">v-449</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="E456" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 1)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="J456" t="inlineStr">
@@ -33284,14 +33364,14 @@
       </c>
       <c r="S456" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-452</t>
+          <t xml:space="preserve">v-450</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="E457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 2)</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
@@ -33326,14 +33406,14 @@
       </c>
       <c r="S457" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-453</t>
+          <t xml:space="preserve">v-451</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="E458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 3)</t>
+          <t xml:space="preserve">Unreadable row (F 1)</t>
         </is>
       </c>
       <c r="J458" t="inlineStr">
@@ -33368,14 +33448,14 @@
       </c>
       <c r="S458" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-454</t>
+          <t xml:space="preserve">v-452</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="E459" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 4)</t>
+          <t xml:space="preserve">Unreadable row (F 2)</t>
         </is>
       </c>
       <c r="J459" t="inlineStr">
@@ -33410,14 +33490,14 @@
       </c>
       <c r="S459" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-455</t>
+          <t xml:space="preserve">v-453</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="E460" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 5)</t>
+          <t xml:space="preserve">Unreadable row (F 3)</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
@@ -33452,14 +33532,14 @@
       </c>
       <c r="S460" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-456</t>
+          <t xml:space="preserve">v-454</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="E461" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 6)</t>
+          <t xml:space="preserve">Unreadable row (F 4)</t>
         </is>
       </c>
       <c r="J461" t="inlineStr">
@@ -33494,14 +33574,14 @@
       </c>
       <c r="S461" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-457</t>
+          <t xml:space="preserve">v-455</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="E462" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 7)</t>
+          <t xml:space="preserve">Unreadable row (F 5)</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
@@ -33536,14 +33616,14 @@
       </c>
       <c r="S462" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-458</t>
+          <t xml:space="preserve">v-456</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="E463" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 8)</t>
+          <t xml:space="preserve">Unreadable row (F 6)</t>
         </is>
       </c>
       <c r="J463" t="inlineStr">
@@ -33578,14 +33658,14 @@
       </c>
       <c r="S463" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-459</t>
+          <t xml:space="preserve">v-457</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="E464" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (F 9)</t>
+          <t xml:space="preserve">Unreadable row (F 7)</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
@@ -33620,14 +33700,14 @@
       </c>
       <c r="S464" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-460</t>
+          <t xml:space="preserve">v-458</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="E465" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 1)</t>
+          <t xml:space="preserve">Unreadable row (F 8)</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
@@ -33662,14 +33742,14 @@
       </c>
       <c r="S465" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-461</t>
+          <t xml:space="preserve">v-459</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="E466" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 2)</t>
+          <t xml:space="preserve">Unreadable row (F 9)</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
@@ -33704,14 +33784,14 @@
       </c>
       <c r="S466" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-462</t>
+          <t xml:space="preserve">v-460</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="E467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 3)</t>
+          <t xml:space="preserve">Unreadable row (G 1)</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
@@ -33746,14 +33826,14 @@
       </c>
       <c r="S467" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-463</t>
+          <t xml:space="preserve">v-461</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="E468" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 4)</t>
+          <t xml:space="preserve">Unreadable row (G 2)</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -33788,14 +33868,14 @@
       </c>
       <c r="S468" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-464</t>
+          <t xml:space="preserve">v-462</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="E469" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 5)</t>
+          <t xml:space="preserve">Unreadable row (G 3)</t>
         </is>
       </c>
       <c r="J469" t="inlineStr">
@@ -33830,14 +33910,14 @@
       </c>
       <c r="S469" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-465</t>
+          <t xml:space="preserve">v-463</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="E470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 6)</t>
+          <t xml:space="preserve">Unreadable row (G 4)</t>
         </is>
       </c>
       <c r="J470" t="inlineStr">
@@ -33872,14 +33952,14 @@
       </c>
       <c r="S470" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-466</t>
+          <t xml:space="preserve">v-464</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="E471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 7)</t>
+          <t xml:space="preserve">Unreadable row (G 5)</t>
         </is>
       </c>
       <c r="J471" t="inlineStr">
@@ -33914,14 +33994,14 @@
       </c>
       <c r="S471" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-467</t>
+          <t xml:space="preserve">v-465</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="E472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 8)</t>
+          <t xml:space="preserve">Unreadable row (G 6)</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
@@ -33956,14 +34036,14 @@
       </c>
       <c r="S472" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-468</t>
+          <t xml:space="preserve">v-466</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="E473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (G 9)</t>
+          <t xml:space="preserve">Unreadable row (G 7)</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
@@ -33998,14 +34078,14 @@
       </c>
       <c r="S473" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-469</t>
+          <t xml:space="preserve">v-467</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="E474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 1)</t>
+          <t xml:space="preserve">Unreadable row (G 8)</t>
         </is>
       </c>
       <c r="J474" t="inlineStr">
@@ -34040,14 +34120,14 @@
       </c>
       <c r="S474" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-470</t>
+          <t xml:space="preserve">v-468</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="E475" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 2)</t>
+          <t xml:space="preserve">Unreadable row (G 9)</t>
         </is>
       </c>
       <c r="J475" t="inlineStr">
@@ -34082,14 +34162,14 @@
       </c>
       <c r="S475" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-471</t>
+          <t xml:space="preserve">v-469</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="E476" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 3)</t>
+          <t xml:space="preserve">Unreadable row (H 1)</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
@@ -34124,14 +34204,14 @@
       </c>
       <c r="S476" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-472</t>
+          <t xml:space="preserve">v-470</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="E477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 4)</t>
+          <t xml:space="preserve">Unreadable row (H 2)</t>
         </is>
       </c>
       <c r="J477" t="inlineStr">
@@ -34166,14 +34246,14 @@
       </c>
       <c r="S477" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-473</t>
+          <t xml:space="preserve">v-471</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="E478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 5)</t>
+          <t xml:space="preserve">Unreadable row (H 3)</t>
         </is>
       </c>
       <c r="J478" t="inlineStr">
@@ -34208,14 +34288,14 @@
       </c>
       <c r="S478" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-474</t>
+          <t xml:space="preserve">v-472</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="E479" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 6)</t>
+          <t xml:space="preserve">Unreadable row (H 4)</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
@@ -34250,14 +34330,14 @@
       </c>
       <c r="S479" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-475</t>
+          <t xml:space="preserve">v-473</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="E480" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 7)</t>
+          <t xml:space="preserve">Unreadable row (H 5)</t>
         </is>
       </c>
       <c r="J480" t="inlineStr">
@@ -34292,14 +34372,14 @@
       </c>
       <c r="S480" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-476</t>
+          <t xml:space="preserve">v-474</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="E481" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 8)</t>
+          <t xml:space="preserve">Unreadable row (H 6)</t>
         </is>
       </c>
       <c r="J481" t="inlineStr">
@@ -34334,14 +34414,14 @@
       </c>
       <c r="S481" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-477</t>
+          <t xml:space="preserve">v-475</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="E482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 9)</t>
+          <t xml:space="preserve">Unreadable row (H 7)</t>
         </is>
       </c>
       <c r="J482" t="inlineStr">
@@ -34376,14 +34456,14 @@
       </c>
       <c r="S482" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-478</t>
+          <t xml:space="preserve">v-476</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="E483" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 1)</t>
+          <t xml:space="preserve">Unreadable row (H 8)</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -34418,14 +34498,14 @@
       </c>
       <c r="S483" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-479</t>
+          <t xml:space="preserve">v-477</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="E484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 2)</t>
+          <t xml:space="preserve">Unreadable row (H 9)</t>
         </is>
       </c>
       <c r="J484" t="inlineStr">
@@ -34460,14 +34540,14 @@
       </c>
       <c r="S484" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-480</t>
+          <t xml:space="preserve">v-478</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="E485" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 3)</t>
+          <t xml:space="preserve">Unreadable row (I 1)</t>
         </is>
       </c>
       <c r="J485" t="inlineStr">
@@ -34502,14 +34582,14 @@
       </c>
       <c r="S485" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-481</t>
+          <t xml:space="preserve">v-479</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="E486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 4)</t>
+          <t xml:space="preserve">Unreadable row (I 2)</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
@@ -34544,14 +34624,14 @@
       </c>
       <c r="S486" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-482</t>
+          <t xml:space="preserve">v-480</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="E487" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 5)</t>
+          <t xml:space="preserve">Unreadable row (I 3)</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
@@ -34586,14 +34666,14 @@
       </c>
       <c r="S487" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-483</t>
+          <t xml:space="preserve">v-481</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="E488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 6)</t>
+          <t xml:space="preserve">Unreadable row (I 4)</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
@@ -34628,14 +34708,14 @@
       </c>
       <c r="S488" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-484</t>
+          <t xml:space="preserve">v-482</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="E489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 7)</t>
+          <t xml:space="preserve">Unreadable row (I 5)</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -34670,14 +34750,14 @@
       </c>
       <c r="S489" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-485</t>
+          <t xml:space="preserve">v-483</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="E490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 8)</t>
+          <t xml:space="preserve">Unreadable row (I 6)</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
@@ -34712,47 +34792,131 @@
       </c>
       <c r="S490" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-486</t>
+          <t xml:space="preserve">v-484</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="E491" t="inlineStr">
         <is>
+          <t xml:space="preserve">Unreadable row (I 7)</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-485</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="E492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unreadable row (I 8)</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yes</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-486</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="E493" t="inlineStr">
+        <is>
           <t xml:space="preserve">Unreadable row (I 9)</t>
         </is>
       </c>
-      <c r="J491" t="inlineStr">
+      <c r="J493" t="inlineStr">
         <is>
           <t xml:space="preserve">yes</t>
         </is>
       </c>
-      <c r="L491" t="inlineStr">
+      <c r="L493" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
         </is>
       </c>
-      <c r="M491" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="N491" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="O491" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="R491" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stored</t>
-        </is>
-      </c>
-      <c r="S491" t="inlineStr">
+      <c r="M493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stored</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
         <is>
           <t xml:space="preserve">v-487</t>
         </is>
@@ -35456,17 +35620,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -35481,18 +35645,18 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -35502,7 +35666,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E24">
@@ -35512,18 +35676,18 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -35533,7 +35697,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E25">
@@ -35543,13 +35707,28 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 7)</t>
+          <t xml:space="preserve">LUCX gP1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LuCap35CR</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WT</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E26">
@@ -35559,13 +35738,13 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 8)</t>
+          <t xml:space="preserve">Unreadable row (E 7)</t>
         </is>
       </c>
       <c r="E27">
@@ -35581,7 +35760,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 9)</t>
+          <t xml:space="preserve">Unreadable row (E 8)</t>
         </is>
       </c>
       <c r="E28">
@@ -35597,43 +35776,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">Unreadable row (E 9)</t>
         </is>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -35643,7 +35807,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E30">
@@ -35659,17 +35823,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-I no sort</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -35684,13 +35848,13 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-K no sort</t>
+          <t xml:space="preserve">LCC-I no sort</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -35721,7 +35885,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-R no sort</t>
+          <t xml:space="preserve">LCC-K no sort</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -35752,7 +35916,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LCC-R no sort</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -35767,7 +35931,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E34">
@@ -35777,13 +35941,13 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX (no sort)</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -35793,12 +35957,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E35">
@@ -35808,13 +35972,28 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (E 6)</t>
+          <t xml:space="preserve">LnCap Canada CASPEX (no sort)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E36">
@@ -35824,13 +36003,13 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 8)</t>
+          <t xml:space="preserve">Unreadable row (E 6)</t>
         </is>
       </c>
       <c r="E37">
@@ -35846,7 +36025,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (H 9)</t>
+          <t xml:space="preserve">Unreadable row (H 8)</t>
         </is>
       </c>
       <c r="E38">
@@ -35862,7 +36041,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unreadable row (I 8)</t>
+          <t xml:space="preserve">Unreadable row (H 9)</t>
         </is>
       </c>
       <c r="E39">
@@ -35878,38 +36057,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 TOX4 KO g2.2</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OX</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">g2.2</t>
+          <t xml:space="preserve">Unreadable row (I 8)</t>
         </is>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR</t>
+          <t xml:space="preserve">Du145 TOX4 KO g2.2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -35919,12 +36083,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2.2</t>
         </is>
       </c>
       <c r="E41">
@@ -35940,7 +36104,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR ATF3 KO</t>
+          <t xml:space="preserve">DuDtxR</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -35950,7 +36114,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -35971,7 +36135,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR ATP7B KO</t>
+          <t xml:space="preserve">DuPar50CR ATF3 KO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -36002,7 +36166,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR MTF1 KO</t>
+          <t xml:space="preserve">DuPar50CR ATP7B KO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -36033,7 +36197,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR NT KO</t>
+          <t xml:space="preserve">DuPar50CR MTF1 KO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -36064,7 +36228,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR TOX4 KO g1.2</t>
+          <t xml:space="preserve">DuPar50CR NT KO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -36074,12 +36238,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E46">
@@ -36095,7 +36259,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR TOX4 KO g2.2</t>
+          <t xml:space="preserve">DuPar50CR TOX4 KO g1.2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -36110,7 +36274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2.2</t>
+          <t xml:space="preserve">g1.2</t>
         </is>
       </c>
       <c r="E47">
@@ -36126,22 +36290,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">DuPar50CR TOX4 KO g2.2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2.2</t>
         </is>
       </c>
       <c r="E48">
@@ -36151,7 +36315,7 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -40663,10 +40827,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J6">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20879,9 +20879,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20397,9 +20397,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -20474,9 +20474,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -24554,9 +24554,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -26517,14 +26517,14 @@
           <t xml:space="preserve">unknown</t>
         </is>
       </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
+        </is>
+      </c>
       <c r="I321" t="inlineStr">
         <is>
           <t xml:space="preserve">caNT read</t>
-        </is>
-      </c>
-      <c r="J321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -28095,9 +28095,9 @@
           <t xml:space="preserve">absolute</t>
         </is>
       </c>
-      <c r="J340" t="inlineStr">
-        <is>
-          <t xml:space="preserve">yes</t>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -201,7 +201,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -283,7 +283,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -365,7 +365,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -21793,7 +21793,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -22449,7 +22449,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -23177,7 +23177,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -23505,7 +23505,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -23669,7 +23669,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -25468,7 +25468,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -28681,7 +28681,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -29419,7 +29419,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -29665,7 +29665,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -3039,7 +3039,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -23023,7 +23023,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -27528,7 +27528,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
@@ -27620,7 +27620,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -201,7 +201,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -283,7 +283,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -365,7 +365,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -447,7 +447,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5365,7 +5365,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5621,7 +5621,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -9495,7 +9495,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -9987,7 +9987,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O143" t="inlineStr">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O145" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O146" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -12375,7 +12375,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -12457,7 +12457,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
@@ -15352,7 +15352,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
@@ -17196,7 +17196,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O208" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
@@ -18026,7 +18026,7 @@
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O217" t="inlineStr">
@@ -18118,7 +18118,7 @@
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O218" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -21793,7 +21793,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -22367,7 +22367,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -22449,7 +22449,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -22613,7 +22613,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -22695,7 +22695,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -22777,7 +22777,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -23023,7 +23023,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O278" t="inlineStr">
@@ -23095,7 +23095,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -23177,7 +23177,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -23259,7 +23259,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -23341,7 +23341,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -23505,7 +23505,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -23669,7 +23669,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -25304,7 +25304,7 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -25386,7 +25386,7 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -25468,7 +25468,7 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -27528,7 +27528,7 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
@@ -27620,7 +27620,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -27712,7 +27712,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -27794,7 +27794,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -28681,7 +28681,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -29091,7 +29091,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -29173,7 +29173,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -29337,7 +29337,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -29419,7 +29419,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -29665,7 +29665,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20943,7 +20943,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek gnt</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -21025,7 +21025,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek gnt</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -21070,7 +21070,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -19892,7 +19892,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ko rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -31043,7 +31043,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX Single</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -31053,7 +31053,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -31074,7 +31074,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK CASPEX Single</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -31084,12 +31084,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E45">
@@ -31105,7 +31105,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -31115,12 +31115,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E46">
@@ -31136,7 +31136,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh2</t>
+          <t xml:space="preserve">HEK E2F1 sh1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -31167,7 +31167,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g1</t>
+          <t xml:space="preserve">HEK E2F1 sh2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -31177,12 +31177,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E48">
@@ -31198,7 +31198,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g2</t>
+          <t xml:space="preserve">HEK FOXA1 KO g1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -31213,7 +31213,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E49">
@@ -31229,7 +31229,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 OX</t>
+          <t xml:space="preserve">HEK FOXA1 KO g2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -31244,7 +31244,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E50">
@@ -31260,7 +31260,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 OX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -31270,12 +31270,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E51">
@@ -31285,13 +31285,13 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -31306,7 +31306,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E52">
@@ -31316,13 +31316,13 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -31353,7 +31353,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -31363,12 +31363,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E54">
@@ -31378,28 +31378,28 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E55">
@@ -31409,13 +31409,13 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -31425,7 +31425,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -31446,7 +31446,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -31456,7 +31456,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -31477,17 +31477,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -31502,13 +31502,13 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17%</t>
+          <t xml:space="preserve">LCC-V</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -31539,12 +31539,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LCC-V 99.17%</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -31554,7 +31554,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E60">
@@ -31564,18 +31564,18 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -31585,7 +31585,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E61">
@@ -31601,7 +31601,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -31611,7 +31611,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -31632,7 +31632,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -31642,7 +31642,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -31663,7 +31663,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -31673,7 +31673,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -31688,13 +31688,13 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -31719,13 +31719,13 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -31750,13 +31750,13 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -31781,23 +31781,23 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ko rep2</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -19974,7 +19974,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ko rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20056,7 +20056,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek 3xflag</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20138,7 +20138,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek 3xflag</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20220,7 +20220,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -31074,7 +31074,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX Single</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -31084,7 +31084,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -31105,7 +31105,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK CASPEX Single</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -31115,12 +31115,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E46">
@@ -31136,7 +31136,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -31146,12 +31146,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E47">
@@ -31167,7 +31167,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh2</t>
+          <t xml:space="preserve">HEK E2F1 sh1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -31198,7 +31198,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g1</t>
+          <t xml:space="preserve">HEK E2F1 sh2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -31208,12 +31208,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E49">
@@ -31229,7 +31229,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g2</t>
+          <t xml:space="preserve">HEK FOXA1 KO g1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -31244,7 +31244,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E50">
@@ -31260,7 +31260,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 OX</t>
+          <t xml:space="preserve">HEK FOXA1 KO g2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -31275,7 +31275,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E51">
@@ -31291,7 +31291,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK HOXB6 OX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -31301,12 +31301,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E52">
@@ -31316,13 +31316,13 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -31337,7 +31337,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E53">
@@ -31347,13 +31347,13 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -31384,7 +31384,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -31394,12 +31394,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E55">
@@ -31409,28 +31409,28 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E56">
@@ -31440,13 +31440,13 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -31456,7 +31456,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -31477,7 +31477,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -31487,7 +31487,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -31508,17 +31508,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -31533,13 +31533,13 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17%</t>
+          <t xml:space="preserve">LCC-V</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -31570,12 +31570,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LCC-V 99.17%</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -31585,7 +31585,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E61">
@@ -31595,18 +31595,18 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -31616,7 +31616,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E62">
@@ -31632,7 +31632,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -31642,7 +31642,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -31663,7 +31663,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -31673,7 +31673,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -31694,7 +31694,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -31704,7 +31704,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -31719,13 +31719,13 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -31750,13 +31750,13 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -31781,13 +31781,13 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -31812,23 +31812,23 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20302,7 +20302,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20302,7 +20302,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -28087,12 +28087,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p45769</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -29558,7 +29558,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p218</t>
+          <t xml:space="preserve">P218</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -34439,6 +34439,302 @@
         <v>81</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>9</v>
+      </c>
+      <c r="H8">
+        <v>81</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+      <c r="H9">
+        <v>81</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box3</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+      <c r="G10">
+        <v>9</v>
+      </c>
+      <c r="H10">
+        <v>81</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box4</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>9</v>
+      </c>
+      <c r="G11">
+        <v>9</v>
+      </c>
+      <c r="H11">
+        <v>81</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F12">
+        <v>9</v>
+      </c>
+      <c r="G12">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>81</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-80 Box6</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F13">
+        <v>9</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
+      </c>
+      <c r="H13">
+        <v>81</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LiqNitro 1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F14">
+        <v>9</v>
+      </c>
+      <c r="G14">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <v>81</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LiqNitro 2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>9</v>
+      </c>
+      <c r="G15">
+        <v>9</v>
+      </c>
+      <c r="H15">
+        <v>81</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -4356,7 +4356,7 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -34860,6 +34860,117 @@
         <v>81</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Hücre Box 1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F16">
+        <v>9</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="H16">
+        <v>81</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Sıvı Azot Box 1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F17">
+        <v>9</v>
+      </c>
+      <c r="G17">
+        <v>9</v>
+      </c>
+      <c r="H17">
+        <v>81</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not placed yet</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Beyza Caa Hücre Box 2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grid</t>
+        </is>
+      </c>
+      <c r="F18">
+        <v>9</v>
+      </c>
+      <c r="G18">
+        <v>9</v>
+      </c>
+      <c r="H18">
+        <v>81</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -19887,7 +19887,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -19947,7 +19947,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-mtrdxsum-1</t>
         </is>
       </c>
     </row>
@@ -19969,12 +19969,12 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -20004,7 +20004,7 @@
       </c>
       <c r="L241" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M241" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-1</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
@@ -20051,7 +20051,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdyhss-1</t>
         </is>
       </c>
     </row>
@@ -20133,17 +20133,17 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -20168,7 +20168,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-1</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
@@ -20215,12 +20215,12 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -20275,7 +20275,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-1</t>
         </is>
       </c>
     </row>
@@ -20297,17 +20297,17 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -20317,12 +20317,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -20332,7 +20327,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -20357,7 +20352,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-1</t>
+          <t xml:space="preserve">v-335</t>
         </is>
       </c>
     </row>
@@ -20379,7 +20374,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20434,7 +20429,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-335</t>
+          <t xml:space="preserve">v-336</t>
         </is>
       </c>
     </row>
@@ -20456,7 +20451,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20466,7 +20461,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -20476,7 +20471,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-11-27</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27-11-25</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-336</t>
+          <t xml:space="preserve">v-337</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -20553,12 +20553,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-11-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-337</t>
+          <t xml:space="preserve">v-338</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -20635,12 +20635,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-338</t>
+          <t xml:space="preserve">v-339</t>
         </is>
       </c>
     </row>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -20717,12 +20717,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-339</t>
+          <t xml:space="preserve">v-340</t>
         </is>
       </c>
     </row>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -20789,7 +20789,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -20799,12 +20799,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -20839,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-340</t>
+          <t xml:space="preserve">v-341</t>
         </is>
       </c>
     </row>
@@ -20861,34 +20856,39 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p21</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -20906,7 +20906,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-341</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-mtrdx0po-1</t>
         </is>
       </c>
     </row>
@@ -21020,17 +21020,17 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -21040,17 +21040,17 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -21070,7 +21070,7 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-1</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -21358,7 +21358,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -21368,12 +21368,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -21430,39 +21430,39 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21470,17 +21470,17 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -21512,32 +21512,32 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -21552,17 +21552,17 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -21676,39 +21676,39 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21716,17 +21716,17 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -21758,17 +21758,17 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -21778,17 +21778,17 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -21798,17 +21798,17 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -21850,7 +21850,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -21860,12 +21860,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21922,42 +21922,42 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p17</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p15</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
@@ -22004,7 +22004,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre0w3q-1</t>
         </is>
       </c>
     </row>
@@ -22086,17 +22086,17 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -22121,7 +22121,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-1</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre1ko0-1</t>
         </is>
       </c>
     </row>
@@ -22250,57 +22250,57 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-1</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -22332,32 +22332,32 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -22414,12 +22414,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -22496,32 +22496,32 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -22598,12 +22598,12 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -22720,7 +22720,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -22742,37 +22742,32 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -22782,12 +22777,12 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
@@ -22802,7 +22797,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22824,12 +22819,12 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -22869,7 +22864,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22879,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22901,17 +22896,17 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -22921,12 +22916,17 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-07-26</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -22941,12 +22941,12 @@
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22973,22 +22973,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -22998,17 +22998,17 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -23018,7 +23018,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -23142,32 +23142,32 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23224,22 +23224,22 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23306,7 +23306,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23388,17 +23388,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -23408,12 +23408,12 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23470,17 +23470,17 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23552,22 +23552,22 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23634,32 +23634,32 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -23684,7 +23684,7 @@
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23716,57 +23716,57 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23880,12 +23880,12 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -23915,7 +23915,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23962,7 +23962,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -24044,17 +24044,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -24064,12 +24064,12 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -24126,17 +24126,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24208,17 +24208,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24228,12 +24228,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24290,12 +24290,12 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24372,12 +24372,12 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24422,7 +24422,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24432,7 +24432,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24454,17 +24454,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24474,12 +24474,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24489,7 +24484,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -24504,7 +24499,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24514,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24536,7 +24531,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -24546,7 +24541,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -24556,7 +24551,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24613,39 +24613,39 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK APEX1 g1</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -24663,7 +24663,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24695,17 +24695,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24715,12 +24715,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24777,17 +24777,17 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24859,12 +24859,12 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24941,12 +24941,12 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -25023,32 +25023,32 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -25105,22 +25105,22 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -25140,7 +25140,7 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25187,57 +25187,57 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25269,22 +25269,22 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25351,22 +25351,22 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25433,22 +25433,22 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -25473,17 +25473,17 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25515,7 +25515,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25597,39 +25597,39 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -25637,17 +25637,17 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25679,22 +25679,22 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25761,32 +25761,32 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25843,32 +25843,32 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25925,17 +25925,17 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
@@ -25945,37 +25945,37 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -26007,12 +26007,12 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -26089,12 +26089,12 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26171,12 +26171,12 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -26206,7 +26206,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26253,32 +26253,32 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26335,22 +26335,22 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26417,32 +26417,32 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26499,32 +26499,32 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26581,17 +26581,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -26601,12 +26601,12 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26663,17 +26663,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26683,22 +26683,22 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26745,7 +26745,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26909,7 +26909,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26991,17 +26991,17 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -27073,22 +27073,22 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -27155,17 +27155,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27175,12 +27175,12 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27237,7 +27237,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -27247,7 +27247,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27257,12 +27257,12 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27319,32 +27319,32 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27354,7 +27354,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -27369,7 +27369,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27401,37 +27401,37 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -27446,12 +27446,22 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27461,7 +27471,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27483,7 +27493,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -27553,7 +27563,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27575,17 +27585,17 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27595,12 +27605,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27625,17 +27635,7 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27667,7 +27667,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -27677,7 +27677,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -27687,12 +27687,12 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27749,32 +27749,32 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27794,12 +27794,12 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27831,12 +27831,12 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27913,12 +27913,12 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27995,32 +27995,27 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I339" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28040,7 +28035,7 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
@@ -28055,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -28077,12 +28072,12 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -28097,7 +28092,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-22</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -28154,42 +28154,42 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -28199,12 +28199,12 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28236,17 +28236,17 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -28256,12 +28256,12 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28318,17 +28318,17 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -28338,12 +28338,12 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28400,17 +28400,17 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -28450,7 +28450,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28482,7 +28482,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28564,32 +28564,32 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28609,12 +28609,12 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28646,32 +28646,32 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -28681,7 +28681,7 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
@@ -28691,12 +28691,12 @@
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28728,17 +28728,17 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -28748,12 +28748,12 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -28778,7 +28778,7 @@
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28810,17 +28810,17 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -28830,12 +28830,12 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28892,57 +28892,57 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O350" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -28984,7 +28984,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
@@ -28994,12 +28994,12 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29220,7 +29220,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29302,7 +29302,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29384,32 +29384,32 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
@@ -29424,17 +29424,17 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -29466,39 +29466,39 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -29506,7 +29506,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CisR</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -29526,7 +29526,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
@@ -29548,17 +29548,17 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p8</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -29588,17 +29588,17 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
@@ -29608,39 +29608,19 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I9</t>
-        </is>
-      </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -29650,47 +29630,47 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O359" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R359" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
@@ -31105,7 +31085,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -31115,7 +31095,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -31136,7 +31116,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK CASPEX Single</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -31146,7 +31126,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -31167,7 +31147,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX Single</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -31177,12 +31157,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E46">
@@ -31198,7 +31178,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK E2F1 sh1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -31208,12 +31188,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E47">
@@ -31229,7 +31209,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh1</t>
+          <t xml:space="preserve">HEK E2F1 sh2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -31260,7 +31240,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh2</t>
+          <t xml:space="preserve">HEK FOXA1 KO g1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -31270,12 +31250,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E49">
@@ -31291,7 +31271,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g1</t>
+          <t xml:space="preserve">HEK FOXA1 KO g2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -31306,7 +31286,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E50">
@@ -31322,7 +31302,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 OX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -31337,7 +31317,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E51">
@@ -31353,7 +31333,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 OX</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -31363,12 +31343,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E52">
@@ -31378,13 +31358,13 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -31399,7 +31379,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E53">
@@ -31409,13 +31389,13 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -31446,7 +31426,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -31456,12 +31436,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E55">
@@ -31471,28 +31451,28 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E56">
@@ -31502,13 +31482,13 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -31518,7 +31498,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -31539,7 +31519,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -31549,7 +31529,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -31570,17 +31550,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">LCC-V</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -31595,13 +31575,13 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V</t>
+          <t xml:space="preserve">LCC-V 99.17%</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -31632,12 +31612,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17%</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -31647,7 +31627,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E61">
@@ -31657,18 +31637,18 @@
         <v>0</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -31678,7 +31658,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E62">
@@ -31694,7 +31674,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -31704,7 +31684,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -31725,7 +31705,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -31735,7 +31715,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -31756,7 +31736,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -31766,7 +31746,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -31781,13 +31761,13 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -31812,13 +31792,13 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -31843,13 +31823,13 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -31874,23 +31854,23 @@
         <v>0</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -31899,7 +31879,7 @@
         </is>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -31911,7 +31891,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -31921,7 +31901,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -31942,7 +31922,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31952,12 +31932,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E71">
@@ -31973,22 +31953,22 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E72">
@@ -32004,7 +31984,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32014,12 +31994,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E73">
@@ -32035,7 +32015,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32045,12 +32025,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E74">
@@ -32066,7 +32046,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32076,12 +32056,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E75">
@@ -32097,7 +32077,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -32119,7 +32099,7 @@
         <v>1</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -34283,6 +34263,53 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -34521,10 +34548,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J6">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -19969,7 +19969,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdyhss-1</t>
         </is>
       </c>
     </row>
@@ -20051,17 +20051,17 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-1</t>
+          <t xml:space="preserve">v-mtrdz1vx-1</t>
         </is>
       </c>
     </row>
@@ -20133,17 +20133,17 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -20153,12 +20153,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -20168,7 +20163,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -20193,7 +20188,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-335</t>
         </is>
       </c>
     </row>
@@ -20215,17 +20210,17 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -20235,12 +20230,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -20250,7 +20240,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -20275,7 +20265,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-1</t>
+          <t xml:space="preserve">v-336</t>
         </is>
       </c>
     </row>
@@ -20297,7 +20287,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -20307,7 +20297,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -20317,7 +20307,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-11-27</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27-11-25</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -20352,7 +20347,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-335</t>
+          <t xml:space="preserve">v-337</t>
         </is>
       </c>
     </row>
@@ -20374,7 +20369,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20384,7 +20379,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -20394,7 +20389,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-11-06</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-336</t>
+          <t xml:space="preserve">v-338</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -20471,12 +20471,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-27</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-11-25</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-337</t>
+          <t xml:space="preserve">v-339</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-338</t>
+          <t xml:space="preserve">v-340</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -20635,12 +20635,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -20675,7 +20670,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-339</t>
+          <t xml:space="preserve">v-341</t>
         </is>
       </c>
     </row>
@@ -20697,39 +20692,39 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p21</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p16</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-06</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6/11/2025</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -20747,7 +20742,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -20757,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-340</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
@@ -20779,34 +20774,39 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p21</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -20824,7 +20824,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-341</t>
+          <t xml:space="preserve">v-mtrdx0po-1</t>
         </is>
       </c>
     </row>
@@ -20856,17 +20856,17 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -20876,17 +20876,17 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20938,17 +20938,17 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -20958,17 +20958,17 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-1</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -21194,7 +21194,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -21204,12 +21204,12 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -21266,39 +21266,39 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p10</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-12</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21306,17 +21306,17 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -21430,32 +21430,32 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -21470,17 +21470,17 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -21512,39 +21512,39 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21552,17 +21552,17 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -21594,17 +21594,17 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -21614,17 +21614,17 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-17</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-12-25</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21676,12 +21676,12 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -21696,17 +21696,17 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -21716,17 +21716,17 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21758,42 +21758,42 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p17</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p51</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-10</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/11/2025</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
@@ -21840,42 +21840,42 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p17</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p15</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-mtre0w3q-1</t>
         </is>
       </c>
     </row>
@@ -21922,17 +21922,17 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -21957,7 +21957,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
@@ -22004,17 +22004,17 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-1</t>
+          <t xml:space="preserve">v-mtre1ko0-1</t>
         </is>
       </c>
     </row>
@@ -22086,57 +22086,57 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -22168,17 +22168,17 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -22188,37 +22188,37 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-1</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -22250,32 +22250,32 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -22332,32 +22332,32 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -22414,32 +22414,32 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -22516,12 +22516,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -22578,37 +22578,32 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -22618,12 +22613,12 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
@@ -22638,7 +22633,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22660,37 +22655,32 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -22700,17 +22690,17 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22720,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22742,17 +22732,17 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -22762,12 +22752,17 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-07-26</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -22782,12 +22777,12 @@
       </c>
       <c r="N275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22797,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22814,22 +22809,22 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -22839,12 +22834,17 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-12-25</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -22854,17 +22854,17 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -22891,22 +22891,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -22916,17 +22916,17 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -22978,32 +22978,32 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23060,32 +23060,32 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23142,22 +23142,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23224,17 +23224,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -23244,12 +23244,12 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23306,17 +23306,17 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -23326,12 +23326,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23388,22 +23388,22 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23470,12 +23470,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -23490,12 +23490,12 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23552,17 +23552,17 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
@@ -23572,37 +23572,37 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23634,57 +23634,57 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23716,12 +23716,12 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23798,12 +23798,12 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -23880,17 +23880,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -23900,12 +23900,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -23962,17 +23962,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23982,12 +23982,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24044,12 +24044,12 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24126,17 +24126,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24208,12 +24208,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24290,17 +24290,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24310,12 +24310,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24325,7 +24320,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -24340,7 +24335,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24350,7 +24345,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24372,12 +24367,12 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -24407,7 +24402,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -24422,7 +24417,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24432,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24454,34 +24449,39 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK APEX1 g1</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -24499,7 +24499,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24531,42 +24531,42 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p28</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-05</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/1/2026</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24613,17 +24613,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24695,17 +24695,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24715,12 +24715,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24777,12 +24777,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -24859,32 +24859,32 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -24941,17 +24941,17 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -24961,12 +24961,12 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25023,17 +25023,17 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -25043,37 +25043,37 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25105,17 +25105,17 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -25125,37 +25125,37 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25187,17 +25187,17 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25269,17 +25269,17 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
@@ -25309,17 +25309,17 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25351,22 +25351,22 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -25391,17 +25391,17 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25433,39 +25433,39 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -25473,17 +25473,17 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25515,39 +25515,39 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p14</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -25555,17 +25555,17 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25597,17 +25597,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25617,12 +25617,12 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25699,12 +25699,12 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25761,57 +25761,57 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -25843,17 +25843,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25863,37 +25863,37 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -25925,12 +25925,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26007,12 +26007,12 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26089,32 +26089,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26171,17 +26171,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26191,12 +26191,12 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26253,32 +26253,32 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26417,32 +26417,32 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26519,22 +26519,22 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26581,17 +26581,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -26601,22 +26601,22 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26663,17 +26663,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26698,7 +26698,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26745,17 +26745,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26909,22 +26909,22 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26991,32 +26991,32 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27073,12 +27073,12 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -27093,12 +27093,12 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27155,32 +27155,32 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27190,7 +27190,7 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -27205,7 +27205,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27237,17 +27237,17 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27257,22 +27257,22 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27282,12 +27282,22 @@
       </c>
       <c r="N330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27307,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27319,37 +27329,37 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -27364,12 +27374,22 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27399,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27401,17 +27421,17 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27421,12 +27441,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27451,17 +27471,7 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P332" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q332" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27471,7 +27481,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27493,12 +27503,12 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -27543,17 +27553,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27585,32 +27585,32 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27630,12 +27630,12 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R334" t="inlineStr">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27667,32 +27667,32 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27712,12 +27712,12 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27749,12 +27749,12 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27831,32 +27831,27 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I337" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27876,7 +27871,7 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
@@ -27891,7 +27886,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27913,32 +27908,32 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27958,7 +27953,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -27973,7 +27968,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27995,37 +27990,42 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2026-04-10</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -28035,12 +28035,12 @@
       </c>
       <c r="N339" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28072,42 +28072,42 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28117,12 +28117,12 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28154,7 +28154,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28236,12 +28236,12 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -28256,12 +28256,12 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -28286,7 +28286,7 @@
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28318,17 +28318,17 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -28353,7 +28353,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28400,32 +28400,32 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28445,12 +28445,12 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28482,12 +28482,12 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -28502,12 +28502,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28517,7 +28517,7 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -28532,7 +28532,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28564,32 +28564,32 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28599,7 +28599,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -28609,12 +28609,12 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28646,17 +28646,17 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28728,57 +28728,57 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28810,57 +28810,57 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -28912,12 +28912,12 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29220,32 +29220,32 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -29260,17 +29260,17 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -29302,32 +29302,32 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuPar50CR+1</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">P218</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -29342,17 +29342,17 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CisR</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
@@ -29384,39 +29384,39 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p8</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -29424,17 +29424,17 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -29444,39 +29444,19 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I8</t>
-        </is>
-      </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -29486,27 +29466,27 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -29521,44 +29501,24 @@
       </c>
       <c r="R357" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I9</t>
-        </is>
-      </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -29568,59 +29528,59 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -29645,7 +29605,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -29670,7 +29630,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
@@ -30434,17 +30394,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -30459,18 +30419,18 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -30480,7 +30440,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E24">
@@ -30490,18 +30450,18 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LUCX gP1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -30511,7 +30471,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E25">
@@ -30521,38 +30481,38 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -31085,7 +31045,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK CASPEX Single</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -31095,7 +31055,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -31116,7 +31076,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX Single</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -31126,12 +31086,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E45">
@@ -31147,7 +31107,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK E2F1 sh1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -31157,12 +31117,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E46">
@@ -31178,7 +31138,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh1</t>
+          <t xml:space="preserve">HEK E2F1 sh2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -31209,7 +31169,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh2</t>
+          <t xml:space="preserve">HEK FOXA1 KO g1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -31219,12 +31179,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E48">
@@ -31240,7 +31200,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g1</t>
+          <t xml:space="preserve">HEK FOXA1 KO g2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -31255,7 +31215,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E49">
@@ -31271,7 +31231,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 OX</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -31286,7 +31246,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E50">
@@ -31302,7 +31262,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 OX</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -31312,12 +31272,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E51">
@@ -31327,13 +31287,13 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -31348,7 +31308,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E52">
@@ -31358,13 +31318,13 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -31395,7 +31355,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -31405,12 +31365,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E54">
@@ -31420,28 +31380,28 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E55">
@@ -31451,13 +31411,13 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -31467,7 +31427,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -31488,7 +31448,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -31498,7 +31458,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -31519,17 +31479,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">LCC-V</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -31544,13 +31504,13 @@
         <v>0</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V</t>
+          <t xml:space="preserve">LCC-V 99.17%</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -31581,12 +31541,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17%</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -31596,7 +31556,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E60">
@@ -31606,18 +31566,18 @@
         <v>0</v>
       </c>
       <c r="G60">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -31627,7 +31587,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E61">
@@ -31643,7 +31603,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -31653,7 +31613,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -31674,7 +31634,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -31684,7 +31644,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -31705,7 +31665,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -31715,7 +31675,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -31730,13 +31690,13 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -31761,13 +31721,13 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -31792,13 +31752,13 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -31823,23 +31783,23 @@
         <v>0</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -31848,7 +31808,7 @@
         </is>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -31860,7 +31820,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -31870,7 +31830,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -31891,7 +31851,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -31901,12 +31861,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E70">
@@ -31922,22 +31882,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E71">
@@ -31953,7 +31913,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31963,12 +31923,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E72">
@@ -31984,7 +31944,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -31994,12 +31954,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E73">
@@ -32015,7 +31975,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32025,12 +31985,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E74">
@@ -32046,7 +32006,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32068,7 +32028,7 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -32077,7 +32037,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -32099,7 +32059,7 @@
         <v>1</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -32108,7 +32068,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -32118,7 +32078,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -32139,7 +32099,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -32170,7 +32130,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -32192,7 +32152,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -34310,6 +34270,100 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 3xFLAG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A8</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -34548,10 +34602,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="J6">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20692,7 +20692,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-mtrdx0po-1</t>
         </is>
       </c>
     </row>
@@ -20774,17 +20774,17 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -20794,17 +20794,17 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-1</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -21122,12 +21122,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -21184,39 +21184,39 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21224,17 +21224,17 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -21266,32 +21266,32 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -21306,17 +21306,17 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O257" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -21430,39 +21430,39 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21470,17 +21470,17 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -21512,17 +21512,17 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -21532,17 +21532,17 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -21552,17 +21552,17 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O260" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -21604,7 +21604,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -21614,12 +21614,12 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21676,42 +21676,42 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p17</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p15</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre0w3q-1</t>
         </is>
       </c>
     </row>
@@ -21840,17 +21840,17 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-1</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre1ko0-1</t>
         </is>
       </c>
     </row>
@@ -22004,57 +22004,57 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-1</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -22086,32 +22086,32 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -22168,12 +22168,12 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -22250,32 +22250,32 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -22352,12 +22352,12 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -22496,37 +22496,32 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -22536,12 +22531,12 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
@@ -22556,7 +22551,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22578,12 +22573,12 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -22623,7 +22618,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22633,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22655,17 +22650,17 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -22675,12 +22670,17 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-07-26</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -22695,12 +22695,12 @@
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22727,22 +22727,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -22752,17 +22752,17 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -22772,7 +22772,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -22814,7 +22814,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -22896,32 +22896,32 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22978,22 +22978,22 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23142,17 +23142,17 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -23162,12 +23162,12 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23224,17 +23224,17 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23306,22 +23306,22 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23388,32 +23388,32 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23470,57 +23470,57 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23552,7 +23552,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23634,12 +23634,12 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -23669,7 +23669,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23716,7 +23716,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -23798,17 +23798,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -23818,12 +23818,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -23880,17 +23880,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -23900,12 +23900,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -23962,17 +23962,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23982,12 +23982,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24044,12 +24044,12 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24126,12 +24126,12 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24208,17 +24208,17 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24228,12 +24228,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24243,7 +24238,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -24258,7 +24253,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24268,7 +24263,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24290,7 +24285,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -24300,7 +24295,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24310,7 +24305,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24367,39 +24367,39 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK APEX1 g1</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24449,17 +24449,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24469,12 +24469,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24531,17 +24531,17 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -24551,12 +24551,12 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24613,12 +24613,12 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24695,12 +24695,12 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -24777,32 +24777,32 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -24859,22 +24859,22 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -24894,7 +24894,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -24941,57 +24941,57 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25023,22 +25023,22 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25105,22 +25105,22 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25187,22 +25187,22 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -25227,17 +25227,17 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25269,7 +25269,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25351,39 +25351,39 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -25391,17 +25391,17 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25433,22 +25433,22 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25515,32 +25515,32 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25597,32 +25597,32 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25679,17 +25679,17 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -25699,37 +25699,37 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -25761,12 +25761,12 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -25843,12 +25843,12 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -25925,12 +25925,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26007,32 +26007,32 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26089,22 +26089,22 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26171,32 +26171,32 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26206,7 +26206,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26253,32 +26253,32 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26355,12 +26355,12 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26417,17 +26417,17 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -26437,22 +26437,22 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26581,17 +26581,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26745,17 +26745,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26827,22 +26827,22 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26909,17 +26909,17 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -26929,12 +26929,12 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -27001,7 +27001,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -27011,12 +27011,12 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27073,32 +27073,32 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27155,37 +27155,37 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -27200,12 +27200,22 @@
       </c>
       <c r="N329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27215,7 +27225,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27237,7 +27247,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -27307,7 +27317,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27329,17 +27339,17 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -27349,12 +27359,12 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27379,17 +27389,7 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q331" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27399,7 +27399,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27421,7 +27421,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -27431,7 +27431,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -27441,12 +27441,12 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27481,7 +27481,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27503,32 +27503,32 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27548,12 +27548,12 @@
       </c>
       <c r="N333" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27585,12 +27585,12 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27667,12 +27667,12 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27749,32 +27749,27 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I336" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27794,7 +27789,7 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
@@ -27809,7 +27804,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27831,12 +27826,12 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -27851,7 +27846,12 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-22</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27908,42 +27908,42 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -27953,12 +27953,12 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R338" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -27990,17 +27990,17 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -28010,12 +28010,12 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28072,17 +28072,17 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -28092,12 +28092,12 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28154,17 +28154,17 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -28204,7 +28204,7 @@
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28236,7 +28236,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28318,32 +28318,32 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28363,12 +28363,12 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28400,32 +28400,32 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -28445,12 +28445,12 @@
       </c>
       <c r="N344" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28482,17 +28482,17 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -28502,12 +28502,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28532,7 +28532,7 @@
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28564,17 +28564,17 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -28584,12 +28584,12 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28646,57 +28646,57 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28728,7 +28728,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -28738,7 +28738,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -28748,12 +28748,12 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29138,32 +29138,32 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -29178,17 +29178,17 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -29220,39 +29220,39 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -29260,7 +29260,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CisR</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
@@ -29302,17 +29302,17 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p8</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -29342,17 +29342,17 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29362,39 +29362,19 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I9</t>
-        </is>
-      </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -29404,17 +29384,17 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -29424,27 +29404,27 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
@@ -30301,12 +30281,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -30316,7 +30296,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E20">
@@ -30326,18 +30306,18 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">DuPar50CR+1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -30347,28 +30327,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -30378,14 +30358,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E22">
         <v>4</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -34364,6 +34344,53 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -34602,10 +34629,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="J6">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -21676,7 +21676,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre0w3q-1</t>
         </is>
       </c>
     </row>
@@ -21758,17 +21758,17 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -21793,7 +21793,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-1</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
@@ -21840,7 +21840,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre1ko0-1</t>
         </is>
       </c>
     </row>
@@ -21922,57 +21922,57 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-1</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -22004,32 +22004,32 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -22086,12 +22086,12 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -22168,32 +22168,32 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -22270,12 +22270,12 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -22332,7 +22332,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -22414,37 +22414,32 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -22454,12 +22449,12 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O271" t="inlineStr">
@@ -22474,7 +22469,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22496,12 +22491,12 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -22541,7 +22536,7 @@
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -22551,7 +22546,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22573,17 +22568,17 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -22593,12 +22588,17 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-07-26</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -22613,12 +22613,12 @@
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22645,22 +22645,22 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -22670,17 +22670,17 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -22690,7 +22690,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -22700,7 +22700,7 @@
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -22732,7 +22732,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -22814,32 +22814,32 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22896,22 +22896,22 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -22978,7 +22978,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23060,17 +23060,17 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -23080,12 +23080,12 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23142,17 +23142,17 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23224,22 +23224,22 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23306,32 +23306,32 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23388,57 +23388,57 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23470,7 +23470,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23552,12 +23552,12 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23634,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -23716,17 +23716,17 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23736,12 +23736,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -23798,17 +23798,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -23818,12 +23818,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -23880,17 +23880,17 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -23900,12 +23900,12 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -23962,12 +23962,12 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24044,12 +24044,12 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24126,17 +24126,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24146,12 +24146,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I292" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24161,7 +24156,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -24176,7 +24171,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24186,7 +24181,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24208,7 +24203,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -24218,7 +24213,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -24228,7 +24223,12 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24285,39 +24285,39 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK APEX1 g1</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -24335,7 +24335,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24367,17 +24367,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -24387,12 +24387,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24449,17 +24449,17 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24469,12 +24469,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24531,12 +24531,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -24566,7 +24566,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24613,12 +24613,12 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -24695,32 +24695,32 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -24777,22 +24777,22 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -24859,57 +24859,57 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -24941,22 +24941,22 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25023,22 +25023,22 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25105,22 +25105,22 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -25145,17 +25145,17 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25187,7 +25187,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25269,39 +25269,39 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -25309,17 +25309,17 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25351,22 +25351,22 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25433,32 +25433,32 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25515,32 +25515,32 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25597,17 +25597,17 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -25617,37 +25617,37 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -25679,12 +25679,12 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -25761,12 +25761,12 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -25843,12 +25843,12 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -25925,32 +25925,32 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26007,22 +26007,22 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26089,32 +26089,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26171,32 +26171,32 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26206,7 +26206,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26253,17 +26253,17 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -26273,12 +26273,12 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26335,17 +26335,17 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -26355,22 +26355,22 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26417,7 +26417,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26534,7 +26534,7 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -26549,7 +26549,7 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26663,17 +26663,17 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -26698,7 +26698,7 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26745,22 +26745,22 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26827,17 +26827,17 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26847,12 +26847,12 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26862,7 +26862,7 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -26877,7 +26877,7 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -26909,7 +26909,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -26929,12 +26929,12 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -26991,32 +26991,32 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27073,37 +27073,37 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -27118,12 +27118,22 @@
       </c>
       <c r="N328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27143,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27155,7 +27165,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -27225,7 +27235,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27247,17 +27257,17 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27267,12 +27277,12 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27297,17 +27307,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q330" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27317,7 +27317,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27339,7 +27339,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -27359,12 +27359,12 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27399,7 +27399,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27421,32 +27421,32 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -27466,12 +27466,12 @@
       </c>
       <c r="N332" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R332" t="inlineStr">
@@ -27481,7 +27481,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27503,12 +27503,12 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27585,12 +27585,12 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27667,32 +27667,27 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I335" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27712,7 +27707,7 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
@@ -27727,7 +27722,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27749,12 +27744,12 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -27769,7 +27764,12 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-22</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27826,42 +27826,42 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -27871,12 +27871,12 @@
       </c>
       <c r="N337" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R337" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -27908,17 +27908,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -27928,12 +27928,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -27990,17 +27990,17 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -28010,12 +28010,12 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28072,17 +28072,17 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28122,7 +28122,7 @@
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28154,7 +28154,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28236,32 +28236,32 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28281,12 +28281,12 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28318,32 +28318,32 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28353,7 +28353,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -28363,12 +28363,12 @@
       </c>
       <c r="N343" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28400,17 +28400,17 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -28420,12 +28420,12 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28450,7 +28450,7 @@
       </c>
       <c r="O344" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28482,17 +28482,17 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -28502,12 +28502,12 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28564,57 +28564,57 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -28656,7 +28656,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -28666,12 +28666,12 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -28728,7 +28728,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29056,32 +29056,32 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -29096,17 +29096,17 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O352" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -29138,39 +29138,39 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -29178,7 +29178,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CisR</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
@@ -29220,17 +29220,17 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p8</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -29260,17 +29260,17 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
@@ -29280,39 +29280,19 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I9</t>
-        </is>
-      </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -29322,17 +29302,17 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -29342,34 +29322,34 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -29399,7 +29379,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -29414,7 +29394,7 @@
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R356" t="inlineStr">
@@ -29424,14 +29404,14 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -29461,7 +29441,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -29486,19 +29466,19 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -29523,7 +29503,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -29548,19 +29528,19 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -29580,12 +29560,12 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -29610,7 +29590,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
@@ -30529,7 +30509,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -30539,7 +30519,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -30560,7 +30540,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -30570,12 +30550,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E29">
@@ -30591,12 +30571,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">LCC-I no sort</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -30606,7 +30586,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E30">
@@ -30616,13 +30596,13 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-I no sort</t>
+          <t xml:space="preserve">LCC-K no sort</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -30653,7 +30633,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-K no sort</t>
+          <t xml:space="preserve">LCC-R no sort</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -30684,7 +30664,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-R no sort</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -30699,7 +30679,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E33">
@@ -30709,13 +30689,13 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LnCap Canada CASPEX (no sort)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -30725,12 +30705,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E34">
@@ -30740,32 +30720,32 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX (no sort)</t>
+          <t xml:space="preserve">Du145 TOX4 KO g2.2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2.2</t>
         </is>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -30777,7 +30757,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 TOX4 KO g2.2</t>
+          <t xml:space="preserve">DuDtxR</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -30787,12 +30767,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E36">
@@ -30808,7 +30788,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR</t>
+          <t xml:space="preserve">DuPar50CR ATF3 KO</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -30818,7 +30798,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -30839,7 +30819,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR ATF3 KO</t>
+          <t xml:space="preserve">DuPar50CR ATP7B KO</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -30870,7 +30850,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR ATP7B KO</t>
+          <t xml:space="preserve">DuPar50CR MTF1 KO</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -30901,7 +30881,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR MTF1 KO</t>
+          <t xml:space="preserve">DuPar50CR NT KO</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -30932,7 +30912,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR NT KO</t>
+          <t xml:space="preserve">DuPar50CR TOX4 KO g1.2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -30942,12 +30922,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.2</t>
         </is>
       </c>
       <c r="E41">
@@ -30963,7 +30943,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR TOX4 KO g1.2</t>
+          <t xml:space="preserve">DuPar50CR TOX4 KO g2.2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -30978,7 +30958,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.2</t>
+          <t xml:space="preserve">g2.2</t>
         </is>
       </c>
       <c r="E42">
@@ -30994,22 +30974,22 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR TOX4 KO g2.2</t>
+          <t xml:space="preserve">HEK CASPEX Single</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E43">
@@ -31025,7 +31005,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX Single</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -31035,12 +31015,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E44">
@@ -31056,7 +31036,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK E2F1 sh1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -31066,12 +31046,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E45">
@@ -31087,7 +31067,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh1</t>
+          <t xml:space="preserve">HEK E2F1 sh2</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -31118,7 +31098,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh2</t>
+          <t xml:space="preserve">HEK FOXA1 KO g1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -31128,12 +31108,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E47">
@@ -31149,7 +31129,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g1</t>
+          <t xml:space="preserve">HEK FOXA1 KO g2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -31164,7 +31144,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E48">
@@ -31180,7 +31160,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 OX</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -31195,7 +31175,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E49">
@@ -31211,7 +31191,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 OX</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -31221,12 +31201,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E50">
@@ -31236,13 +31216,13 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -31257,7 +31237,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E51">
@@ -31267,13 +31247,13 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -31304,7 +31284,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -31314,12 +31294,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E53">
@@ -31329,35 +31309,35 @@
         <v>0</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E54">
         <v>2</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54">
         <v>2</v>
@@ -34391,6 +34371,53 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -34629,10 +34656,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J6">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -21758,7 +21758,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre1ko0-1</t>
         </is>
       </c>
     </row>
@@ -21840,57 +21840,57 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-1</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -21922,32 +21922,32 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -21972,7 +21972,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -22004,12 +22004,12 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -22054,7 +22054,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -22086,32 +22086,32 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -22168,7 +22168,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -22188,12 +22188,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -22332,37 +22332,32 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -22372,12 +22367,12 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O270" t="inlineStr">
@@ -22392,7 +22387,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22414,12 +22409,12 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -22459,7 +22454,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22469,7 +22464,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22491,17 +22486,17 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -22511,12 +22506,17 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-07-26</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -22531,12 +22531,12 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O272" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
@@ -22546,7 +22546,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22563,22 +22563,22 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -22588,17 +22588,17 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -22608,7 +22608,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="O273" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
@@ -22628,7 +22628,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -22650,7 +22650,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -22710,7 +22710,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -22732,32 +22732,32 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -22782,7 +22782,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -22814,22 +22814,22 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -22896,7 +22896,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -22978,17 +22978,17 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -22998,12 +22998,12 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="O278" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23060,17 +23060,17 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23142,22 +23142,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23224,32 +23224,32 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -23274,7 +23274,7 @@
       </c>
       <c r="O281" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23306,57 +23306,57 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23388,7 +23388,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23470,12 +23470,12 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -23505,7 +23505,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23552,7 +23552,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -23634,17 +23634,17 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -23654,12 +23654,12 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -23716,17 +23716,17 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -23736,12 +23736,12 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="O287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -23798,17 +23798,17 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -23818,12 +23818,12 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -23848,7 +23848,7 @@
       </c>
       <c r="O288" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -23880,12 +23880,12 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="O289" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -23962,12 +23962,12 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -24012,7 +24012,7 @@
       </c>
       <c r="O290" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24044,17 +24044,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -24064,12 +24064,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -24079,7 +24074,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -24094,7 +24089,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24104,7 +24099,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24126,7 +24121,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -24136,7 +24131,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24146,7 +24141,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24181,7 +24181,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24203,39 +24203,39 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK APEX1 g1</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -24253,7 +24253,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24263,7 +24263,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24285,17 +24285,17 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -24305,12 +24305,12 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -24320,7 +24320,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -24335,7 +24335,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24345,7 +24345,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24367,17 +24367,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -24387,12 +24387,12 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -24417,7 +24417,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24449,12 +24449,12 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -24484,7 +24484,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -24499,7 +24499,7 @@
       </c>
       <c r="O296" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24531,12 +24531,12 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -24613,32 +24613,32 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -24695,22 +24695,22 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -24777,57 +24777,57 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -24859,22 +24859,22 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="O301" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -24941,22 +24941,22 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25023,22 +25023,22 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -25063,17 +25063,17 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25105,7 +25105,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25187,39 +25187,39 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -25227,17 +25227,17 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25269,22 +25269,22 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25351,32 +25351,32 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25433,32 +25433,32 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25515,17 +25515,17 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -25535,37 +25535,37 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -25597,12 +25597,12 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -25632,7 +25632,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -25679,12 +25679,12 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -25714,7 +25714,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -25761,12 +25761,12 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -25796,7 +25796,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -25843,32 +25843,32 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -25878,7 +25878,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -25893,7 +25893,7 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -25925,22 +25925,22 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26007,32 +26007,32 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26089,32 +26089,32 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26171,17 +26171,17 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -26191,12 +26191,12 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26253,17 +26253,17 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -26273,22 +26273,22 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -26303,7 +26303,7 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26335,7 +26335,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26417,17 +26417,17 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26499,7 +26499,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26581,17 +26581,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26663,22 +26663,22 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -26713,7 +26713,7 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -26745,17 +26745,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26765,12 +26765,12 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -26837,7 +26837,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -26847,12 +26847,12 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -26909,32 +26909,32 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -26991,37 +26991,37 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -27036,12 +27036,22 @@
       </c>
       <c r="N327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27061,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27073,7 +27083,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -27143,7 +27153,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27165,17 +27175,17 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27185,12 +27195,12 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27215,17 +27225,7 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q329" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R329" t="inlineStr">
@@ -27235,7 +27235,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27257,7 +27257,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -27267,7 +27267,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -27277,12 +27277,12 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27317,7 +27317,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27339,32 +27339,32 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -27384,12 +27384,12 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27399,7 +27399,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27421,12 +27421,12 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -27481,7 +27481,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27503,12 +27503,12 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27585,32 +27585,27 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I334" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27630,7 +27625,7 @@
       </c>
       <c r="N334" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O334" t="inlineStr">
@@ -27645,7 +27640,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27667,12 +27662,12 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -27687,7 +27682,12 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-22</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27722,7 +27722,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -27744,42 +27744,42 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -27789,12 +27789,12 @@
       </c>
       <c r="N336" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R336" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -27826,17 +27826,17 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -27846,12 +27846,12 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -27908,17 +27908,17 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -27928,12 +27928,12 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27968,7 +27968,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -27990,17 +27990,17 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -28040,7 +28040,7 @@
       </c>
       <c r="O339" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28072,7 +28072,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28154,32 +28154,32 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -28199,12 +28199,12 @@
       </c>
       <c r="N341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O341" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28236,32 +28236,32 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -28281,12 +28281,12 @@
       </c>
       <c r="N342" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O342" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28318,17 +28318,17 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -28338,12 +28338,12 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28400,17 +28400,17 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -28420,12 +28420,12 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28482,57 +28482,57 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28564,7 +28564,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -28584,12 +28584,12 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -28728,7 +28728,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28810,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -28974,32 +28974,32 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -29014,17 +29014,17 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -29056,39 +29056,39 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K352" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -29096,7 +29096,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CisR</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
@@ -29138,17 +29138,17 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p8</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -29178,17 +29178,17 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O353" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R353" t="inlineStr">
@@ -29198,39 +29198,19 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I9</t>
-        </is>
-      </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -29240,17 +29220,17 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -29260,34 +29240,34 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O354" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R354" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -29317,7 +29297,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -29332,7 +29312,7 @@
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29342,14 +29322,14 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="E356" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -29379,7 +29359,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -29404,19 +29384,19 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -29441,7 +29421,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -29466,19 +29446,19 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -29498,12 +29478,12 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -29528,19 +29508,19 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -29565,7 +29545,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -29590,7 +29570,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
@@ -31377,7 +31357,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -31387,7 +31367,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -31408,17 +31388,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">LCC-V</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -31433,13 +31413,13 @@
         <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V</t>
+          <t xml:space="preserve">LCC-V 99.17%</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -31470,12 +31450,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17%</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -31485,7 +31465,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="E59">
@@ -31495,18 +31475,18 @@
         <v>0</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LnCap (m3) (sortER)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -31516,7 +31496,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E60">
@@ -31532,7 +31512,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap (m3) (sortER)</t>
+          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -31542,7 +31522,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -31563,7 +31543,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada CASPEX mCherry 1 (no use)</t>
+          <t xml:space="preserve">LnCap Canadaa V1G1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -31573,7 +31553,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -31594,7 +31574,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canadaa V1G1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -31604,7 +31584,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -31619,13 +31599,13 @@
         <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -31650,13 +31630,13 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -31681,13 +31661,13 @@
         <v>0</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select H</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -31712,23 +31692,23 @@
         <v>0</v>
       </c>
       <c r="G66">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select H</t>
+          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -31737,7 +31717,7 @@
         </is>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -31749,7 +31729,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 KO rep2</t>
+          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -31759,7 +31739,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -31780,7 +31760,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145 ATF3 OX rep2</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -31790,12 +31770,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="E69">
@@ -31811,22 +31791,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">HEK APEX1 KO g2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E70">
@@ -31842,7 +31822,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 KO g2</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31852,12 +31832,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E71">
@@ -31873,7 +31853,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK APEX1 g1</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31883,12 +31863,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E72">
@@ -31904,7 +31884,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK ATF3 KO 20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -31914,12 +31894,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E73">
@@ -31935,7 +31915,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO 20</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -31957,7 +31937,7 @@
         <v>1</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -31966,7 +31946,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 KO10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -31988,7 +31968,7 @@
         <v>1</v>
       </c>
       <c r="F75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -31997,7 +31977,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO10</t>
+          <t xml:space="preserve">HEK ATF3 OX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -32007,7 +31987,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -32028,7 +32008,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX</t>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -32059,7 +32039,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -32081,7 +32061,7 @@
         <v>1</v>
       </c>
       <c r="F78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -32090,7 +32070,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 OX10r1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -32112,7 +32092,7 @@
         <v>1</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -32121,7 +32101,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX10r1</t>
+          <t xml:space="preserve">HEK ATF3 OX20r1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -32152,7 +32132,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX20r1</t>
+          <t xml:space="preserve">HEK ATF3OX10r1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -32183,7 +32163,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3OX10r1</t>
+          <t xml:space="preserve">HEK ATP7B KO-1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -32193,7 +32173,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -32214,7 +32194,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-1</t>
+          <t xml:space="preserve">HEK ATP7B KO-2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -32245,7 +32225,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-2</t>
+          <t xml:space="preserve">HEK ATP7B KO-3</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -32276,7 +32256,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO-3</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -32286,12 +32266,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E85">
@@ -32307,7 +32287,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -32317,12 +32297,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E86">
@@ -32338,7 +32318,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -32348,12 +32328,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E87">
@@ -32369,7 +32349,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -32379,12 +32359,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E88">
@@ -32400,7 +32380,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -32415,7 +32395,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E89">
@@ -32431,7 +32411,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -32441,7 +32421,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -32462,7 +32442,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -32472,12 +32452,12 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E91">
@@ -32493,7 +32473,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g2</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -32508,7 +32488,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E92">
@@ -32524,7 +32504,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g2</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -32555,7 +32535,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -32570,7 +32550,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E94">
@@ -32586,7 +32566,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -32601,7 +32581,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E95">
@@ -32617,7 +32597,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -32632,7 +32612,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E96">
@@ -32648,7 +32628,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -32663,7 +32643,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E97">
@@ -32679,7 +32659,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -32694,7 +32674,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E98">
@@ -32710,7 +32690,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -32725,7 +32705,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="E99">
@@ -32741,7 +32721,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -32772,7 +32752,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -32787,7 +32767,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="E101">
@@ -32803,7 +32783,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -32813,12 +32793,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E102">
@@ -32834,7 +32814,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 OX 3xFLAG</t>
+          <t xml:space="preserve">HEK gNT (10)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -32844,12 +32824,12 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E103">
@@ -32865,7 +32845,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">HEK lef1 OX</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -32875,12 +32855,12 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E104">
@@ -32896,17 +32876,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK lef1 OX</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -32927,7 +32907,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 KO20</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -32958,7 +32938,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO20</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -32968,7 +32948,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -32989,7 +32969,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep2</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -33011,7 +32991,7 @@
         <v>1</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108">
         <v>1</v>
@@ -34418,6 +34398,53 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -34656,10 +34683,10 @@
         <v>81</v>
       </c>
       <c r="I6">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J6">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -19969,7 +19969,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-0</t>
+          <t xml:space="preserve">v-mtrdyhss-1</t>
         </is>
       </c>
     </row>
@@ -20051,17 +20051,17 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdyhss-1</t>
+          <t xml:space="preserve">v-mtrdz1vx-0</t>
         </is>
       </c>
     </row>
@@ -20133,12 +20133,12 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -20193,7 +20193,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-1</t>
         </is>
       </c>
     </row>
@@ -20215,17 +20215,17 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -20235,12 +20235,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -20250,7 +20245,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -20275,7 +20270,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-1</t>
+          <t xml:space="preserve">v-335</t>
         </is>
       </c>
     </row>
@@ -20297,7 +20292,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -20352,7 +20347,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-335</t>
+          <t xml:space="preserve">v-336</t>
         </is>
       </c>
     </row>
@@ -20374,7 +20369,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20384,7 +20379,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -20394,7 +20389,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-11-27</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27-11-25</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-336</t>
+          <t xml:space="preserve">v-337</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -20471,12 +20471,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-11-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-337</t>
+          <t xml:space="preserve">v-338</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -20553,12 +20553,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-338</t>
+          <t xml:space="preserve">v-339</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -20635,12 +20635,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -20675,7 +20675,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-339</t>
+          <t xml:space="preserve">v-340</t>
         </is>
       </c>
     </row>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -20717,12 +20717,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
@@ -20757,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-340</t>
+          <t xml:space="preserve">v-341</t>
         </is>
       </c>
     </row>
@@ -20779,34 +20774,39 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p21</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -20824,7 +20824,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-341</t>
+          <t xml:space="preserve">v-mtrdx0po-0</t>
         </is>
       </c>
     </row>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-mtrdx0po-1</t>
         </is>
       </c>
     </row>
@@ -20938,17 +20938,17 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -20958,17 +20958,17 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-1</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21184,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -21276,7 +21276,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -21286,12 +21286,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -21348,39 +21348,39 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21388,17 +21388,17 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -21430,32 +21430,32 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -21470,17 +21470,17 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -21512,7 +21512,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -21594,39 +21594,39 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21634,17 +21634,17 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -21676,17 +21676,17 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -21696,17 +21696,17 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -21716,17 +21716,17 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O262" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21758,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">p51</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -21778,12 +21778,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-10</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/11/2025</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21840,42 +21840,42 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p17</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p15</t>
-        </is>
-      </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre0w3q-1</t>
         </is>
       </c>
     </row>
@@ -22004,17 +22004,17 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-1</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-mtre1ko0-1</t>
         </is>
       </c>
     </row>
@@ -22168,57 +22168,57 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O268" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-1</t>
+          <t xml:space="preserve">v-362</t>
         </is>
       </c>
     </row>
@@ -22250,32 +22250,32 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2025-12-04</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
+          <t xml:space="preserve">4/12/2025</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -22300,7 +22300,7 @@
       </c>
       <c r="O269" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
@@ -22310,7 +22310,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-362</t>
+          <t xml:space="preserve">v-363</t>
         </is>
       </c>
     </row>
@@ -22332,12 +22332,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEXe g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="O270" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
@@ -22392,7 +22392,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-363</t>
+          <t xml:space="preserve">v-364</t>
         </is>
       </c>
     </row>
@@ -22414,32 +22414,32 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-04</t>
+          <t xml:space="preserve">2025-12-05</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/12/2025</t>
+          <t xml:space="preserve">5/12/2025</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -22464,7 +22464,7 @@
       </c>
       <c r="O271" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R271" t="inlineStr">
@@ -22474,7 +22474,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-364</t>
+          <t xml:space="preserve">v-365</t>
         </is>
       </c>
     </row>
@@ -22496,7 +22496,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -22516,12 +22516,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-365</t>
+          <t xml:space="preserve">v-366</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
@@ -22638,7 +22638,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-366</t>
+          <t xml:space="preserve">v-367</t>
         </is>
       </c>
     </row>
@@ -22660,37 +22660,32 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1 (eski)</t>
+          <t xml:space="preserve">MDA-MB g1.1 p10</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-02</t>
+          <t xml:space="preserve">2026-06-22</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/12/2025</t>
-        </is>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">22-06-26</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -22700,12 +22695,12 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O274" t="inlineStr">
@@ -22720,7 +22715,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-367</t>
+          <t xml:space="preserve">v-371</t>
         </is>
       </c>
     </row>
@@ -22742,12 +22737,12 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB g1.1 p10</t>
+          <t xml:space="preserve">MDA-MB gNT</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -22787,7 +22782,7 @@
       </c>
       <c r="O275" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R275" t="inlineStr">
@@ -22797,7 +22792,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-371</t>
+          <t xml:space="preserve">v-372</t>
         </is>
       </c>
     </row>
@@ -22819,17 +22814,17 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">MDA-MB gNT</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -22839,12 +22834,17 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-22</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-06-26</t>
+          <t xml:space="preserve">31-07-26</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -22859,12 +22859,12 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O276" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-372</t>
+          <t xml:space="preserve">v-380</t>
         </is>
       </c>
     </row>
@@ -22891,22 +22891,22 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t xml:space="preserve">UMUT CELLS -4-</t>
+          <t xml:space="preserve">UMUT CELLS -80</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">A1</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p4</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -22916,17 +22916,17 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-12-31</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">31-12-25</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -22936,7 +22936,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -22946,7 +22946,7 @@
       </c>
       <c r="O277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
@@ -22956,7 +22956,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-380</t>
+          <t xml:space="preserve">v-83</t>
         </is>
       </c>
     </row>
@@ -22978,7 +22978,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t xml:space="preserve">A1</t>
+          <t xml:space="preserve">A2</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -23038,7 +23038,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-83</t>
+          <t xml:space="preserve">v-84</t>
         </is>
       </c>
     </row>
@@ -23060,32 +23060,32 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t xml:space="preserve">A2</t>
+          <t xml:space="preserve">A3</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-31</t>
+          <t xml:space="preserve">2025-12-23</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-12-25</t>
+          <t xml:space="preserve">23-12-25</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -23110,7 +23110,7 @@
       </c>
       <c r="O279" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-84</t>
+          <t xml:space="preserve">v-85</t>
         </is>
       </c>
     </row>
@@ -23142,22 +23142,22 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t xml:space="preserve">A3</t>
+          <t xml:space="preserve">A4</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-85</t>
+          <t xml:space="preserve">v-86</t>
         </is>
       </c>
     </row>
@@ -23224,7 +23224,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t xml:space="preserve">A4</t>
+          <t xml:space="preserve">A5</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -23284,7 +23284,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-86</t>
+          <t xml:space="preserve">v-87</t>
         </is>
       </c>
     </row>
@@ -23306,17 +23306,17 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t xml:space="preserve">A5</t>
+          <t xml:space="preserve">A6</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+5</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -23326,12 +23326,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-23</t>
+          <t xml:space="preserve">2026-01-02</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-12-25</t>
+          <t xml:space="preserve">2/1/2026</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="O282" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-87</t>
+          <t xml:space="preserve">v-88</t>
         </is>
       </c>
     </row>
@@ -23388,17 +23388,17 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t xml:space="preserve">A6</t>
+          <t xml:space="preserve">A7</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -23438,7 +23438,7 @@
       </c>
       <c r="O283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
@@ -23448,7 +23448,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-88</t>
+          <t xml:space="preserve">v-89</t>
         </is>
       </c>
     </row>
@@ -23470,22 +23470,22 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">A7</t>
+          <t xml:space="preserve">A8</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p5</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -23520,7 +23520,7 @@
       </c>
       <c r="O284" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R284" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-89</t>
+          <t xml:space="preserve">v-90</t>
         </is>
       </c>
     </row>
@@ -23552,32 +23552,32 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p5</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-02</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/1/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -23602,7 +23602,7 @@
       </c>
       <c r="O285" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
@@ -23612,7 +23612,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-90</t>
+          <t xml:space="preserve">v-91</t>
         </is>
       </c>
     </row>
@@ -23634,57 +23634,57 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-29</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">29-12-25</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
@@ -23694,7 +23694,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-91</t>
+          <t xml:space="preserve">v-92</t>
         </is>
       </c>
     </row>
@@ -23716,7 +23716,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -23776,7 +23776,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-92</t>
+          <t xml:space="preserve">v-93</t>
         </is>
       </c>
     </row>
@@ -23798,12 +23798,12 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -23833,7 +23833,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -23858,7 +23858,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-93</t>
+          <t xml:space="preserve">v-94</t>
         </is>
       </c>
     </row>
@@ -23880,7 +23880,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -23940,7 +23940,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-94</t>
+          <t xml:space="preserve">v-95</t>
         </is>
       </c>
     </row>
@@ -23962,17 +23962,17 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK JUN KO g1</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -23982,12 +23982,12 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-29</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">29-12-25</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -24022,7 +24022,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-95</t>
+          <t xml:space="preserve">v-96</t>
         </is>
       </c>
     </row>
@@ -24044,17 +24044,17 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN KO g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p30</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -24064,12 +24064,12 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
@@ -24104,7 +24104,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-96</t>
+          <t xml:space="preserve">v-97</t>
         </is>
       </c>
     </row>
@@ -24126,17 +24126,17 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK STAT1 KO g1</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">p30</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -24146,12 +24146,12 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-08</t>
+          <t xml:space="preserve">2025-12-18</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">8/1/2026</t>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
@@ -24186,7 +24186,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-97</t>
+          <t xml:space="preserve">v-98</t>
         </is>
       </c>
     </row>
@@ -24208,12 +24208,12 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B8</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g1</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -24258,7 +24258,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
@@ -24268,7 +24268,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-98</t>
+          <t xml:space="preserve">v-99</t>
         </is>
       </c>
     </row>
@@ -24290,12 +24290,12 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g2</t>
+          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -24340,7 +24340,7 @@
       </c>
       <c r="O294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
@@ -24350,7 +24350,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-99</t>
+          <t xml:space="preserve">v-100</t>
         </is>
       </c>
     </row>
@@ -24372,17 +24372,17 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SMARCE1 KO g1</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -24392,12 +24392,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -24407,7 +24402,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -24422,7 +24417,7 @@
       </c>
       <c r="O295" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
@@ -24432,7 +24427,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-100</t>
+          <t xml:space="preserve">v-101</t>
         </is>
       </c>
     </row>
@@ -24454,7 +24449,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -24464,7 +24459,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -24474,7 +24469,12 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -24509,7 +24509,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-101</t>
+          <t xml:space="preserve">v-102</t>
         </is>
       </c>
     </row>
@@ -24531,39 +24531,39 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK APEX1 g1</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p19</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-18</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-12-25</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p19</t>
-        </is>
-      </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-18</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18-12-25</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -24581,7 +24581,7 @@
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
@@ -24591,7 +24591,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-102</t>
+          <t xml:space="preserve">v-103</t>
         </is>
       </c>
     </row>
@@ -24613,17 +24613,17 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 g1</t>
+          <t xml:space="preserve">HEK STAT1 KO g2</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -24633,12 +24633,12 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-18</t>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-12-25</t>
+          <t xml:space="preserve">5/1/2026</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -24663,7 +24663,7 @@
       </c>
       <c r="O298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R298" t="inlineStr">
@@ -24673,7 +24673,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-103</t>
+          <t xml:space="preserve">v-104</t>
         </is>
       </c>
     </row>
@@ -24695,17 +24695,17 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK STAT1 KO g2</t>
+          <t xml:space="preserve">HEK gNT(20)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -24715,12 +24715,12 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-05</t>
+          <t xml:space="preserve">2026-01-14</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2026</t>
+          <t xml:space="preserve">14-01-26</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -24745,7 +24745,7 @@
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-104</t>
+          <t xml:space="preserve">v-105</t>
         </is>
       </c>
     </row>
@@ -24777,12 +24777,12 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT(20)</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -24812,7 +24812,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -24827,7 +24827,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-105</t>
+          <t xml:space="preserve">v-106</t>
         </is>
       </c>
     </row>
@@ -24859,12 +24859,12 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -24919,7 +24919,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-106</t>
+          <t xml:space="preserve">v-107</t>
         </is>
       </c>
     </row>
@@ -24941,32 +24941,32 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-14</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-01-26</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -24976,7 +24976,7 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
@@ -25001,7 +25001,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-107</t>
+          <t xml:space="preserve">v-108</t>
         </is>
       </c>
     </row>
@@ -25023,22 +25023,22 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -25058,7 +25058,7 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -25073,7 +25073,7 @@
       </c>
       <c r="O303" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R303" t="inlineStr">
@@ -25083,7 +25083,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-108</t>
+          <t xml:space="preserve">v-109</t>
         </is>
       </c>
     </row>
@@ -25105,57 +25105,57 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-01-08</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">8/1/2026</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O304" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
@@ -25165,7 +25165,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-109</t>
+          <t xml:space="preserve">v-110</t>
         </is>
       </c>
     </row>
@@ -25187,22 +25187,22 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p7</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -25237,7 +25237,7 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g5.1</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-110</t>
+          <t xml:space="preserve">v-111</t>
         </is>
       </c>
     </row>
@@ -25269,22 +25269,22 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g5.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p7</t>
+          <t xml:space="preserve">p|+7</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g5.1</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-111</t>
+          <t xml:space="preserve">v-112</t>
         </is>
       </c>
     </row>
@@ -25351,22 +25351,22 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p|+7</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -25391,17 +25391,17 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O307" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-112</t>
+          <t xml:space="preserve">v-113</t>
         </is>
       </c>
     </row>
@@ -25433,7 +25433,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -25493,7 +25493,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-113</t>
+          <t xml:space="preserve">v-114</t>
         </is>
       </c>
     </row>
@@ -25515,39 +25515,39 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+9</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-01-08</t>
-        </is>
-      </c>
-      <c r="I309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8/1/2026</t>
-        </is>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -25555,17 +25555,17 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DSg1.2</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-114</t>
+          <t xml:space="preserve">v-115</t>
         </is>
       </c>
     </row>
@@ -25597,22 +25597,22 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">D7</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX DSg1.2</t>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -25647,7 +25647,7 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t xml:space="preserve">DSg1.2</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
@@ -25657,7 +25657,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-115</t>
+          <t xml:space="preserve">v-116</t>
         </is>
       </c>
     </row>
@@ -25679,32 +25679,32 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">D7</t>
+          <t xml:space="preserve">D8</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
@@ -25739,7 +25739,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-116</t>
+          <t xml:space="preserve">v-117</t>
         </is>
       </c>
     </row>
@@ -25761,32 +25761,32 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">D8</t>
+          <t xml:space="preserve">D9</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-05</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">5/5/2025</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-117</t>
+          <t xml:space="preserve">v-118</t>
         </is>
       </c>
     </row>
@@ -25843,17 +25843,17 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">D9</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7 HOXB6 OX</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p6</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -25863,37 +25863,37 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-05</t>
+          <t xml:space="preserve">2026-06-01</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/5/2025</t>
+          <t xml:space="preserve">1/6/2026</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R313" t="inlineStr">
@@ -25903,7 +25903,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-118</t>
+          <t xml:space="preserve">v-119</t>
         </is>
       </c>
     </row>
@@ -25925,12 +25925,12 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">E1</t>
+          <t xml:space="preserve">E2</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 HOXB6 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -25960,7 +25960,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -25975,7 +25975,7 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R314" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-119</t>
+          <t xml:space="preserve">v-120</t>
         </is>
       </c>
     </row>
@@ -26007,12 +26007,12 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t xml:space="preserve">E2</t>
+          <t xml:space="preserve">E3</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g1</t>
+          <t xml:space="preserve">Huh7 CBX3 OX</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -26042,7 +26042,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-120</t>
+          <t xml:space="preserve">v-121</t>
         </is>
       </c>
     </row>
@@ -26089,12 +26089,12 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t xml:space="preserve">E3</t>
+          <t xml:space="preserve">E4</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 CBX3 OX</t>
+          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-121</t>
+          <t xml:space="preserve">v-122</t>
         </is>
       </c>
     </row>
@@ -26171,32 +26171,32 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">E4</t>
+          <t xml:space="preserve">E5</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 POU3F3 KO g2</t>
+          <t xml:space="preserve">Huh7 TOX4 KO</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p6</t>
+          <t xml:space="preserve">p+12</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-01</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">1/6/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -26206,7 +26206,7 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -26221,7 +26221,7 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
@@ -26231,7 +26231,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-122</t>
+          <t xml:space="preserve">v-123</t>
         </is>
       </c>
     </row>
@@ -26253,22 +26253,22 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">E5</t>
+          <t xml:space="preserve">E6</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+12</t>
+          <t xml:space="preserve">p82</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-123</t>
+          <t xml:space="preserve">v-124</t>
         </is>
       </c>
     </row>
@@ -26335,32 +26335,32 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">E6</t>
+          <t xml:space="preserve">E7</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p82</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">caNT read</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -26370,7 +26370,7 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
@@ -26385,7 +26385,7 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
@@ -26395,7 +26395,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-124</t>
+          <t xml:space="preserve">v-125</t>
         </is>
       </c>
     </row>
@@ -26417,32 +26417,32 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t xml:space="preserve">E7</t>
+          <t xml:space="preserve">E8</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 TOX4 KO g1</t>
+          <t xml:space="preserve">Huh7 ATP7B KO</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p81</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-21</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">caNT read</t>
+          <t xml:space="preserve">21-04-25</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -26452,7 +26452,7 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -26467,7 +26467,7 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R320" t="inlineStr">
@@ -26477,7 +26477,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-125</t>
+          <t xml:space="preserve">v-126</t>
         </is>
       </c>
     </row>
@@ -26499,17 +26499,17 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">E8</t>
+          <t xml:space="preserve">E9</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO</t>
+          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p81</t>
+          <t xml:space="preserve">p84</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -26519,12 +26519,12 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-21</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-126</t>
+          <t xml:space="preserve">v-127</t>
         </is>
       </c>
     </row>
@@ -26581,17 +26581,17 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t xml:space="preserve">E9</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATP7B KO #24</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p84</t>
+          <t xml:space="preserve">p48</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
@@ -26601,22 +26601,22 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2026-05-04</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">4/5/2026</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -26631,7 +26631,7 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R322" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-127</t>
+          <t xml:space="preserve">v-128</t>
         </is>
       </c>
     </row>
@@ -26663,7 +26663,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">F2</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -26723,7 +26723,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-128</t>
+          <t xml:space="preserve">v-129</t>
         </is>
       </c>
     </row>
@@ -26745,17 +26745,17 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">F2</t>
+          <t xml:space="preserve">F3</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p48</t>
+          <t xml:space="preserve">p22</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -26780,7 +26780,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -26795,7 +26795,7 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R324" t="inlineStr">
@@ -26805,7 +26805,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-129</t>
+          <t xml:space="preserve">v-130</t>
         </is>
       </c>
     </row>
@@ -26827,7 +26827,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">F3</t>
+          <t xml:space="preserve">F4</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -26887,7 +26887,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-130</t>
+          <t xml:space="preserve">v-131</t>
         </is>
       </c>
     </row>
@@ -26909,17 +26909,17 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">F4</t>
+          <t xml:space="preserve">F5</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK POU3F3 KO g2</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p22</t>
+          <t xml:space="preserve">p37</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R326" t="inlineStr">
@@ -26969,7 +26969,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-131</t>
+          <t xml:space="preserve">v-132</t>
         </is>
       </c>
     </row>
@@ -26991,22 +26991,22 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">F5</t>
+          <t xml:space="preserve">F6</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p37</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R327" t="inlineStr">
@@ -27051,7 +27051,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-132</t>
+          <t xml:space="preserve">v-133</t>
         </is>
       </c>
     </row>
@@ -27073,17 +27073,17 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t xml:space="preserve">F6</t>
+          <t xml:space="preserve">F7</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK TOX4 KO g2</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -27093,12 +27093,12 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -27108,7 +27108,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -27123,7 +27123,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="R328" t="inlineStr">
@@ -27133,7 +27133,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-133</t>
+          <t xml:space="preserve">v-134</t>
         </is>
       </c>
     </row>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">F7</t>
+          <t xml:space="preserve">F8</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+7</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -27175,12 +27175,12 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2025-05-02</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2/5/2025</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -27215,7 +27215,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-134</t>
+          <t xml:space="preserve">v-135</t>
         </is>
       </c>
     </row>
@@ -27237,32 +27237,32 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t xml:space="preserve">F8</t>
+          <t xml:space="preserve">F9</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK TOX4 KO g2</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+7</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-02</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/5/2025</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R330" t="inlineStr">
@@ -27297,7 +27297,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-135</t>
+          <t xml:space="preserve">v-136</t>
         </is>
       </c>
     </row>
@@ -27319,37 +27319,37 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">F9</t>
+          <t xml:space="preserve">G1</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -27364,12 +27364,22 @@
       </c>
       <c r="N331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
         </is>
       </c>
       <c r="R331" t="inlineStr">
@@ -27379,7 +27389,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-136</t>
+          <t xml:space="preserve">v-137</t>
         </is>
       </c>
     </row>
@@ -27401,7 +27411,7 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t xml:space="preserve">G1</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -27471,7 +27481,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-137</t>
+          <t xml:space="preserve">v-138</t>
         </is>
       </c>
     </row>
@@ -27493,17 +27503,17 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">G2</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -27513,12 +27523,12 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -27543,17 +27553,7 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
-        </is>
-      </c>
-      <c r="P333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
-        </is>
-      </c>
-      <c r="Q333" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="R333" t="inlineStr">
@@ -27563,7 +27563,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-138</t>
+          <t xml:space="preserve">v-139</t>
         </is>
       </c>
     </row>
@@ -27585,7 +27585,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -27605,12 +27605,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -27645,7 +27645,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-139</t>
+          <t xml:space="preserve">v-140</t>
         </is>
       </c>
     </row>
@@ -27667,32 +27667,32 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -27712,12 +27712,12 @@
       </c>
       <c r="N335" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R335" t="inlineStr">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-140</t>
+          <t xml:space="preserve">v-141</t>
         </is>
       </c>
     </row>
@@ -27749,12 +27749,12 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-141</t>
+          <t xml:space="preserve">v-142</t>
         </is>
       </c>
     </row>
@@ -27831,12 +27831,12 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-142</t>
+          <t xml:space="preserve">v-143</t>
         </is>
       </c>
     </row>
@@ -27913,32 +27913,27 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
-        </is>
-      </c>
-      <c r="I338" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -27958,7 +27953,7 @@
       </c>
       <c r="N338" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O338" t="inlineStr">
@@ -27973,7 +27968,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-143</t>
+          <t xml:space="preserve">v-144</t>
         </is>
       </c>
     </row>
@@ -27995,12 +27990,12 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -28015,7 +28010,12 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-04-22</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -28050,7 +28050,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-144</t>
+          <t xml:space="preserve">v-145</t>
         </is>
       </c>
     </row>
@@ -28072,42 +28072,42 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -28117,12 +28117,12 @@
       </c>
       <c r="N340" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O340" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R340" t="inlineStr">
@@ -28132,7 +28132,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-145</t>
+          <t xml:space="preserve">v-146</t>
         </is>
       </c>
     </row>
@@ -28154,17 +28154,17 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -28174,12 +28174,12 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -28214,7 +28214,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-146</t>
+          <t xml:space="preserve">v-147</t>
         </is>
       </c>
     </row>
@@ -28236,17 +28236,17 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -28256,12 +28256,12 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-147</t>
+          <t xml:space="preserve">v-148</t>
         </is>
       </c>
     </row>
@@ -28318,17 +28318,17 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -28353,7 +28353,7 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="O343" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R343" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-148</t>
+          <t xml:space="preserve">v-149</t>
         </is>
       </c>
     </row>
@@ -28400,7 +28400,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -28460,7 +28460,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-149</t>
+          <t xml:space="preserve">v-150</t>
         </is>
       </c>
     </row>
@@ -28482,32 +28482,32 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -28527,12 +28527,12 @@
       </c>
       <c r="N345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O345" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R345" t="inlineStr">
@@ -28542,7 +28542,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-150</t>
+          <t xml:space="preserve">v-151</t>
         </is>
       </c>
     </row>
@@ -28564,32 +28564,32 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -28599,7 +28599,7 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -28609,12 +28609,12 @@
       </c>
       <c r="N346" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O346" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="R346" t="inlineStr">
@@ -28624,7 +28624,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-151</t>
+          <t xml:space="preserve">v-152</t>
         </is>
       </c>
     </row>
@@ -28646,17 +28646,17 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -28666,12 +28666,12 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -28696,7 +28696,7 @@
       </c>
       <c r="O347" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R347" t="inlineStr">
@@ -28706,7 +28706,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-152</t>
+          <t xml:space="preserve">v-153</t>
         </is>
       </c>
     </row>
@@ -28728,17 +28728,17 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -28748,12 +28748,12 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -28788,7 +28788,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-153</t>
+          <t xml:space="preserve">v-154</t>
         </is>
       </c>
     </row>
@@ -28810,57 +28810,57 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R349" t="inlineStr">
@@ -28870,7 +28870,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-154</t>
+          <t xml:space="preserve">v-155</t>
         </is>
       </c>
     </row>
@@ -28892,7 +28892,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
@@ -28902,7 +28902,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -28912,12 +28912,12 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -28952,7 +28952,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-155</t>
+          <t xml:space="preserve">v-156</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -29034,7 +29034,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-156</t>
+          <t xml:space="preserve">v-157</t>
         </is>
       </c>
     </row>
@@ -29056,7 +29056,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
@@ -29116,7 +29116,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-157</t>
+          <t xml:space="preserve">v-158</t>
         </is>
       </c>
     </row>
@@ -29138,7 +29138,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -29198,7 +29198,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-158</t>
+          <t xml:space="preserve">v-159</t>
         </is>
       </c>
     </row>
@@ -29220,7 +29220,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-159</t>
+          <t xml:space="preserve">v-160</t>
         </is>
       </c>
     </row>
@@ -29302,32 +29302,32 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K355" t="inlineStr">
@@ -29342,17 +29342,17 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O355" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R355" t="inlineStr">
@@ -29362,7 +29362,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-160</t>
+          <t xml:space="preserve">v-161</t>
         </is>
       </c>
     </row>
@@ -29384,39 +29384,39 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I8</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p?</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unknown</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-04-24</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24-04-25</t>
-        </is>
-      </c>
-      <c r="K356" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -29424,7 +29424,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CisR</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -29444,7 +29444,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-161</t>
+          <t xml:space="preserve">v-162</t>
         </is>
       </c>
     </row>
@@ -29466,17 +29466,17 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I9</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p8</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -29506,17 +29506,17 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O357" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R357" t="inlineStr">
@@ -29526,39 +29526,19 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-162</t>
+          <t xml:space="preserve">v-163</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rack 1</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UMUT CELLS -80</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I9</t>
-        </is>
-      </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -29568,54 +29548,54 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">2026-09-07</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O358" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R358" t="inlineStr">
         <is>
-          <t xml:space="preserve">stored</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-163</t>
+          <t xml:space="preserve">v-mtrdxsum-0</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="E359" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -29645,7 +29625,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -29670,7 +29650,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdxsum-0</t>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
         </is>
       </c>
     </row>
@@ -30434,17 +30414,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">HepG2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -30459,18 +30439,18 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">HepG2</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -30480,7 +30460,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="E24">
@@ -30490,18 +30470,18 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LUCX gP1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -30511,7 +30491,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="E25">
@@ -30521,38 +30501,38 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -34310,6 +34290,53 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-08</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK 3xFLAG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rack 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UMUT CELLS -4-</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">v-mtrdyhss-0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -34548,10 +34575,10 @@
         <v>81</v>
       </c>
       <c r="I6">
+        <v>40</v>
+      </c>
+      <c r="J6">
         <v>41</v>
-      </c>
-      <c r="J6">
-        <v>40</v>
       </c>
     </row>
     <row r="7">

--- a/cellstocks/data/umut.xlsx
+++ b/cellstocks/data/umut.xlsx
@@ -20051,12 +20051,12 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t xml:space="preserve">A8</t>
+          <t xml:space="preserve">A9</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-0</t>
+          <t xml:space="preserve">v-mtrdz1vx-1</t>
         </is>
       </c>
     </row>
@@ -20133,17 +20133,17 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t xml:space="preserve">A9</t>
+          <t xml:space="preserve">B1</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -20153,12 +20153,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -20168,7 +20163,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -20193,7 +20188,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdz1vx-1</t>
+          <t xml:space="preserve">v-335</t>
         </is>
       </c>
     </row>
@@ -20215,7 +20210,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t xml:space="preserve">B1</t>
+          <t xml:space="preserve">B2</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -20270,7 +20265,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-335</t>
+          <t xml:space="preserve">v-336</t>
         </is>
       </c>
     </row>
@@ -20292,7 +20287,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t xml:space="preserve">B2</t>
+          <t xml:space="preserve">B3</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -20302,7 +20297,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -20312,7 +20307,12 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2025-11-27</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27-11-25</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-336</t>
+          <t xml:space="preserve">v-337</t>
         </is>
       </c>
     </row>
@@ -20369,7 +20369,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t xml:space="preserve">B3</t>
+          <t xml:space="preserve">B4</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -20379,7 +20379,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -20389,12 +20389,12 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-11-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-337</t>
+          <t xml:space="preserve">v-338</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20451,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t xml:space="preserve">B4</t>
+          <t xml:space="preserve">B5</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -20471,12 +20471,12 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
@@ -20511,7 +20511,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-338</t>
+          <t xml:space="preserve">v-339</t>
         </is>
       </c>
     </row>
@@ -20533,7 +20533,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t xml:space="preserve">B5</t>
+          <t xml:space="preserve">B6</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -20543,7 +20543,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -20553,12 +20553,12 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-11-06</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">6/11/2025</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-339</t>
+          <t xml:space="preserve">v-340</t>
         </is>
       </c>
     </row>
@@ -20615,7 +20615,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t xml:space="preserve">B6</t>
+          <t xml:space="preserve">B7</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -20635,12 +20635,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-06</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6/11/2025</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
@@ -20675,7 +20670,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-340</t>
+          <t xml:space="preserve">v-341</t>
         </is>
       </c>
     </row>
@@ -20697,34 +20692,39 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t xml:space="preserve">B7</t>
+          <t xml:space="preserve">B9</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p21</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
           <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p14</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unknown</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEK293T</t>
-        </is>
-      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R250" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-341</t>
+          <t xml:space="preserve">v-mtrdx0po-1</t>
         </is>
       </c>
     </row>
@@ -20774,17 +20774,17 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t xml:space="preserve">B8</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -20794,17 +20794,17 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -20824,7 +20824,7 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R251" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-0</t>
+          <t xml:space="preserve">v-344</t>
         </is>
       </c>
     </row>
@@ -20856,17 +20856,17 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t xml:space="preserve">B9</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -20876,17 +20876,17 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="O252" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R252" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtrdx0po-1</t>
+          <t xml:space="preserve">v-345</t>
         </is>
       </c>
     </row>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -20998,7 +20998,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-344</t>
+          <t xml:space="preserve">v-346</t>
         </is>
       </c>
     </row>
@@ -21020,7 +21020,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-345</t>
+          <t xml:space="preserve">v-347</t>
         </is>
       </c>
     </row>
@@ -21102,7 +21102,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -21122,12 +21122,12 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-346</t>
+          <t xml:space="preserve">v-348</t>
         </is>
       </c>
     </row>
@@ -21184,39 +21184,39 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">C6</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+3</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-11</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11/12/2025</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p10</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-12</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12/12/2025</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21224,17 +21224,17 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="R256" t="inlineStr">
@@ -21244,7 +21244,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-347</t>
+          <t xml:space="preserve">v-349</t>
         </is>
       </c>
     </row>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C7</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -21326,7 +21326,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-348</t>
+          <t xml:space="preserve">v-350</t>
         </is>
       </c>
     </row>
@@ -21348,32 +21348,32 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t xml:space="preserve">C6</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX gNT</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-11</t>
+          <t xml:space="preserve">2025-12-17</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">11/12/2025</t>
+          <t xml:space="preserve">17-12-25</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -21388,17 +21388,17 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O258" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R258" t="inlineStr">
@@ -21408,7 +21408,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-349</t>
+          <t xml:space="preserve">v-351</t>
         </is>
       </c>
     </row>
@@ -21430,39 +21430,39 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t xml:space="preserve">C7</t>
+          <t xml:space="preserve">C9</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-05</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5/12/2025</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
           <t xml:space="preserve">Du145</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p11</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-12-17</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17-12-25</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Du145</t>
-        </is>
-      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t xml:space="preserve">WT</t>
@@ -21470,17 +21470,17 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O259" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="R259" t="inlineStr">
@@ -21490,7 +21490,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-350</t>
+          <t xml:space="preserve">v-352</t>
         </is>
       </c>
     </row>
@@ -21512,17 +21512,17 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p51</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -21532,17 +21532,17 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-17</t>
+          <t xml:space="preserve">2025-11-10</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-12-25</t>
+          <t xml:space="preserve">10/11/2025</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-351</t>
+          <t xml:space="preserve">v-353</t>
         </is>
       </c>
     </row>
@@ -21594,12 +21594,12 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t xml:space="preserve">C9</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -21614,17 +21614,17 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-05</t>
+          <t xml:space="preserve">2026-08-10</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/12/2025</t>
+          <t xml:space="preserve">10/8/2026</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">Huh7</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -21634,17 +21634,17 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="O261" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-352</t>
+          <t xml:space="preserve">v-354</t>
         </is>
       </c>
     </row>
@@ -21676,42 +21676,42 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p17</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p51</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-11-10</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/11/2025</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-353</t>
+          <t xml:space="preserve">v-mtre0w3q-0</t>
         </is>
       </c>
     </row>
@@ -21758,42 +21758,42 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p17</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
           <t xml:space="preserve">Huh7</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">p15</t>
-        </is>
-      </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">absolute</t>
-        </is>
-      </c>
-      <c r="H263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-08-10</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/8/2026</t>
-        </is>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Huh7</t>
-        </is>
-      </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">WT</t>
+          <t xml:space="preserve">FLAG</t>
         </is>
       </c>
       <c r="M263" t="inlineStr">
@@ -21818,7 +21818,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-354</t>
+          <t xml:space="preserve">v-mtre0w3q-1</t>
         </is>
       </c>
     </row>
@@ -21840,17 +21840,17 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -21900,7 +21900,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-0</t>
+          <t xml:space="preserve">v-mtre1ko0-0</t>
         </is>
       </c>
     </row>
@@ -21922,17 +21922,17 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -21957,7 +21957,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t xml:space="preserve">FLAG</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre0w3q-1</t>
+          <t xml:space="preserve">v-mtre1ko0-1</t>
         </is>
       </c>
     </row>
@@ -22004,57 +22004,57 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">E1</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2025-12-02</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07</t>
+          <t xml:space="preserve">2/12/2025</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">WT</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t xml:space="preserve">v-mtre1ko0-0</t>
+          <t xml:space="preserve">v-362</t>
         </is>
   